--- a/Savets 2026/admin/output/Knockout Scorecards.xlsx
+++ b/Savets 2026/admin/output/Knockout Scorecards.xlsx
@@ -66,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1396" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1396" uniqueCount="52">
   <si>
     <t>ROUND:</t>
   </si>
@@ -192,6 +192,27 @@
   </si>
   <si>
     <t>19:30</t>
+  </si>
+  <si>
+    <t>Bernard Stewe &amp; Lindsay October</t>
+  </si>
+  <si>
+    <t>Allan Clark &amp; Gaston Koetaan</t>
+  </si>
+  <si>
+    <t>Frans Erasmus &amp; Demos Dracoulides</t>
+  </si>
+  <si>
+    <t>Simon Dimant &amp; Jose da Silva</t>
+  </si>
+  <si>
+    <t>Ashley Wesson &amp; Terence Cable</t>
+  </si>
+  <si>
+    <t>Saaliegh Jabaar &amp; Rafiq Tofa</t>
+  </si>
+  <si>
+    <t>Zahier Isaacs &amp; David Nwafo</t>
   </si>
   <si>
     <t>20:00</t>
@@ -3740,7 +3761,7 @@
         <v>18</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="C5" s="17"/>
       <c r="D5" s="18"/>
@@ -3756,7 +3777,7 @@
         <v>20</v>
       </c>
       <c r="B6" s="24" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="C6" s="25"/>
       <c r="D6" s="26"/>
@@ -3932,7 +3953,7 @@
         <v>18</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="C5" s="17"/>
       <c r="D5" s="18"/>
@@ -3948,7 +3969,7 @@
         <v>20</v>
       </c>
       <c r="B6" s="24" t="s">
-        <v>19</v>
+        <v>45</v>
       </c>
       <c r="C6" s="25"/>
       <c r="D6" s="26"/>
@@ -4124,7 +4145,7 @@
         <v>18</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>19</v>
+        <v>46</v>
       </c>
       <c r="C5" s="17"/>
       <c r="D5" s="18"/>
@@ -4316,7 +4337,7 @@
         <v>18</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>19</v>
+        <v>47</v>
       </c>
       <c r="C5" s="17"/>
       <c r="D5" s="18"/>
@@ -4332,7 +4353,7 @@
         <v>20</v>
       </c>
       <c r="B6" s="24" t="s">
-        <v>19</v>
+        <v>48</v>
       </c>
       <c r="C6" s="25"/>
       <c r="D6" s="26"/>
@@ -4447,7 +4468,7 @@
         <v>3</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>5</v>
@@ -4639,7 +4660,7 @@
         <v>3</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>5</v>
@@ -4817,7 +4838,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="3" t="s">
@@ -5009,7 +5030,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="3" t="s">
@@ -5393,7 +5414,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="3" t="s">
@@ -5585,7 +5606,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="3" t="s">
@@ -5814,7 +5835,7 @@
       </c>
       <c r="H2" s="7"/>
       <c r="I2" s="7" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="J2" s="7"/>
     </row>
@@ -6006,7 +6027,7 @@
       </c>
       <c r="H2" s="7"/>
       <c r="I2" s="7" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="J2" s="7"/>
     </row>
@@ -6198,7 +6219,7 @@
       </c>
       <c r="H2" s="7"/>
       <c r="I2" s="7" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="J2" s="7"/>
     </row>
@@ -6390,7 +6411,7 @@
       </c>
       <c r="H2" s="7"/>
       <c r="I2" s="7" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="J2" s="7"/>
     </row>
@@ -6582,7 +6603,7 @@
       </c>
       <c r="H2" s="7"/>
       <c r="I2" s="7" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="J2" s="7"/>
     </row>
@@ -6774,7 +6795,7 @@
       </c>
       <c r="H2" s="7"/>
       <c r="I2" s="7" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="J2" s="7"/>
     </row>
@@ -6966,7 +6987,7 @@
       </c>
       <c r="H2" s="7"/>
       <c r="I2" s="7" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="J2" s="7"/>
     </row>
@@ -7158,7 +7179,7 @@
       </c>
       <c r="H2" s="7"/>
       <c r="I2" s="7" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="J2" s="7"/>
     </row>
@@ -7542,7 +7563,7 @@
       </c>
       <c r="H2" s="7"/>
       <c r="I2" s="7" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="J2" s="7"/>
     </row>
@@ -7734,7 +7755,7 @@
       </c>
       <c r="H2" s="7"/>
       <c r="I2" s="7" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="J2" s="7"/>
     </row>
@@ -7926,7 +7947,7 @@
       </c>
       <c r="H2" s="7"/>
       <c r="I2" s="7" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="J2" s="7"/>
     </row>
@@ -8118,7 +8139,7 @@
       </c>
       <c r="H2" s="7"/>
       <c r="I2" s="7" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="J2" s="7"/>
     </row>
@@ -8310,7 +8331,7 @@
       </c>
       <c r="H2" s="7"/>
       <c r="I2" s="7" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="J2" s="7"/>
     </row>
@@ -8502,7 +8523,7 @@
       </c>
       <c r="H2" s="7"/>
       <c r="I2" s="7" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="J2" s="7"/>
     </row>
@@ -8657,7 +8678,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="3" t="s">
@@ -8694,7 +8715,7 @@
       </c>
       <c r="H2" s="7"/>
       <c r="I2" s="7" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="J2" s="7"/>
     </row>

--- a/Savets 2026/admin/output/Knockout Scorecards.xlsx
+++ b/Savets 2026/admin/output/Knockout Scorecards.xlsx
@@ -35,38 +35,23 @@
     <sheet sheetId="29" name="Men's 50+ Final M1" state="visible" r:id="rId32"/>
     <sheet sheetId="30" name="Men's 60+ Final M1" state="visible" r:id="rId33"/>
     <sheet sheetId="31" name="Men's Doubles Final M1" state="visible" r:id="rId34"/>
-    <sheet sheetId="32" name="Women's 35+ Round of 16 M1" state="visible" r:id="rId35"/>
-    <sheet sheetId="33" name="Women's 35+ Round of 16 M2" state="visible" r:id="rId36"/>
-    <sheet sheetId="34" name="Women's 35+ Round of 16 M3" state="visible" r:id="rId37"/>
-    <sheet sheetId="35" name="Women's 35+ Round of 16 M4" state="visible" r:id="rId38"/>
-    <sheet sheetId="36" name="Women's 35+ Round of 16 M5" state="visible" r:id="rId39"/>
-    <sheet sheetId="37" name="Women's 35+ Round of 16 M6" state="visible" r:id="rId40"/>
-    <sheet sheetId="38" name="Women's 35+ Round of 16 M7" state="visible" r:id="rId41"/>
-    <sheet sheetId="39" name="Women's 35+ Round of 16 M8" state="visible" r:id="rId42"/>
-    <sheet sheetId="40" name="Women's 35+ Quarterfinal M1" state="visible" r:id="rId43"/>
-    <sheet sheetId="41" name="Women's 35+ Quarterfinal M2" state="visible" r:id="rId44"/>
-    <sheet sheetId="42" name="Women's 35+ Quarterfinal M3" state="visible" r:id="rId45"/>
-    <sheet sheetId="43" name="Women's 35+ Quarterfinal M4" state="visible" r:id="rId46"/>
-    <sheet sheetId="44" name="Women's 35+ Semifinal M1" state="visible" r:id="rId47"/>
-    <sheet sheetId="45" name="Women's 35+ Semifinal M2" state="visible" r:id="rId48"/>
-    <sheet sheetId="46" name="Women's 35+ Final M1" state="visible" r:id="rId49"/>
-    <sheet sheetId="47" name="Blank Knockout 1" state="visible" r:id="rId50"/>
-    <sheet sheetId="48" name="Blank Knockout 2" state="visible" r:id="rId51"/>
-    <sheet sheetId="49" name="Blank Knockout 3" state="visible" r:id="rId52"/>
-    <sheet sheetId="50" name="Blank Knockout 4" state="visible" r:id="rId53"/>
-    <sheet sheetId="51" name="Blank Knockout 5" state="visible" r:id="rId54"/>
-    <sheet sheetId="52" name="Blank Knockout 6" state="visible" r:id="rId55"/>
-    <sheet sheetId="53" name="Blank Knockout 7" state="visible" r:id="rId56"/>
-    <sheet sheetId="54" name="Blank Knockout 8" state="visible" r:id="rId57"/>
-    <sheet sheetId="55" name="Blank Knockout 9" state="visible" r:id="rId58"/>
-    <sheet sheetId="56" name="Blank Knockout 10" state="visible" r:id="rId59"/>
+    <sheet sheetId="32" name="Blank Knockout 1" state="visible" r:id="rId35"/>
+    <sheet sheetId="33" name="Blank Knockout 2" state="visible" r:id="rId36"/>
+    <sheet sheetId="34" name="Blank Knockout 3" state="visible" r:id="rId37"/>
+    <sheet sheetId="35" name="Blank Knockout 4" state="visible" r:id="rId38"/>
+    <sheet sheetId="36" name="Blank Knockout 5" state="visible" r:id="rId39"/>
+    <sheet sheetId="37" name="Blank Knockout 6" state="visible" r:id="rId40"/>
+    <sheet sheetId="38" name="Blank Knockout 7" state="visible" r:id="rId41"/>
+    <sheet sheetId="39" name="Blank Knockout 8" state="visible" r:id="rId42"/>
+    <sheet sheetId="40" name="Blank Knockout 9" state="visible" r:id="rId43"/>
+    <sheet sheetId="41" name="Blank Knockout 10" state="visible" r:id="rId44"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1396" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1006" uniqueCount="51">
   <si>
     <t>ROUND:</t>
   </si>
@@ -89,7 +74,7 @@
     <t>1</t>
   </si>
   <si>
-    <t>RAVENS 2026 TERRENCE ORR CHAMPIONSHIP</t>
+    <t>SAVETTS 2026</t>
   </si>
   <si>
     <t>EVENT:</t>
@@ -219,9 +204,6 @@
   </si>
   <si>
     <t>Final</t>
-  </si>
-  <si>
-    <t>Women's 35+</t>
   </si>
 </sst>
 </file>
@@ -381,30 +363,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="medium">
         <color indexed="64"/>
       </left>
@@ -478,30 +436,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="medium">
         <color indexed="64"/>
       </left>
@@ -561,11 +495,59 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -611,39 +593,45 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1075,94 +1063,96 @@
       <c r="B5" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="C5" s="17"/>
-      <c r="D5" s="18"/>
-      <c r="E5" s="19"/>
-      <c r="F5" s="20"/>
-      <c r="G5" s="20"/>
-      <c r="H5" s="20"/>
-      <c r="I5" s="21"/>
-      <c r="J5" s="22"/>
+      <c r="C5" s="16"/>
+      <c r="D5" s="16"/>
+      <c r="E5" s="17"/>
+      <c r="F5" s="18"/>
+      <c r="G5" s="18"/>
+      <c r="H5" s="18"/>
+      <c r="I5" s="19"/>
+      <c r="J5" s="20"/>
     </row>
     <row r="6" ht="150" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="23" t="s">
+      <c r="A6" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="24" t="s">
+      <c r="B6" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="C6" s="25"/>
-      <c r="D6" s="26"/>
-      <c r="E6" s="27"/>
-      <c r="F6" s="28"/>
-      <c r="G6" s="28"/>
-      <c r="H6" s="28"/>
-      <c r="I6" s="29"/>
-      <c r="J6" s="30"/>
+      <c r="C6" s="22"/>
+      <c r="D6" s="22"/>
+      <c r="E6" s="23"/>
+      <c r="F6" s="24"/>
+      <c r="G6" s="24"/>
+      <c r="H6" s="24"/>
+      <c r="I6" s="25"/>
+      <c r="J6" s="26"/>
     </row>
     <row r="7" ht="78.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="8" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="31" t="s">
+      <c r="A8" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="31"/>
-      <c r="C8" s="31"/>
-      <c r="D8" s="31"/>
-      <c r="E8" s="31"/>
-      <c r="F8" s="32" t="s">
+      <c r="B8" s="27"/>
+      <c r="C8" s="27"/>
+      <c r="D8" s="27"/>
+      <c r="E8" s="27"/>
+      <c r="F8" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="G8" s="32"/>
-      <c r="H8" s="32"/>
-      <c r="I8" s="32"/>
-      <c r="J8" s="32"/>
+      <c r="G8" s="28"/>
+      <c r="H8" s="28"/>
+      <c r="I8" s="28"/>
+      <c r="J8" s="28"/>
     </row>
     <row r="9" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="31"/>
-      <c r="B9" s="31"/>
-      <c r="C9" s="31"/>
-      <c r="D9" s="31"/>
-      <c r="E9" s="31"/>
-      <c r="F9" s="32"/>
-      <c r="G9" s="32"/>
-      <c r="H9" s="32"/>
-      <c r="I9" s="32"/>
-      <c r="J9" s="32"/>
+      <c r="A9" s="27"/>
+      <c r="B9" s="27"/>
+      <c r="C9" s="27"/>
+      <c r="D9" s="27"/>
+      <c r="E9" s="27"/>
+      <c r="F9" s="28"/>
+      <c r="G9" s="28"/>
+      <c r="H9" s="28"/>
+      <c r="I9" s="28"/>
+      <c r="J9" s="28"/>
     </row>
     <row r="10" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="31" t="s">
+      <c r="A10" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="B10" s="31"/>
-      <c r="C10" s="31"/>
-      <c r="D10" s="31"/>
-      <c r="E10" s="31"/>
-      <c r="F10" s="32" t="s">
+      <c r="B10" s="27"/>
+      <c r="C10" s="27"/>
+      <c r="D10" s="27"/>
+      <c r="E10" s="27"/>
+      <c r="F10" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="G10" s="32"/>
-      <c r="H10" s="32"/>
-      <c r="I10" s="32"/>
-      <c r="J10" s="32"/>
+      <c r="G10" s="28"/>
+      <c r="H10" s="28"/>
+      <c r="I10" s="28"/>
+      <c r="J10" s="28"/>
     </row>
     <row r="11" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="31"/>
-      <c r="B11" s="31"/>
-      <c r="C11" s="31"/>
-      <c r="D11" s="31"/>
-      <c r="E11" s="31"/>
-      <c r="F11" s="32"/>
-      <c r="G11" s="32"/>
-      <c r="H11" s="32"/>
-      <c r="I11" s="32"/>
-      <c r="J11" s="32"/>
+      <c r="A11" s="27"/>
+      <c r="B11" s="27"/>
+      <c r="C11" s="27"/>
+      <c r="D11" s="27"/>
+      <c r="E11" s="27"/>
+      <c r="F11" s="28"/>
+      <c r="G11" s="28"/>
+      <c r="H11" s="28"/>
+      <c r="I11" s="28"/>
+      <c r="J11" s="28"/>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="10">
     <mergeCell ref="B1:C1"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="G2:H2"/>
     <mergeCell ref="I2:J2"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B6:D6"/>
     <mergeCell ref="A8:E9"/>
     <mergeCell ref="F8:J9"/>
     <mergeCell ref="A10:E11"/>
@@ -1267,94 +1257,96 @@
       <c r="B5" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="C5" s="17"/>
-      <c r="D5" s="18"/>
-      <c r="E5" s="19"/>
-      <c r="F5" s="20"/>
-      <c r="G5" s="20"/>
-      <c r="H5" s="20"/>
-      <c r="I5" s="21"/>
-      <c r="J5" s="22"/>
+      <c r="C5" s="16"/>
+      <c r="D5" s="16"/>
+      <c r="E5" s="17"/>
+      <c r="F5" s="18"/>
+      <c r="G5" s="18"/>
+      <c r="H5" s="18"/>
+      <c r="I5" s="19"/>
+      <c r="J5" s="20"/>
     </row>
     <row r="6" ht="150" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="23" t="s">
+      <c r="A6" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="24" t="s">
+      <c r="B6" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="C6" s="25"/>
-      <c r="D6" s="26"/>
-      <c r="E6" s="27"/>
-      <c r="F6" s="28"/>
-      <c r="G6" s="28"/>
-      <c r="H6" s="28"/>
-      <c r="I6" s="29"/>
-      <c r="J6" s="30"/>
+      <c r="C6" s="22"/>
+      <c r="D6" s="22"/>
+      <c r="E6" s="23"/>
+      <c r="F6" s="24"/>
+      <c r="G6" s="24"/>
+      <c r="H6" s="24"/>
+      <c r="I6" s="25"/>
+      <c r="J6" s="26"/>
     </row>
     <row r="7" ht="78.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="8" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="31" t="s">
+      <c r="A8" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="31"/>
-      <c r="C8" s="31"/>
-      <c r="D8" s="31"/>
-      <c r="E8" s="31"/>
-      <c r="F8" s="32" t="s">
+      <c r="B8" s="27"/>
+      <c r="C8" s="27"/>
+      <c r="D8" s="27"/>
+      <c r="E8" s="27"/>
+      <c r="F8" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="G8" s="32"/>
-      <c r="H8" s="32"/>
-      <c r="I8" s="32"/>
-      <c r="J8" s="32"/>
+      <c r="G8" s="28"/>
+      <c r="H8" s="28"/>
+      <c r="I8" s="28"/>
+      <c r="J8" s="28"/>
     </row>
     <row r="9" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="31"/>
-      <c r="B9" s="31"/>
-      <c r="C9" s="31"/>
-      <c r="D9" s="31"/>
-      <c r="E9" s="31"/>
-      <c r="F9" s="32"/>
-      <c r="G9" s="32"/>
-      <c r="H9" s="32"/>
-      <c r="I9" s="32"/>
-      <c r="J9" s="32"/>
+      <c r="A9" s="27"/>
+      <c r="B9" s="27"/>
+      <c r="C9" s="27"/>
+      <c r="D9" s="27"/>
+      <c r="E9" s="27"/>
+      <c r="F9" s="28"/>
+      <c r="G9" s="28"/>
+      <c r="H9" s="28"/>
+      <c r="I9" s="28"/>
+      <c r="J9" s="28"/>
     </row>
     <row r="10" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="31" t="s">
+      <c r="A10" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="B10" s="31"/>
-      <c r="C10" s="31"/>
-      <c r="D10" s="31"/>
-      <c r="E10" s="31"/>
-      <c r="F10" s="32" t="s">
+      <c r="B10" s="27"/>
+      <c r="C10" s="27"/>
+      <c r="D10" s="27"/>
+      <c r="E10" s="27"/>
+      <c r="F10" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="G10" s="32"/>
-      <c r="H10" s="32"/>
-      <c r="I10" s="32"/>
-      <c r="J10" s="32"/>
+      <c r="G10" s="28"/>
+      <c r="H10" s="28"/>
+      <c r="I10" s="28"/>
+      <c r="J10" s="28"/>
     </row>
     <row r="11" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="31"/>
-      <c r="B11" s="31"/>
-      <c r="C11" s="31"/>
-      <c r="D11" s="31"/>
-      <c r="E11" s="31"/>
-      <c r="F11" s="32"/>
-      <c r="G11" s="32"/>
-      <c r="H11" s="32"/>
-      <c r="I11" s="32"/>
-      <c r="J11" s="32"/>
+      <c r="A11" s="27"/>
+      <c r="B11" s="27"/>
+      <c r="C11" s="27"/>
+      <c r="D11" s="27"/>
+      <c r="E11" s="27"/>
+      <c r="F11" s="28"/>
+      <c r="G11" s="28"/>
+      <c r="H11" s="28"/>
+      <c r="I11" s="28"/>
+      <c r="J11" s="28"/>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="10">
     <mergeCell ref="B1:C1"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="G2:H2"/>
     <mergeCell ref="I2:J2"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B6:D6"/>
     <mergeCell ref="A8:E9"/>
     <mergeCell ref="F8:J9"/>
     <mergeCell ref="A10:E11"/>
@@ -1459,94 +1451,96 @@
       <c r="B5" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="C5" s="17"/>
-      <c r="D5" s="18"/>
-      <c r="E5" s="19"/>
-      <c r="F5" s="20"/>
-      <c r="G5" s="20"/>
-      <c r="H5" s="20"/>
-      <c r="I5" s="21"/>
-      <c r="J5" s="22"/>
+      <c r="C5" s="16"/>
+      <c r="D5" s="16"/>
+      <c r="E5" s="17"/>
+      <c r="F5" s="18"/>
+      <c r="G5" s="18"/>
+      <c r="H5" s="18"/>
+      <c r="I5" s="19"/>
+      <c r="J5" s="20"/>
     </row>
     <row r="6" ht="150" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="23" t="s">
+      <c r="A6" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="24" t="s">
+      <c r="B6" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="C6" s="25"/>
-      <c r="D6" s="26"/>
-      <c r="E6" s="27"/>
-      <c r="F6" s="28"/>
-      <c r="G6" s="28"/>
-      <c r="H6" s="28"/>
-      <c r="I6" s="29"/>
-      <c r="J6" s="30"/>
+      <c r="C6" s="22"/>
+      <c r="D6" s="22"/>
+      <c r="E6" s="23"/>
+      <c r="F6" s="24"/>
+      <c r="G6" s="24"/>
+      <c r="H6" s="24"/>
+      <c r="I6" s="25"/>
+      <c r="J6" s="26"/>
     </row>
     <row r="7" ht="78.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="8" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="31" t="s">
+      <c r="A8" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="31"/>
-      <c r="C8" s="31"/>
-      <c r="D8" s="31"/>
-      <c r="E8" s="31"/>
-      <c r="F8" s="32" t="s">
+      <c r="B8" s="27"/>
+      <c r="C8" s="27"/>
+      <c r="D8" s="27"/>
+      <c r="E8" s="27"/>
+      <c r="F8" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="G8" s="32"/>
-      <c r="H8" s="32"/>
-      <c r="I8" s="32"/>
-      <c r="J8" s="32"/>
+      <c r="G8" s="28"/>
+      <c r="H8" s="28"/>
+      <c r="I8" s="28"/>
+      <c r="J8" s="28"/>
     </row>
     <row r="9" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="31"/>
-      <c r="B9" s="31"/>
-      <c r="C9" s="31"/>
-      <c r="D9" s="31"/>
-      <c r="E9" s="31"/>
-      <c r="F9" s="32"/>
-      <c r="G9" s="32"/>
-      <c r="H9" s="32"/>
-      <c r="I9" s="32"/>
-      <c r="J9" s="32"/>
+      <c r="A9" s="27"/>
+      <c r="B9" s="27"/>
+      <c r="C9" s="27"/>
+      <c r="D9" s="27"/>
+      <c r="E9" s="27"/>
+      <c r="F9" s="28"/>
+      <c r="G9" s="28"/>
+      <c r="H9" s="28"/>
+      <c r="I9" s="28"/>
+      <c r="J9" s="28"/>
     </row>
     <row r="10" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="31" t="s">
+      <c r="A10" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="B10" s="31"/>
-      <c r="C10" s="31"/>
-      <c r="D10" s="31"/>
-      <c r="E10" s="31"/>
-      <c r="F10" s="32" t="s">
+      <c r="B10" s="27"/>
+      <c r="C10" s="27"/>
+      <c r="D10" s="27"/>
+      <c r="E10" s="27"/>
+      <c r="F10" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="G10" s="32"/>
-      <c r="H10" s="32"/>
-      <c r="I10" s="32"/>
-      <c r="J10" s="32"/>
+      <c r="G10" s="28"/>
+      <c r="H10" s="28"/>
+      <c r="I10" s="28"/>
+      <c r="J10" s="28"/>
     </row>
     <row r="11" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="31"/>
-      <c r="B11" s="31"/>
-      <c r="C11" s="31"/>
-      <c r="D11" s="31"/>
-      <c r="E11" s="31"/>
-      <c r="F11" s="32"/>
-      <c r="G11" s="32"/>
-      <c r="H11" s="32"/>
-      <c r="I11" s="32"/>
-      <c r="J11" s="32"/>
+      <c r="A11" s="27"/>
+      <c r="B11" s="27"/>
+      <c r="C11" s="27"/>
+      <c r="D11" s="27"/>
+      <c r="E11" s="27"/>
+      <c r="F11" s="28"/>
+      <c r="G11" s="28"/>
+      <c r="H11" s="28"/>
+      <c r="I11" s="28"/>
+      <c r="J11" s="28"/>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="10">
     <mergeCell ref="B1:C1"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="G2:H2"/>
     <mergeCell ref="I2:J2"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B6:D6"/>
     <mergeCell ref="A8:E9"/>
     <mergeCell ref="F8:J9"/>
     <mergeCell ref="A10:E11"/>
@@ -1651,94 +1645,96 @@
       <c r="B5" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="C5" s="17"/>
-      <c r="D5" s="18"/>
-      <c r="E5" s="19"/>
-      <c r="F5" s="20"/>
-      <c r="G5" s="20"/>
-      <c r="H5" s="20"/>
-      <c r="I5" s="21"/>
-      <c r="J5" s="22"/>
+      <c r="C5" s="16"/>
+      <c r="D5" s="16"/>
+      <c r="E5" s="17"/>
+      <c r="F5" s="18"/>
+      <c r="G5" s="18"/>
+      <c r="H5" s="18"/>
+      <c r="I5" s="19"/>
+      <c r="J5" s="20"/>
     </row>
     <row r="6" ht="150" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="23" t="s">
+      <c r="A6" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="24" t="s">
+      <c r="B6" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="C6" s="25"/>
-      <c r="D6" s="26"/>
-      <c r="E6" s="27"/>
-      <c r="F6" s="28"/>
-      <c r="G6" s="28"/>
-      <c r="H6" s="28"/>
-      <c r="I6" s="29"/>
-      <c r="J6" s="30"/>
+      <c r="C6" s="22"/>
+      <c r="D6" s="22"/>
+      <c r="E6" s="23"/>
+      <c r="F6" s="24"/>
+      <c r="G6" s="24"/>
+      <c r="H6" s="24"/>
+      <c r="I6" s="25"/>
+      <c r="J6" s="26"/>
     </row>
     <row r="7" ht="78.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="8" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="31" t="s">
+      <c r="A8" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="31"/>
-      <c r="C8" s="31"/>
-      <c r="D8" s="31"/>
-      <c r="E8" s="31"/>
-      <c r="F8" s="32" t="s">
+      <c r="B8" s="27"/>
+      <c r="C8" s="27"/>
+      <c r="D8" s="27"/>
+      <c r="E8" s="27"/>
+      <c r="F8" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="G8" s="32"/>
-      <c r="H8" s="32"/>
-      <c r="I8" s="32"/>
-      <c r="J8" s="32"/>
+      <c r="G8" s="28"/>
+      <c r="H8" s="28"/>
+      <c r="I8" s="28"/>
+      <c r="J8" s="28"/>
     </row>
     <row r="9" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="31"/>
-      <c r="B9" s="31"/>
-      <c r="C9" s="31"/>
-      <c r="D9" s="31"/>
-      <c r="E9" s="31"/>
-      <c r="F9" s="32"/>
-      <c r="G9" s="32"/>
-      <c r="H9" s="32"/>
-      <c r="I9" s="32"/>
-      <c r="J9" s="32"/>
+      <c r="A9" s="27"/>
+      <c r="B9" s="27"/>
+      <c r="C9" s="27"/>
+      <c r="D9" s="27"/>
+      <c r="E9" s="27"/>
+      <c r="F9" s="28"/>
+      <c r="G9" s="28"/>
+      <c r="H9" s="28"/>
+      <c r="I9" s="28"/>
+      <c r="J9" s="28"/>
     </row>
     <row r="10" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="31" t="s">
+      <c r="A10" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="B10" s="31"/>
-      <c r="C10" s="31"/>
-      <c r="D10" s="31"/>
-      <c r="E10" s="31"/>
-      <c r="F10" s="32" t="s">
+      <c r="B10" s="27"/>
+      <c r="C10" s="27"/>
+      <c r="D10" s="27"/>
+      <c r="E10" s="27"/>
+      <c r="F10" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="G10" s="32"/>
-      <c r="H10" s="32"/>
-      <c r="I10" s="32"/>
-      <c r="J10" s="32"/>
+      <c r="G10" s="28"/>
+      <c r="H10" s="28"/>
+      <c r="I10" s="28"/>
+      <c r="J10" s="28"/>
     </row>
     <row r="11" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="31"/>
-      <c r="B11" s="31"/>
-      <c r="C11" s="31"/>
-      <c r="D11" s="31"/>
-      <c r="E11" s="31"/>
-      <c r="F11" s="32"/>
-      <c r="G11" s="32"/>
-      <c r="H11" s="32"/>
-      <c r="I11" s="32"/>
-      <c r="J11" s="32"/>
+      <c r="A11" s="27"/>
+      <c r="B11" s="27"/>
+      <c r="C11" s="27"/>
+      <c r="D11" s="27"/>
+      <c r="E11" s="27"/>
+      <c r="F11" s="28"/>
+      <c r="G11" s="28"/>
+      <c r="H11" s="28"/>
+      <c r="I11" s="28"/>
+      <c r="J11" s="28"/>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="10">
     <mergeCell ref="B1:C1"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="G2:H2"/>
     <mergeCell ref="I2:J2"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B6:D6"/>
     <mergeCell ref="A8:E9"/>
     <mergeCell ref="F8:J9"/>
     <mergeCell ref="A10:E11"/>
@@ -1843,94 +1839,96 @@
       <c r="B5" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="C5" s="17"/>
-      <c r="D5" s="18"/>
-      <c r="E5" s="19"/>
-      <c r="F5" s="20"/>
-      <c r="G5" s="20"/>
-      <c r="H5" s="20"/>
-      <c r="I5" s="21"/>
-      <c r="J5" s="22"/>
+      <c r="C5" s="16"/>
+      <c r="D5" s="16"/>
+      <c r="E5" s="17"/>
+      <c r="F5" s="18"/>
+      <c r="G5" s="18"/>
+      <c r="H5" s="18"/>
+      <c r="I5" s="19"/>
+      <c r="J5" s="20"/>
     </row>
     <row r="6" ht="150" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="23" t="s">
+      <c r="A6" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="24" t="s">
+      <c r="B6" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="C6" s="25"/>
-      <c r="D6" s="26"/>
-      <c r="E6" s="27"/>
-      <c r="F6" s="28"/>
-      <c r="G6" s="28"/>
-      <c r="H6" s="28"/>
-      <c r="I6" s="29"/>
-      <c r="J6" s="30"/>
+      <c r="C6" s="22"/>
+      <c r="D6" s="22"/>
+      <c r="E6" s="23"/>
+      <c r="F6" s="24"/>
+      <c r="G6" s="24"/>
+      <c r="H6" s="24"/>
+      <c r="I6" s="25"/>
+      <c r="J6" s="26"/>
     </row>
     <row r="7" ht="78.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="8" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="31" t="s">
+      <c r="A8" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="31"/>
-      <c r="C8" s="31"/>
-      <c r="D8" s="31"/>
-      <c r="E8" s="31"/>
-      <c r="F8" s="32" t="s">
+      <c r="B8" s="27"/>
+      <c r="C8" s="27"/>
+      <c r="D8" s="27"/>
+      <c r="E8" s="27"/>
+      <c r="F8" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="G8" s="32"/>
-      <c r="H8" s="32"/>
-      <c r="I8" s="32"/>
-      <c r="J8" s="32"/>
+      <c r="G8" s="28"/>
+      <c r="H8" s="28"/>
+      <c r="I8" s="28"/>
+      <c r="J8" s="28"/>
     </row>
     <row r="9" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="31"/>
-      <c r="B9" s="31"/>
-      <c r="C9" s="31"/>
-      <c r="D9" s="31"/>
-      <c r="E9" s="31"/>
-      <c r="F9" s="32"/>
-      <c r="G9" s="32"/>
-      <c r="H9" s="32"/>
-      <c r="I9" s="32"/>
-      <c r="J9" s="32"/>
+      <c r="A9" s="27"/>
+      <c r="B9" s="27"/>
+      <c r="C9" s="27"/>
+      <c r="D9" s="27"/>
+      <c r="E9" s="27"/>
+      <c r="F9" s="28"/>
+      <c r="G9" s="28"/>
+      <c r="H9" s="28"/>
+      <c r="I9" s="28"/>
+      <c r="J9" s="28"/>
     </row>
     <row r="10" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="31" t="s">
+      <c r="A10" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="B10" s="31"/>
-      <c r="C10" s="31"/>
-      <c r="D10" s="31"/>
-      <c r="E10" s="31"/>
-      <c r="F10" s="32" t="s">
+      <c r="B10" s="27"/>
+      <c r="C10" s="27"/>
+      <c r="D10" s="27"/>
+      <c r="E10" s="27"/>
+      <c r="F10" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="G10" s="32"/>
-      <c r="H10" s="32"/>
-      <c r="I10" s="32"/>
-      <c r="J10" s="32"/>
+      <c r="G10" s="28"/>
+      <c r="H10" s="28"/>
+      <c r="I10" s="28"/>
+      <c r="J10" s="28"/>
     </row>
     <row r="11" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="31"/>
-      <c r="B11" s="31"/>
-      <c r="C11" s="31"/>
-      <c r="D11" s="31"/>
-      <c r="E11" s="31"/>
-      <c r="F11" s="32"/>
-      <c r="G11" s="32"/>
-      <c r="H11" s="32"/>
-      <c r="I11" s="32"/>
-      <c r="J11" s="32"/>
+      <c r="A11" s="27"/>
+      <c r="B11" s="27"/>
+      <c r="C11" s="27"/>
+      <c r="D11" s="27"/>
+      <c r="E11" s="27"/>
+      <c r="F11" s="28"/>
+      <c r="G11" s="28"/>
+      <c r="H11" s="28"/>
+      <c r="I11" s="28"/>
+      <c r="J11" s="28"/>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="10">
     <mergeCell ref="B1:C1"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="G2:H2"/>
     <mergeCell ref="I2:J2"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B6:D6"/>
     <mergeCell ref="A8:E9"/>
     <mergeCell ref="F8:J9"/>
     <mergeCell ref="A10:E11"/>
@@ -2035,94 +2033,96 @@
       <c r="B5" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="C5" s="17"/>
-      <c r="D5" s="18"/>
-      <c r="E5" s="19"/>
-      <c r="F5" s="20"/>
-      <c r="G5" s="20"/>
-      <c r="H5" s="20"/>
-      <c r="I5" s="21"/>
-      <c r="J5" s="22"/>
+      <c r="C5" s="16"/>
+      <c r="D5" s="16"/>
+      <c r="E5" s="17"/>
+      <c r="F5" s="18"/>
+      <c r="G5" s="18"/>
+      <c r="H5" s="18"/>
+      <c r="I5" s="19"/>
+      <c r="J5" s="20"/>
     </row>
     <row r="6" ht="150" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="23" t="s">
+      <c r="A6" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="24" t="s">
+      <c r="B6" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="C6" s="25"/>
-      <c r="D6" s="26"/>
-      <c r="E6" s="27"/>
-      <c r="F6" s="28"/>
-      <c r="G6" s="28"/>
-      <c r="H6" s="28"/>
-      <c r="I6" s="29"/>
-      <c r="J6" s="30"/>
+      <c r="C6" s="22"/>
+      <c r="D6" s="22"/>
+      <c r="E6" s="23"/>
+      <c r="F6" s="24"/>
+      <c r="G6" s="24"/>
+      <c r="H6" s="24"/>
+      <c r="I6" s="25"/>
+      <c r="J6" s="26"/>
     </row>
     <row r="7" ht="78.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="8" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="31" t="s">
+      <c r="A8" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="31"/>
-      <c r="C8" s="31"/>
-      <c r="D8" s="31"/>
-      <c r="E8" s="31"/>
-      <c r="F8" s="32" t="s">
+      <c r="B8" s="27"/>
+      <c r="C8" s="27"/>
+      <c r="D8" s="27"/>
+      <c r="E8" s="27"/>
+      <c r="F8" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="G8" s="32"/>
-      <c r="H8" s="32"/>
-      <c r="I8" s="32"/>
-      <c r="J8" s="32"/>
+      <c r="G8" s="28"/>
+      <c r="H8" s="28"/>
+      <c r="I8" s="28"/>
+      <c r="J8" s="28"/>
     </row>
     <row r="9" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="31"/>
-      <c r="B9" s="31"/>
-      <c r="C9" s="31"/>
-      <c r="D9" s="31"/>
-      <c r="E9" s="31"/>
-      <c r="F9" s="32"/>
-      <c r="G9" s="32"/>
-      <c r="H9" s="32"/>
-      <c r="I9" s="32"/>
-      <c r="J9" s="32"/>
+      <c r="A9" s="27"/>
+      <c r="B9" s="27"/>
+      <c r="C9" s="27"/>
+      <c r="D9" s="27"/>
+      <c r="E9" s="27"/>
+      <c r="F9" s="28"/>
+      <c r="G9" s="28"/>
+      <c r="H9" s="28"/>
+      <c r="I9" s="28"/>
+      <c r="J9" s="28"/>
     </row>
     <row r="10" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="31" t="s">
+      <c r="A10" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="B10" s="31"/>
-      <c r="C10" s="31"/>
-      <c r="D10" s="31"/>
-      <c r="E10" s="31"/>
-      <c r="F10" s="32" t="s">
+      <c r="B10" s="27"/>
+      <c r="C10" s="27"/>
+      <c r="D10" s="27"/>
+      <c r="E10" s="27"/>
+      <c r="F10" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="G10" s="32"/>
-      <c r="H10" s="32"/>
-      <c r="I10" s="32"/>
-      <c r="J10" s="32"/>
+      <c r="G10" s="28"/>
+      <c r="H10" s="28"/>
+      <c r="I10" s="28"/>
+      <c r="J10" s="28"/>
     </row>
     <row r="11" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="31"/>
-      <c r="B11" s="31"/>
-      <c r="C11" s="31"/>
-      <c r="D11" s="31"/>
-      <c r="E11" s="31"/>
-      <c r="F11" s="32"/>
-      <c r="G11" s="32"/>
-      <c r="H11" s="32"/>
-      <c r="I11" s="32"/>
-      <c r="J11" s="32"/>
+      <c r="A11" s="27"/>
+      <c r="B11" s="27"/>
+      <c r="C11" s="27"/>
+      <c r="D11" s="27"/>
+      <c r="E11" s="27"/>
+      <c r="F11" s="28"/>
+      <c r="G11" s="28"/>
+      <c r="H11" s="28"/>
+      <c r="I11" s="28"/>
+      <c r="J11" s="28"/>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="10">
     <mergeCell ref="B1:C1"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="G2:H2"/>
     <mergeCell ref="I2:J2"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B6:D6"/>
     <mergeCell ref="A8:E9"/>
     <mergeCell ref="F8:J9"/>
     <mergeCell ref="A10:E11"/>
@@ -2227,94 +2227,96 @@
       <c r="B5" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="C5" s="17"/>
-      <c r="D5" s="18"/>
-      <c r="E5" s="19"/>
-      <c r="F5" s="20"/>
-      <c r="G5" s="20"/>
-      <c r="H5" s="20"/>
-      <c r="I5" s="21"/>
-      <c r="J5" s="22"/>
+      <c r="C5" s="16"/>
+      <c r="D5" s="16"/>
+      <c r="E5" s="17"/>
+      <c r="F5" s="18"/>
+      <c r="G5" s="18"/>
+      <c r="H5" s="18"/>
+      <c r="I5" s="19"/>
+      <c r="J5" s="20"/>
     </row>
     <row r="6" ht="150" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="23" t="s">
+      <c r="A6" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="24" t="s">
+      <c r="B6" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="C6" s="25"/>
-      <c r="D6" s="26"/>
-      <c r="E6" s="27"/>
-      <c r="F6" s="28"/>
-      <c r="G6" s="28"/>
-      <c r="H6" s="28"/>
-      <c r="I6" s="29"/>
-      <c r="J6" s="30"/>
+      <c r="C6" s="22"/>
+      <c r="D6" s="22"/>
+      <c r="E6" s="23"/>
+      <c r="F6" s="24"/>
+      <c r="G6" s="24"/>
+      <c r="H6" s="24"/>
+      <c r="I6" s="25"/>
+      <c r="J6" s="26"/>
     </row>
     <row r="7" ht="78.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="8" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="31" t="s">
+      <c r="A8" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="31"/>
-      <c r="C8" s="31"/>
-      <c r="D8" s="31"/>
-      <c r="E8" s="31"/>
-      <c r="F8" s="32" t="s">
+      <c r="B8" s="27"/>
+      <c r="C8" s="27"/>
+      <c r="D8" s="27"/>
+      <c r="E8" s="27"/>
+      <c r="F8" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="G8" s="32"/>
-      <c r="H8" s="32"/>
-      <c r="I8" s="32"/>
-      <c r="J8" s="32"/>
+      <c r="G8" s="28"/>
+      <c r="H8" s="28"/>
+      <c r="I8" s="28"/>
+      <c r="J8" s="28"/>
     </row>
     <row r="9" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="31"/>
-      <c r="B9" s="31"/>
-      <c r="C9" s="31"/>
-      <c r="D9" s="31"/>
-      <c r="E9" s="31"/>
-      <c r="F9" s="32"/>
-      <c r="G9" s="32"/>
-      <c r="H9" s="32"/>
-      <c r="I9" s="32"/>
-      <c r="J9" s="32"/>
+      <c r="A9" s="27"/>
+      <c r="B9" s="27"/>
+      <c r="C9" s="27"/>
+      <c r="D9" s="27"/>
+      <c r="E9" s="27"/>
+      <c r="F9" s="28"/>
+      <c r="G9" s="28"/>
+      <c r="H9" s="28"/>
+      <c r="I9" s="28"/>
+      <c r="J9" s="28"/>
     </row>
     <row r="10" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="31" t="s">
+      <c r="A10" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="B10" s="31"/>
-      <c r="C10" s="31"/>
-      <c r="D10" s="31"/>
-      <c r="E10" s="31"/>
-      <c r="F10" s="32" t="s">
+      <c r="B10" s="27"/>
+      <c r="C10" s="27"/>
+      <c r="D10" s="27"/>
+      <c r="E10" s="27"/>
+      <c r="F10" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="G10" s="32"/>
-      <c r="H10" s="32"/>
-      <c r="I10" s="32"/>
-      <c r="J10" s="32"/>
+      <c r="G10" s="28"/>
+      <c r="H10" s="28"/>
+      <c r="I10" s="28"/>
+      <c r="J10" s="28"/>
     </row>
     <row r="11" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="31"/>
-      <c r="B11" s="31"/>
-      <c r="C11" s="31"/>
-      <c r="D11" s="31"/>
-      <c r="E11" s="31"/>
-      <c r="F11" s="32"/>
-      <c r="G11" s="32"/>
-      <c r="H11" s="32"/>
-      <c r="I11" s="32"/>
-      <c r="J11" s="32"/>
+      <c r="A11" s="27"/>
+      <c r="B11" s="27"/>
+      <c r="C11" s="27"/>
+      <c r="D11" s="27"/>
+      <c r="E11" s="27"/>
+      <c r="F11" s="28"/>
+      <c r="G11" s="28"/>
+      <c r="H11" s="28"/>
+      <c r="I11" s="28"/>
+      <c r="J11" s="28"/>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="10">
     <mergeCell ref="B1:C1"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="G2:H2"/>
     <mergeCell ref="I2:J2"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B6:D6"/>
     <mergeCell ref="A8:E9"/>
     <mergeCell ref="F8:J9"/>
     <mergeCell ref="A10:E11"/>
@@ -2419,94 +2421,96 @@
       <c r="B5" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="C5" s="17"/>
-      <c r="D5" s="18"/>
-      <c r="E5" s="19"/>
-      <c r="F5" s="20"/>
-      <c r="G5" s="20"/>
-      <c r="H5" s="20"/>
-      <c r="I5" s="21"/>
-      <c r="J5" s="22"/>
+      <c r="C5" s="16"/>
+      <c r="D5" s="16"/>
+      <c r="E5" s="17"/>
+      <c r="F5" s="18"/>
+      <c r="G5" s="18"/>
+      <c r="H5" s="18"/>
+      <c r="I5" s="19"/>
+      <c r="J5" s="20"/>
     </row>
     <row r="6" ht="150" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="23" t="s">
+      <c r="A6" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="24" t="s">
+      <c r="B6" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="C6" s="25"/>
-      <c r="D6" s="26"/>
-      <c r="E6" s="27"/>
-      <c r="F6" s="28"/>
-      <c r="G6" s="28"/>
-      <c r="H6" s="28"/>
-      <c r="I6" s="29"/>
-      <c r="J6" s="30"/>
+      <c r="C6" s="22"/>
+      <c r="D6" s="22"/>
+      <c r="E6" s="23"/>
+      <c r="F6" s="24"/>
+      <c r="G6" s="24"/>
+      <c r="H6" s="24"/>
+      <c r="I6" s="25"/>
+      <c r="J6" s="26"/>
     </row>
     <row r="7" ht="78.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="8" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="31" t="s">
+      <c r="A8" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="31"/>
-      <c r="C8" s="31"/>
-      <c r="D8" s="31"/>
-      <c r="E8" s="31"/>
-      <c r="F8" s="32" t="s">
+      <c r="B8" s="27"/>
+      <c r="C8" s="27"/>
+      <c r="D8" s="27"/>
+      <c r="E8" s="27"/>
+      <c r="F8" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="G8" s="32"/>
-      <c r="H8" s="32"/>
-      <c r="I8" s="32"/>
-      <c r="J8" s="32"/>
+      <c r="G8" s="28"/>
+      <c r="H8" s="28"/>
+      <c r="I8" s="28"/>
+      <c r="J8" s="28"/>
     </row>
     <row r="9" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="31"/>
-      <c r="B9" s="31"/>
-      <c r="C9" s="31"/>
-      <c r="D9" s="31"/>
-      <c r="E9" s="31"/>
-      <c r="F9" s="32"/>
-      <c r="G9" s="32"/>
-      <c r="H9" s="32"/>
-      <c r="I9" s="32"/>
-      <c r="J9" s="32"/>
+      <c r="A9" s="27"/>
+      <c r="B9" s="27"/>
+      <c r="C9" s="27"/>
+      <c r="D9" s="27"/>
+      <c r="E9" s="27"/>
+      <c r="F9" s="28"/>
+      <c r="G9" s="28"/>
+      <c r="H9" s="28"/>
+      <c r="I9" s="28"/>
+      <c r="J9" s="28"/>
     </row>
     <row r="10" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="31" t="s">
+      <c r="A10" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="B10" s="31"/>
-      <c r="C10" s="31"/>
-      <c r="D10" s="31"/>
-      <c r="E10" s="31"/>
-      <c r="F10" s="32" t="s">
+      <c r="B10" s="27"/>
+      <c r="C10" s="27"/>
+      <c r="D10" s="27"/>
+      <c r="E10" s="27"/>
+      <c r="F10" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="G10" s="32"/>
-      <c r="H10" s="32"/>
-      <c r="I10" s="32"/>
-      <c r="J10" s="32"/>
+      <c r="G10" s="28"/>
+      <c r="H10" s="28"/>
+      <c r="I10" s="28"/>
+      <c r="J10" s="28"/>
     </row>
     <row r="11" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="31"/>
-      <c r="B11" s="31"/>
-      <c r="C11" s="31"/>
-      <c r="D11" s="31"/>
-      <c r="E11" s="31"/>
-      <c r="F11" s="32"/>
-      <c r="G11" s="32"/>
-      <c r="H11" s="32"/>
-      <c r="I11" s="32"/>
-      <c r="J11" s="32"/>
+      <c r="A11" s="27"/>
+      <c r="B11" s="27"/>
+      <c r="C11" s="27"/>
+      <c r="D11" s="27"/>
+      <c r="E11" s="27"/>
+      <c r="F11" s="28"/>
+      <c r="G11" s="28"/>
+      <c r="H11" s="28"/>
+      <c r="I11" s="28"/>
+      <c r="J11" s="28"/>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="10">
     <mergeCell ref="B1:C1"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="G2:H2"/>
     <mergeCell ref="I2:J2"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B6:D6"/>
     <mergeCell ref="A8:E9"/>
     <mergeCell ref="F8:J9"/>
     <mergeCell ref="A10:E11"/>
@@ -2611,94 +2615,96 @@
       <c r="B5" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="C5" s="17"/>
-      <c r="D5" s="18"/>
-      <c r="E5" s="19"/>
-      <c r="F5" s="20"/>
-      <c r="G5" s="20"/>
-      <c r="H5" s="20"/>
-      <c r="I5" s="21"/>
-      <c r="J5" s="22"/>
+      <c r="C5" s="16"/>
+      <c r="D5" s="16"/>
+      <c r="E5" s="17"/>
+      <c r="F5" s="18"/>
+      <c r="G5" s="18"/>
+      <c r="H5" s="18"/>
+      <c r="I5" s="19"/>
+      <c r="J5" s="20"/>
     </row>
     <row r="6" ht="150" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="23" t="s">
+      <c r="A6" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="24" t="s">
+      <c r="B6" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="C6" s="25"/>
-      <c r="D6" s="26"/>
-      <c r="E6" s="27"/>
-      <c r="F6" s="28"/>
-      <c r="G6" s="28"/>
-      <c r="H6" s="28"/>
-      <c r="I6" s="29"/>
-      <c r="J6" s="30"/>
+      <c r="C6" s="22"/>
+      <c r="D6" s="22"/>
+      <c r="E6" s="23"/>
+      <c r="F6" s="24"/>
+      <c r="G6" s="24"/>
+      <c r="H6" s="24"/>
+      <c r="I6" s="25"/>
+      <c r="J6" s="26"/>
     </row>
     <row r="7" ht="78.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="8" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="31" t="s">
+      <c r="A8" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="31"/>
-      <c r="C8" s="31"/>
-      <c r="D8" s="31"/>
-      <c r="E8" s="31"/>
-      <c r="F8" s="32" t="s">
+      <c r="B8" s="27"/>
+      <c r="C8" s="27"/>
+      <c r="D8" s="27"/>
+      <c r="E8" s="27"/>
+      <c r="F8" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="G8" s="32"/>
-      <c r="H8" s="32"/>
-      <c r="I8" s="32"/>
-      <c r="J8" s="32"/>
+      <c r="G8" s="28"/>
+      <c r="H8" s="28"/>
+      <c r="I8" s="28"/>
+      <c r="J8" s="28"/>
     </row>
     <row r="9" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="31"/>
-      <c r="B9" s="31"/>
-      <c r="C9" s="31"/>
-      <c r="D9" s="31"/>
-      <c r="E9" s="31"/>
-      <c r="F9" s="32"/>
-      <c r="G9" s="32"/>
-      <c r="H9" s="32"/>
-      <c r="I9" s="32"/>
-      <c r="J9" s="32"/>
+      <c r="A9" s="27"/>
+      <c r="B9" s="27"/>
+      <c r="C9" s="27"/>
+      <c r="D9" s="27"/>
+      <c r="E9" s="27"/>
+      <c r="F9" s="28"/>
+      <c r="G9" s="28"/>
+      <c r="H9" s="28"/>
+      <c r="I9" s="28"/>
+      <c r="J9" s="28"/>
     </row>
     <row r="10" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="31" t="s">
+      <c r="A10" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="B10" s="31"/>
-      <c r="C10" s="31"/>
-      <c r="D10" s="31"/>
-      <c r="E10" s="31"/>
-      <c r="F10" s="32" t="s">
+      <c r="B10" s="27"/>
+      <c r="C10" s="27"/>
+      <c r="D10" s="27"/>
+      <c r="E10" s="27"/>
+      <c r="F10" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="G10" s="32"/>
-      <c r="H10" s="32"/>
-      <c r="I10" s="32"/>
-      <c r="J10" s="32"/>
+      <c r="G10" s="28"/>
+      <c r="H10" s="28"/>
+      <c r="I10" s="28"/>
+      <c r="J10" s="28"/>
     </row>
     <row r="11" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="31"/>
-      <c r="B11" s="31"/>
-      <c r="C11" s="31"/>
-      <c r="D11" s="31"/>
-      <c r="E11" s="31"/>
-      <c r="F11" s="32"/>
-      <c r="G11" s="32"/>
-      <c r="H11" s="32"/>
-      <c r="I11" s="32"/>
-      <c r="J11" s="32"/>
+      <c r="A11" s="27"/>
+      <c r="B11" s="27"/>
+      <c r="C11" s="27"/>
+      <c r="D11" s="27"/>
+      <c r="E11" s="27"/>
+      <c r="F11" s="28"/>
+      <c r="G11" s="28"/>
+      <c r="H11" s="28"/>
+      <c r="I11" s="28"/>
+      <c r="J11" s="28"/>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="10">
     <mergeCell ref="B1:C1"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="G2:H2"/>
     <mergeCell ref="I2:J2"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B6:D6"/>
     <mergeCell ref="A8:E9"/>
     <mergeCell ref="F8:J9"/>
     <mergeCell ref="A10:E11"/>
@@ -2803,94 +2809,96 @@
       <c r="B5" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="C5" s="17"/>
-      <c r="D5" s="18"/>
-      <c r="E5" s="19"/>
-      <c r="F5" s="20"/>
-      <c r="G5" s="20"/>
-      <c r="H5" s="20"/>
-      <c r="I5" s="21"/>
-      <c r="J5" s="22"/>
+      <c r="C5" s="16"/>
+      <c r="D5" s="16"/>
+      <c r="E5" s="17"/>
+      <c r="F5" s="18"/>
+      <c r="G5" s="18"/>
+      <c r="H5" s="18"/>
+      <c r="I5" s="19"/>
+      <c r="J5" s="20"/>
     </row>
     <row r="6" ht="150" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="23" t="s">
+      <c r="A6" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="24" t="s">
+      <c r="B6" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="C6" s="25"/>
-      <c r="D6" s="26"/>
-      <c r="E6" s="27"/>
-      <c r="F6" s="28"/>
-      <c r="G6" s="28"/>
-      <c r="H6" s="28"/>
-      <c r="I6" s="29"/>
-      <c r="J6" s="30"/>
+      <c r="C6" s="22"/>
+      <c r="D6" s="22"/>
+      <c r="E6" s="23"/>
+      <c r="F6" s="24"/>
+      <c r="G6" s="24"/>
+      <c r="H6" s="24"/>
+      <c r="I6" s="25"/>
+      <c r="J6" s="26"/>
     </row>
     <row r="7" ht="78.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="8" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="31" t="s">
+      <c r="A8" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="31"/>
-      <c r="C8" s="31"/>
-      <c r="D8" s="31"/>
-      <c r="E8" s="31"/>
-      <c r="F8" s="32" t="s">
+      <c r="B8" s="27"/>
+      <c r="C8" s="27"/>
+      <c r="D8" s="27"/>
+      <c r="E8" s="27"/>
+      <c r="F8" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="G8" s="32"/>
-      <c r="H8" s="32"/>
-      <c r="I8" s="32"/>
-      <c r="J8" s="32"/>
+      <c r="G8" s="28"/>
+      <c r="H8" s="28"/>
+      <c r="I8" s="28"/>
+      <c r="J8" s="28"/>
     </row>
     <row r="9" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="31"/>
-      <c r="B9" s="31"/>
-      <c r="C9" s="31"/>
-      <c r="D9" s="31"/>
-      <c r="E9" s="31"/>
-      <c r="F9" s="32"/>
-      <c r="G9" s="32"/>
-      <c r="H9" s="32"/>
-      <c r="I9" s="32"/>
-      <c r="J9" s="32"/>
+      <c r="A9" s="27"/>
+      <c r="B9" s="27"/>
+      <c r="C9" s="27"/>
+      <c r="D9" s="27"/>
+      <c r="E9" s="27"/>
+      <c r="F9" s="28"/>
+      <c r="G9" s="28"/>
+      <c r="H9" s="28"/>
+      <c r="I9" s="28"/>
+      <c r="J9" s="28"/>
     </row>
     <row r="10" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="31" t="s">
+      <c r="A10" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="B10" s="31"/>
-      <c r="C10" s="31"/>
-      <c r="D10" s="31"/>
-      <c r="E10" s="31"/>
-      <c r="F10" s="32" t="s">
+      <c r="B10" s="27"/>
+      <c r="C10" s="27"/>
+      <c r="D10" s="27"/>
+      <c r="E10" s="27"/>
+      <c r="F10" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="G10" s="32"/>
-      <c r="H10" s="32"/>
-      <c r="I10" s="32"/>
-      <c r="J10" s="32"/>
+      <c r="G10" s="28"/>
+      <c r="H10" s="28"/>
+      <c r="I10" s="28"/>
+      <c r="J10" s="28"/>
     </row>
     <row r="11" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="31"/>
-      <c r="B11" s="31"/>
-      <c r="C11" s="31"/>
-      <c r="D11" s="31"/>
-      <c r="E11" s="31"/>
-      <c r="F11" s="32"/>
-      <c r="G11" s="32"/>
-      <c r="H11" s="32"/>
-      <c r="I11" s="32"/>
-      <c r="J11" s="32"/>
+      <c r="A11" s="27"/>
+      <c r="B11" s="27"/>
+      <c r="C11" s="27"/>
+      <c r="D11" s="27"/>
+      <c r="E11" s="27"/>
+      <c r="F11" s="28"/>
+      <c r="G11" s="28"/>
+      <c r="H11" s="28"/>
+      <c r="I11" s="28"/>
+      <c r="J11" s="28"/>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="10">
     <mergeCell ref="B1:C1"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="G2:H2"/>
     <mergeCell ref="I2:J2"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B6:D6"/>
     <mergeCell ref="A8:E9"/>
     <mergeCell ref="F8:J9"/>
     <mergeCell ref="A10:E11"/>
@@ -2995,94 +3003,96 @@
       <c r="B5" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="C5" s="17"/>
-      <c r="D5" s="18"/>
-      <c r="E5" s="19"/>
-      <c r="F5" s="20"/>
-      <c r="G5" s="20"/>
-      <c r="H5" s="20"/>
-      <c r="I5" s="21"/>
-      <c r="J5" s="22"/>
+      <c r="C5" s="16"/>
+      <c r="D5" s="16"/>
+      <c r="E5" s="17"/>
+      <c r="F5" s="18"/>
+      <c r="G5" s="18"/>
+      <c r="H5" s="18"/>
+      <c r="I5" s="19"/>
+      <c r="J5" s="20"/>
     </row>
     <row r="6" ht="150" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="23" t="s">
+      <c r="A6" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="24" t="s">
+      <c r="B6" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="C6" s="25"/>
-      <c r="D6" s="26"/>
-      <c r="E6" s="27"/>
-      <c r="F6" s="28"/>
-      <c r="G6" s="28"/>
-      <c r="H6" s="28"/>
-      <c r="I6" s="29"/>
-      <c r="J6" s="30"/>
+      <c r="C6" s="22"/>
+      <c r="D6" s="22"/>
+      <c r="E6" s="23"/>
+      <c r="F6" s="24"/>
+      <c r="G6" s="24"/>
+      <c r="H6" s="24"/>
+      <c r="I6" s="25"/>
+      <c r="J6" s="26"/>
     </row>
     <row r="7" ht="78.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="8" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="31" t="s">
+      <c r="A8" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="31"/>
-      <c r="C8" s="31"/>
-      <c r="D8" s="31"/>
-      <c r="E8" s="31"/>
-      <c r="F8" s="32" t="s">
+      <c r="B8" s="27"/>
+      <c r="C8" s="27"/>
+      <c r="D8" s="27"/>
+      <c r="E8" s="27"/>
+      <c r="F8" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="G8" s="32"/>
-      <c r="H8" s="32"/>
-      <c r="I8" s="32"/>
-      <c r="J8" s="32"/>
+      <c r="G8" s="28"/>
+      <c r="H8" s="28"/>
+      <c r="I8" s="28"/>
+      <c r="J8" s="28"/>
     </row>
     <row r="9" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="31"/>
-      <c r="B9" s="31"/>
-      <c r="C9" s="31"/>
-      <c r="D9" s="31"/>
-      <c r="E9" s="31"/>
-      <c r="F9" s="32"/>
-      <c r="G9" s="32"/>
-      <c r="H9" s="32"/>
-      <c r="I9" s="32"/>
-      <c r="J9" s="32"/>
+      <c r="A9" s="27"/>
+      <c r="B9" s="27"/>
+      <c r="C9" s="27"/>
+      <c r="D9" s="27"/>
+      <c r="E9" s="27"/>
+      <c r="F9" s="28"/>
+      <c r="G9" s="28"/>
+      <c r="H9" s="28"/>
+      <c r="I9" s="28"/>
+      <c r="J9" s="28"/>
     </row>
     <row r="10" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="31" t="s">
+      <c r="A10" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="B10" s="31"/>
-      <c r="C10" s="31"/>
-      <c r="D10" s="31"/>
-      <c r="E10" s="31"/>
-      <c r="F10" s="32" t="s">
+      <c r="B10" s="27"/>
+      <c r="C10" s="27"/>
+      <c r="D10" s="27"/>
+      <c r="E10" s="27"/>
+      <c r="F10" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="G10" s="32"/>
-      <c r="H10" s="32"/>
-      <c r="I10" s="32"/>
-      <c r="J10" s="32"/>
+      <c r="G10" s="28"/>
+      <c r="H10" s="28"/>
+      <c r="I10" s="28"/>
+      <c r="J10" s="28"/>
     </row>
     <row r="11" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="31"/>
-      <c r="B11" s="31"/>
-      <c r="C11" s="31"/>
-      <c r="D11" s="31"/>
-      <c r="E11" s="31"/>
-      <c r="F11" s="32"/>
-      <c r="G11" s="32"/>
-      <c r="H11" s="32"/>
-      <c r="I11" s="32"/>
-      <c r="J11" s="32"/>
+      <c r="A11" s="27"/>
+      <c r="B11" s="27"/>
+      <c r="C11" s="27"/>
+      <c r="D11" s="27"/>
+      <c r="E11" s="27"/>
+      <c r="F11" s="28"/>
+      <c r="G11" s="28"/>
+      <c r="H11" s="28"/>
+      <c r="I11" s="28"/>
+      <c r="J11" s="28"/>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="10">
     <mergeCell ref="B1:C1"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="G2:H2"/>
     <mergeCell ref="I2:J2"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B6:D6"/>
     <mergeCell ref="A8:E9"/>
     <mergeCell ref="F8:J9"/>
     <mergeCell ref="A10:E11"/>
@@ -3187,94 +3197,96 @@
       <c r="B5" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="C5" s="17"/>
-      <c r="D5" s="18"/>
-      <c r="E5" s="19"/>
-      <c r="F5" s="20"/>
-      <c r="G5" s="20"/>
-      <c r="H5" s="20"/>
-      <c r="I5" s="21"/>
-      <c r="J5" s="22"/>
+      <c r="C5" s="16"/>
+      <c r="D5" s="16"/>
+      <c r="E5" s="17"/>
+      <c r="F5" s="18"/>
+      <c r="G5" s="18"/>
+      <c r="H5" s="18"/>
+      <c r="I5" s="19"/>
+      <c r="J5" s="20"/>
     </row>
     <row r="6" ht="150" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="23" t="s">
+      <c r="A6" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="24" t="s">
+      <c r="B6" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="C6" s="25"/>
-      <c r="D6" s="26"/>
-      <c r="E6" s="27"/>
-      <c r="F6" s="28"/>
-      <c r="G6" s="28"/>
-      <c r="H6" s="28"/>
-      <c r="I6" s="29"/>
-      <c r="J6" s="30"/>
+      <c r="C6" s="22"/>
+      <c r="D6" s="22"/>
+      <c r="E6" s="23"/>
+      <c r="F6" s="24"/>
+      <c r="G6" s="24"/>
+      <c r="H6" s="24"/>
+      <c r="I6" s="25"/>
+      <c r="J6" s="26"/>
     </row>
     <row r="7" ht="78.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="8" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="31" t="s">
+      <c r="A8" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="31"/>
-      <c r="C8" s="31"/>
-      <c r="D8" s="31"/>
-      <c r="E8" s="31"/>
-      <c r="F8" s="32" t="s">
+      <c r="B8" s="27"/>
+      <c r="C8" s="27"/>
+      <c r="D8" s="27"/>
+      <c r="E8" s="27"/>
+      <c r="F8" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="G8" s="32"/>
-      <c r="H8" s="32"/>
-      <c r="I8" s="32"/>
-      <c r="J8" s="32"/>
+      <c r="G8" s="28"/>
+      <c r="H8" s="28"/>
+      <c r="I8" s="28"/>
+      <c r="J8" s="28"/>
     </row>
     <row r="9" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="31"/>
-      <c r="B9" s="31"/>
-      <c r="C9" s="31"/>
-      <c r="D9" s="31"/>
-      <c r="E9" s="31"/>
-      <c r="F9" s="32"/>
-      <c r="G9" s="32"/>
-      <c r="H9" s="32"/>
-      <c r="I9" s="32"/>
-      <c r="J9" s="32"/>
+      <c r="A9" s="27"/>
+      <c r="B9" s="27"/>
+      <c r="C9" s="27"/>
+      <c r="D9" s="27"/>
+      <c r="E9" s="27"/>
+      <c r="F9" s="28"/>
+      <c r="G9" s="28"/>
+      <c r="H9" s="28"/>
+      <c r="I9" s="28"/>
+      <c r="J9" s="28"/>
     </row>
     <row r="10" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="31" t="s">
+      <c r="A10" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="B10" s="31"/>
-      <c r="C10" s="31"/>
-      <c r="D10" s="31"/>
-      <c r="E10" s="31"/>
-      <c r="F10" s="32" t="s">
+      <c r="B10" s="27"/>
+      <c r="C10" s="27"/>
+      <c r="D10" s="27"/>
+      <c r="E10" s="27"/>
+      <c r="F10" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="G10" s="32"/>
-      <c r="H10" s="32"/>
-      <c r="I10" s="32"/>
-      <c r="J10" s="32"/>
+      <c r="G10" s="28"/>
+      <c r="H10" s="28"/>
+      <c r="I10" s="28"/>
+      <c r="J10" s="28"/>
     </row>
     <row r="11" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="31"/>
-      <c r="B11" s="31"/>
-      <c r="C11" s="31"/>
-      <c r="D11" s="31"/>
-      <c r="E11" s="31"/>
-      <c r="F11" s="32"/>
-      <c r="G11" s="32"/>
-      <c r="H11" s="32"/>
-      <c r="I11" s="32"/>
-      <c r="J11" s="32"/>
+      <c r="A11" s="27"/>
+      <c r="B11" s="27"/>
+      <c r="C11" s="27"/>
+      <c r="D11" s="27"/>
+      <c r="E11" s="27"/>
+      <c r="F11" s="28"/>
+      <c r="G11" s="28"/>
+      <c r="H11" s="28"/>
+      <c r="I11" s="28"/>
+      <c r="J11" s="28"/>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="10">
     <mergeCell ref="B1:C1"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="G2:H2"/>
     <mergeCell ref="I2:J2"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B6:D6"/>
     <mergeCell ref="A8:E9"/>
     <mergeCell ref="F8:J9"/>
     <mergeCell ref="A10:E11"/>
@@ -3379,94 +3391,96 @@
       <c r="B5" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="C5" s="17"/>
-      <c r="D5" s="18"/>
-      <c r="E5" s="19"/>
-      <c r="F5" s="20"/>
-      <c r="G5" s="20"/>
-      <c r="H5" s="20"/>
-      <c r="I5" s="21"/>
-      <c r="J5" s="22"/>
+      <c r="C5" s="16"/>
+      <c r="D5" s="16"/>
+      <c r="E5" s="17"/>
+      <c r="F5" s="18"/>
+      <c r="G5" s="18"/>
+      <c r="H5" s="18"/>
+      <c r="I5" s="19"/>
+      <c r="J5" s="20"/>
     </row>
     <row r="6" ht="150" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="23" t="s">
+      <c r="A6" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="24" t="s">
+      <c r="B6" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="C6" s="25"/>
-      <c r="D6" s="26"/>
-      <c r="E6" s="27"/>
-      <c r="F6" s="28"/>
-      <c r="G6" s="28"/>
-      <c r="H6" s="28"/>
-      <c r="I6" s="29"/>
-      <c r="J6" s="30"/>
+      <c r="C6" s="22"/>
+      <c r="D6" s="22"/>
+      <c r="E6" s="23"/>
+      <c r="F6" s="24"/>
+      <c r="G6" s="24"/>
+      <c r="H6" s="24"/>
+      <c r="I6" s="25"/>
+      <c r="J6" s="26"/>
     </row>
     <row r="7" ht="78.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="8" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="31" t="s">
+      <c r="A8" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="31"/>
-      <c r="C8" s="31"/>
-      <c r="D8" s="31"/>
-      <c r="E8" s="31"/>
-      <c r="F8" s="32" t="s">
+      <c r="B8" s="27"/>
+      <c r="C8" s="27"/>
+      <c r="D8" s="27"/>
+      <c r="E8" s="27"/>
+      <c r="F8" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="G8" s="32"/>
-      <c r="H8" s="32"/>
-      <c r="I8" s="32"/>
-      <c r="J8" s="32"/>
+      <c r="G8" s="28"/>
+      <c r="H8" s="28"/>
+      <c r="I8" s="28"/>
+      <c r="J8" s="28"/>
     </row>
     <row r="9" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="31"/>
-      <c r="B9" s="31"/>
-      <c r="C9" s="31"/>
-      <c r="D9" s="31"/>
-      <c r="E9" s="31"/>
-      <c r="F9" s="32"/>
-      <c r="G9" s="32"/>
-      <c r="H9" s="32"/>
-      <c r="I9" s="32"/>
-      <c r="J9" s="32"/>
+      <c r="A9" s="27"/>
+      <c r="B9" s="27"/>
+      <c r="C9" s="27"/>
+      <c r="D9" s="27"/>
+      <c r="E9" s="27"/>
+      <c r="F9" s="28"/>
+      <c r="G9" s="28"/>
+      <c r="H9" s="28"/>
+      <c r="I9" s="28"/>
+      <c r="J9" s="28"/>
     </row>
     <row r="10" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="31" t="s">
+      <c r="A10" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="B10" s="31"/>
-      <c r="C10" s="31"/>
-      <c r="D10" s="31"/>
-      <c r="E10" s="31"/>
-      <c r="F10" s="32" t="s">
+      <c r="B10" s="27"/>
+      <c r="C10" s="27"/>
+      <c r="D10" s="27"/>
+      <c r="E10" s="27"/>
+      <c r="F10" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="G10" s="32"/>
-      <c r="H10" s="32"/>
-      <c r="I10" s="32"/>
-      <c r="J10" s="32"/>
+      <c r="G10" s="28"/>
+      <c r="H10" s="28"/>
+      <c r="I10" s="28"/>
+      <c r="J10" s="28"/>
     </row>
     <row r="11" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="31"/>
-      <c r="B11" s="31"/>
-      <c r="C11" s="31"/>
-      <c r="D11" s="31"/>
-      <c r="E11" s="31"/>
-      <c r="F11" s="32"/>
-      <c r="G11" s="32"/>
-      <c r="H11" s="32"/>
-      <c r="I11" s="32"/>
-      <c r="J11" s="32"/>
+      <c r="A11" s="27"/>
+      <c r="B11" s="27"/>
+      <c r="C11" s="27"/>
+      <c r="D11" s="27"/>
+      <c r="E11" s="27"/>
+      <c r="F11" s="28"/>
+      <c r="G11" s="28"/>
+      <c r="H11" s="28"/>
+      <c r="I11" s="28"/>
+      <c r="J11" s="28"/>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="10">
     <mergeCell ref="B1:C1"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="G2:H2"/>
     <mergeCell ref="I2:J2"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B6:D6"/>
     <mergeCell ref="A8:E9"/>
     <mergeCell ref="F8:J9"/>
     <mergeCell ref="A10:E11"/>
@@ -3571,94 +3585,96 @@
       <c r="B5" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="C5" s="17"/>
-      <c r="D5" s="18"/>
-      <c r="E5" s="19"/>
-      <c r="F5" s="20"/>
-      <c r="G5" s="20"/>
-      <c r="H5" s="20"/>
-      <c r="I5" s="21"/>
-      <c r="J5" s="22"/>
+      <c r="C5" s="16"/>
+      <c r="D5" s="16"/>
+      <c r="E5" s="17"/>
+      <c r="F5" s="18"/>
+      <c r="G5" s="18"/>
+      <c r="H5" s="18"/>
+      <c r="I5" s="19"/>
+      <c r="J5" s="20"/>
     </row>
     <row r="6" ht="150" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="23" t="s">
+      <c r="A6" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="24" t="s">
+      <c r="B6" s="22" t="s">
         <v>40</v>
       </c>
-      <c r="C6" s="25"/>
-      <c r="D6" s="26"/>
-      <c r="E6" s="27"/>
-      <c r="F6" s="28"/>
-      <c r="G6" s="28"/>
-      <c r="H6" s="28"/>
-      <c r="I6" s="29"/>
-      <c r="J6" s="30"/>
+      <c r="C6" s="22"/>
+      <c r="D6" s="22"/>
+      <c r="E6" s="23"/>
+      <c r="F6" s="24"/>
+      <c r="G6" s="24"/>
+      <c r="H6" s="24"/>
+      <c r="I6" s="25"/>
+      <c r="J6" s="26"/>
     </row>
     <row r="7" ht="78.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="8" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="31" t="s">
+      <c r="A8" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="31"/>
-      <c r="C8" s="31"/>
-      <c r="D8" s="31"/>
-      <c r="E8" s="31"/>
-      <c r="F8" s="32" t="s">
+      <c r="B8" s="27"/>
+      <c r="C8" s="27"/>
+      <c r="D8" s="27"/>
+      <c r="E8" s="27"/>
+      <c r="F8" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="G8" s="32"/>
-      <c r="H8" s="32"/>
-      <c r="I8" s="32"/>
-      <c r="J8" s="32"/>
+      <c r="G8" s="28"/>
+      <c r="H8" s="28"/>
+      <c r="I8" s="28"/>
+      <c r="J8" s="28"/>
     </row>
     <row r="9" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="31"/>
-      <c r="B9" s="31"/>
-      <c r="C9" s="31"/>
-      <c r="D9" s="31"/>
-      <c r="E9" s="31"/>
-      <c r="F9" s="32"/>
-      <c r="G9" s="32"/>
-      <c r="H9" s="32"/>
-      <c r="I9" s="32"/>
-      <c r="J9" s="32"/>
+      <c r="A9" s="27"/>
+      <c r="B9" s="27"/>
+      <c r="C9" s="27"/>
+      <c r="D9" s="27"/>
+      <c r="E9" s="27"/>
+      <c r="F9" s="28"/>
+      <c r="G9" s="28"/>
+      <c r="H9" s="28"/>
+      <c r="I9" s="28"/>
+      <c r="J9" s="28"/>
     </row>
     <row r="10" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="31" t="s">
+      <c r="A10" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="B10" s="31"/>
-      <c r="C10" s="31"/>
-      <c r="D10" s="31"/>
-      <c r="E10" s="31"/>
-      <c r="F10" s="32" t="s">
+      <c r="B10" s="27"/>
+      <c r="C10" s="27"/>
+      <c r="D10" s="27"/>
+      <c r="E10" s="27"/>
+      <c r="F10" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="G10" s="32"/>
-      <c r="H10" s="32"/>
-      <c r="I10" s="32"/>
-      <c r="J10" s="32"/>
+      <c r="G10" s="28"/>
+      <c r="H10" s="28"/>
+      <c r="I10" s="28"/>
+      <c r="J10" s="28"/>
     </row>
     <row r="11" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="31"/>
-      <c r="B11" s="31"/>
-      <c r="C11" s="31"/>
-      <c r="D11" s="31"/>
-      <c r="E11" s="31"/>
-      <c r="F11" s="32"/>
-      <c r="G11" s="32"/>
-      <c r="H11" s="32"/>
-      <c r="I11" s="32"/>
-      <c r="J11" s="32"/>
+      <c r="A11" s="27"/>
+      <c r="B11" s="27"/>
+      <c r="C11" s="27"/>
+      <c r="D11" s="27"/>
+      <c r="E11" s="27"/>
+      <c r="F11" s="28"/>
+      <c r="G11" s="28"/>
+      <c r="H11" s="28"/>
+      <c r="I11" s="28"/>
+      <c r="J11" s="28"/>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="10">
     <mergeCell ref="B1:C1"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="G2:H2"/>
     <mergeCell ref="I2:J2"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B6:D6"/>
     <mergeCell ref="A8:E9"/>
     <mergeCell ref="F8:J9"/>
     <mergeCell ref="A10:E11"/>
@@ -3763,94 +3779,96 @@
       <c r="B5" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="C5" s="17"/>
-      <c r="D5" s="18"/>
-      <c r="E5" s="19"/>
-      <c r="F5" s="20"/>
-      <c r="G5" s="20"/>
-      <c r="H5" s="20"/>
-      <c r="I5" s="21"/>
-      <c r="J5" s="22"/>
+      <c r="C5" s="16"/>
+      <c r="D5" s="16"/>
+      <c r="E5" s="17"/>
+      <c r="F5" s="18"/>
+      <c r="G5" s="18"/>
+      <c r="H5" s="18"/>
+      <c r="I5" s="19"/>
+      <c r="J5" s="20"/>
     </row>
     <row r="6" ht="150" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="23" t="s">
+      <c r="A6" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="24" t="s">
+      <c r="B6" s="22" t="s">
         <v>43</v>
       </c>
-      <c r="C6" s="25"/>
-      <c r="D6" s="26"/>
-      <c r="E6" s="27"/>
-      <c r="F6" s="28"/>
-      <c r="G6" s="28"/>
-      <c r="H6" s="28"/>
-      <c r="I6" s="29"/>
-      <c r="J6" s="30"/>
+      <c r="C6" s="22"/>
+      <c r="D6" s="22"/>
+      <c r="E6" s="23"/>
+      <c r="F6" s="24"/>
+      <c r="G6" s="24"/>
+      <c r="H6" s="24"/>
+      <c r="I6" s="25"/>
+      <c r="J6" s="26"/>
     </row>
     <row r="7" ht="78.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="8" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="31" t="s">
+      <c r="A8" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="31"/>
-      <c r="C8" s="31"/>
-      <c r="D8" s="31"/>
-      <c r="E8" s="31"/>
-      <c r="F8" s="32" t="s">
+      <c r="B8" s="27"/>
+      <c r="C8" s="27"/>
+      <c r="D8" s="27"/>
+      <c r="E8" s="27"/>
+      <c r="F8" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="G8" s="32"/>
-      <c r="H8" s="32"/>
-      <c r="I8" s="32"/>
-      <c r="J8" s="32"/>
+      <c r="G8" s="28"/>
+      <c r="H8" s="28"/>
+      <c r="I8" s="28"/>
+      <c r="J8" s="28"/>
     </row>
     <row r="9" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="31"/>
-      <c r="B9" s="31"/>
-      <c r="C9" s="31"/>
-      <c r="D9" s="31"/>
-      <c r="E9" s="31"/>
-      <c r="F9" s="32"/>
-      <c r="G9" s="32"/>
-      <c r="H9" s="32"/>
-      <c r="I9" s="32"/>
-      <c r="J9" s="32"/>
+      <c r="A9" s="27"/>
+      <c r="B9" s="27"/>
+      <c r="C9" s="27"/>
+      <c r="D9" s="27"/>
+      <c r="E9" s="27"/>
+      <c r="F9" s="28"/>
+      <c r="G9" s="28"/>
+      <c r="H9" s="28"/>
+      <c r="I9" s="28"/>
+      <c r="J9" s="28"/>
     </row>
     <row r="10" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="31" t="s">
+      <c r="A10" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="B10" s="31"/>
-      <c r="C10" s="31"/>
-      <c r="D10" s="31"/>
-      <c r="E10" s="31"/>
-      <c r="F10" s="32" t="s">
+      <c r="B10" s="27"/>
+      <c r="C10" s="27"/>
+      <c r="D10" s="27"/>
+      <c r="E10" s="27"/>
+      <c r="F10" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="G10" s="32"/>
-      <c r="H10" s="32"/>
-      <c r="I10" s="32"/>
-      <c r="J10" s="32"/>
+      <c r="G10" s="28"/>
+      <c r="H10" s="28"/>
+      <c r="I10" s="28"/>
+      <c r="J10" s="28"/>
     </row>
     <row r="11" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="31"/>
-      <c r="B11" s="31"/>
-      <c r="C11" s="31"/>
-      <c r="D11" s="31"/>
-      <c r="E11" s="31"/>
-      <c r="F11" s="32"/>
-      <c r="G11" s="32"/>
-      <c r="H11" s="32"/>
-      <c r="I11" s="32"/>
-      <c r="J11" s="32"/>
+      <c r="A11" s="27"/>
+      <c r="B11" s="27"/>
+      <c r="C11" s="27"/>
+      <c r="D11" s="27"/>
+      <c r="E11" s="27"/>
+      <c r="F11" s="28"/>
+      <c r="G11" s="28"/>
+      <c r="H11" s="28"/>
+      <c r="I11" s="28"/>
+      <c r="J11" s="28"/>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="10">
     <mergeCell ref="B1:C1"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="G2:H2"/>
     <mergeCell ref="I2:J2"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B6:D6"/>
     <mergeCell ref="A8:E9"/>
     <mergeCell ref="F8:J9"/>
     <mergeCell ref="A10:E11"/>
@@ -3955,94 +3973,96 @@
       <c r="B5" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="C5" s="17"/>
-      <c r="D5" s="18"/>
-      <c r="E5" s="19"/>
-      <c r="F5" s="20"/>
-      <c r="G5" s="20"/>
-      <c r="H5" s="20"/>
-      <c r="I5" s="21"/>
-      <c r="J5" s="22"/>
+      <c r="C5" s="16"/>
+      <c r="D5" s="16"/>
+      <c r="E5" s="17"/>
+      <c r="F5" s="18"/>
+      <c r="G5" s="18"/>
+      <c r="H5" s="18"/>
+      <c r="I5" s="19"/>
+      <c r="J5" s="20"/>
     </row>
     <row r="6" ht="150" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="23" t="s">
+      <c r="A6" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="24" t="s">
+      <c r="B6" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="C6" s="25"/>
-      <c r="D6" s="26"/>
-      <c r="E6" s="27"/>
-      <c r="F6" s="28"/>
-      <c r="G6" s="28"/>
-      <c r="H6" s="28"/>
-      <c r="I6" s="29"/>
-      <c r="J6" s="30"/>
+      <c r="C6" s="22"/>
+      <c r="D6" s="22"/>
+      <c r="E6" s="23"/>
+      <c r="F6" s="24"/>
+      <c r="G6" s="24"/>
+      <c r="H6" s="24"/>
+      <c r="I6" s="25"/>
+      <c r="J6" s="26"/>
     </row>
     <row r="7" ht="78.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="8" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="31" t="s">
+      <c r="A8" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="31"/>
-      <c r="C8" s="31"/>
-      <c r="D8" s="31"/>
-      <c r="E8" s="31"/>
-      <c r="F8" s="32" t="s">
+      <c r="B8" s="27"/>
+      <c r="C8" s="27"/>
+      <c r="D8" s="27"/>
+      <c r="E8" s="27"/>
+      <c r="F8" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="G8" s="32"/>
-      <c r="H8" s="32"/>
-      <c r="I8" s="32"/>
-      <c r="J8" s="32"/>
+      <c r="G8" s="28"/>
+      <c r="H8" s="28"/>
+      <c r="I8" s="28"/>
+      <c r="J8" s="28"/>
     </row>
     <row r="9" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="31"/>
-      <c r="B9" s="31"/>
-      <c r="C9" s="31"/>
-      <c r="D9" s="31"/>
-      <c r="E9" s="31"/>
-      <c r="F9" s="32"/>
-      <c r="G9" s="32"/>
-      <c r="H9" s="32"/>
-      <c r="I9" s="32"/>
-      <c r="J9" s="32"/>
+      <c r="A9" s="27"/>
+      <c r="B9" s="27"/>
+      <c r="C9" s="27"/>
+      <c r="D9" s="27"/>
+      <c r="E9" s="27"/>
+      <c r="F9" s="28"/>
+      <c r="G9" s="28"/>
+      <c r="H9" s="28"/>
+      <c r="I9" s="28"/>
+      <c r="J9" s="28"/>
     </row>
     <row r="10" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="31" t="s">
+      <c r="A10" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="B10" s="31"/>
-      <c r="C10" s="31"/>
-      <c r="D10" s="31"/>
-      <c r="E10" s="31"/>
-      <c r="F10" s="32" t="s">
+      <c r="B10" s="27"/>
+      <c r="C10" s="27"/>
+      <c r="D10" s="27"/>
+      <c r="E10" s="27"/>
+      <c r="F10" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="G10" s="32"/>
-      <c r="H10" s="32"/>
-      <c r="I10" s="32"/>
-      <c r="J10" s="32"/>
+      <c r="G10" s="28"/>
+      <c r="H10" s="28"/>
+      <c r="I10" s="28"/>
+      <c r="J10" s="28"/>
     </row>
     <row r="11" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="31"/>
-      <c r="B11" s="31"/>
-      <c r="C11" s="31"/>
-      <c r="D11" s="31"/>
-      <c r="E11" s="31"/>
-      <c r="F11" s="32"/>
-      <c r="G11" s="32"/>
-      <c r="H11" s="32"/>
-      <c r="I11" s="32"/>
-      <c r="J11" s="32"/>
+      <c r="A11" s="27"/>
+      <c r="B11" s="27"/>
+      <c r="C11" s="27"/>
+      <c r="D11" s="27"/>
+      <c r="E11" s="27"/>
+      <c r="F11" s="28"/>
+      <c r="G11" s="28"/>
+      <c r="H11" s="28"/>
+      <c r="I11" s="28"/>
+      <c r="J11" s="28"/>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="10">
     <mergeCell ref="B1:C1"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="G2:H2"/>
     <mergeCell ref="I2:J2"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B6:D6"/>
     <mergeCell ref="A8:E9"/>
     <mergeCell ref="F8:J9"/>
     <mergeCell ref="A10:E11"/>
@@ -4147,94 +4167,96 @@
       <c r="B5" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="C5" s="17"/>
-      <c r="D5" s="18"/>
-      <c r="E5" s="19"/>
-      <c r="F5" s="20"/>
-      <c r="G5" s="20"/>
-      <c r="H5" s="20"/>
-      <c r="I5" s="21"/>
-      <c r="J5" s="22"/>
+      <c r="C5" s="16"/>
+      <c r="D5" s="16"/>
+      <c r="E5" s="17"/>
+      <c r="F5" s="18"/>
+      <c r="G5" s="18"/>
+      <c r="H5" s="18"/>
+      <c r="I5" s="19"/>
+      <c r="J5" s="20"/>
     </row>
     <row r="6" ht="150" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="23" t="s">
+      <c r="A6" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="24" t="s">
+      <c r="B6" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="C6" s="25"/>
-      <c r="D6" s="26"/>
-      <c r="E6" s="27"/>
-      <c r="F6" s="28"/>
-      <c r="G6" s="28"/>
-      <c r="H6" s="28"/>
-      <c r="I6" s="29"/>
-      <c r="J6" s="30"/>
+      <c r="C6" s="22"/>
+      <c r="D6" s="22"/>
+      <c r="E6" s="23"/>
+      <c r="F6" s="24"/>
+      <c r="G6" s="24"/>
+      <c r="H6" s="24"/>
+      <c r="I6" s="25"/>
+      <c r="J6" s="26"/>
     </row>
     <row r="7" ht="78.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="8" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="31" t="s">
+      <c r="A8" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="31"/>
-      <c r="C8" s="31"/>
-      <c r="D8" s="31"/>
-      <c r="E8" s="31"/>
-      <c r="F8" s="32" t="s">
+      <c r="B8" s="27"/>
+      <c r="C8" s="27"/>
+      <c r="D8" s="27"/>
+      <c r="E8" s="27"/>
+      <c r="F8" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="G8" s="32"/>
-      <c r="H8" s="32"/>
-      <c r="I8" s="32"/>
-      <c r="J8" s="32"/>
+      <c r="G8" s="28"/>
+      <c r="H8" s="28"/>
+      <c r="I8" s="28"/>
+      <c r="J8" s="28"/>
     </row>
     <row r="9" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="31"/>
-      <c r="B9" s="31"/>
-      <c r="C9" s="31"/>
-      <c r="D9" s="31"/>
-      <c r="E9" s="31"/>
-      <c r="F9" s="32"/>
-      <c r="G9" s="32"/>
-      <c r="H9" s="32"/>
-      <c r="I9" s="32"/>
-      <c r="J9" s="32"/>
+      <c r="A9" s="27"/>
+      <c r="B9" s="27"/>
+      <c r="C9" s="27"/>
+      <c r="D9" s="27"/>
+      <c r="E9" s="27"/>
+      <c r="F9" s="28"/>
+      <c r="G9" s="28"/>
+      <c r="H9" s="28"/>
+      <c r="I9" s="28"/>
+      <c r="J9" s="28"/>
     </row>
     <row r="10" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="31" t="s">
+      <c r="A10" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="B10" s="31"/>
-      <c r="C10" s="31"/>
-      <c r="D10" s="31"/>
-      <c r="E10" s="31"/>
-      <c r="F10" s="32" t="s">
+      <c r="B10" s="27"/>
+      <c r="C10" s="27"/>
+      <c r="D10" s="27"/>
+      <c r="E10" s="27"/>
+      <c r="F10" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="G10" s="32"/>
-      <c r="H10" s="32"/>
-      <c r="I10" s="32"/>
-      <c r="J10" s="32"/>
+      <c r="G10" s="28"/>
+      <c r="H10" s="28"/>
+      <c r="I10" s="28"/>
+      <c r="J10" s="28"/>
     </row>
     <row r="11" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="31"/>
-      <c r="B11" s="31"/>
-      <c r="C11" s="31"/>
-      <c r="D11" s="31"/>
-      <c r="E11" s="31"/>
-      <c r="F11" s="32"/>
-      <c r="G11" s="32"/>
-      <c r="H11" s="32"/>
-      <c r="I11" s="32"/>
-      <c r="J11" s="32"/>
+      <c r="A11" s="27"/>
+      <c r="B11" s="27"/>
+      <c r="C11" s="27"/>
+      <c r="D11" s="27"/>
+      <c r="E11" s="27"/>
+      <c r="F11" s="28"/>
+      <c r="G11" s="28"/>
+      <c r="H11" s="28"/>
+      <c r="I11" s="28"/>
+      <c r="J11" s="28"/>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="10">
     <mergeCell ref="B1:C1"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="G2:H2"/>
     <mergeCell ref="I2:J2"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B6:D6"/>
     <mergeCell ref="A8:E9"/>
     <mergeCell ref="F8:J9"/>
     <mergeCell ref="A10:E11"/>
@@ -4339,94 +4361,96 @@
       <c r="B5" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="C5" s="17"/>
-      <c r="D5" s="18"/>
-      <c r="E5" s="19"/>
-      <c r="F5" s="20"/>
-      <c r="G5" s="20"/>
-      <c r="H5" s="20"/>
-      <c r="I5" s="21"/>
-      <c r="J5" s="22"/>
+      <c r="C5" s="16"/>
+      <c r="D5" s="16"/>
+      <c r="E5" s="17"/>
+      <c r="F5" s="18"/>
+      <c r="G5" s="18"/>
+      <c r="H5" s="18"/>
+      <c r="I5" s="19"/>
+      <c r="J5" s="20"/>
     </row>
     <row r="6" ht="150" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="23" t="s">
+      <c r="A6" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="24" t="s">
+      <c r="B6" s="22" t="s">
         <v>48</v>
       </c>
-      <c r="C6" s="25"/>
-      <c r="D6" s="26"/>
-      <c r="E6" s="27"/>
-      <c r="F6" s="28"/>
-      <c r="G6" s="28"/>
-      <c r="H6" s="28"/>
-      <c r="I6" s="29"/>
-      <c r="J6" s="30"/>
+      <c r="C6" s="22"/>
+      <c r="D6" s="22"/>
+      <c r="E6" s="23"/>
+      <c r="F6" s="24"/>
+      <c r="G6" s="24"/>
+      <c r="H6" s="24"/>
+      <c r="I6" s="25"/>
+      <c r="J6" s="26"/>
     </row>
     <row r="7" ht="78.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="8" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="31" t="s">
+      <c r="A8" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="31"/>
-      <c r="C8" s="31"/>
-      <c r="D8" s="31"/>
-      <c r="E8" s="31"/>
-      <c r="F8" s="32" t="s">
+      <c r="B8" s="27"/>
+      <c r="C8" s="27"/>
+      <c r="D8" s="27"/>
+      <c r="E8" s="27"/>
+      <c r="F8" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="G8" s="32"/>
-      <c r="H8" s="32"/>
-      <c r="I8" s="32"/>
-      <c r="J8" s="32"/>
+      <c r="G8" s="28"/>
+      <c r="H8" s="28"/>
+      <c r="I8" s="28"/>
+      <c r="J8" s="28"/>
     </row>
     <row r="9" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="31"/>
-      <c r="B9" s="31"/>
-      <c r="C9" s="31"/>
-      <c r="D9" s="31"/>
-      <c r="E9" s="31"/>
-      <c r="F9" s="32"/>
-      <c r="G9" s="32"/>
-      <c r="H9" s="32"/>
-      <c r="I9" s="32"/>
-      <c r="J9" s="32"/>
+      <c r="A9" s="27"/>
+      <c r="B9" s="27"/>
+      <c r="C9" s="27"/>
+      <c r="D9" s="27"/>
+      <c r="E9" s="27"/>
+      <c r="F9" s="28"/>
+      <c r="G9" s="28"/>
+      <c r="H9" s="28"/>
+      <c r="I9" s="28"/>
+      <c r="J9" s="28"/>
     </row>
     <row r="10" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="31" t="s">
+      <c r="A10" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="B10" s="31"/>
-      <c r="C10" s="31"/>
-      <c r="D10" s="31"/>
-      <c r="E10" s="31"/>
-      <c r="F10" s="32" t="s">
+      <c r="B10" s="27"/>
+      <c r="C10" s="27"/>
+      <c r="D10" s="27"/>
+      <c r="E10" s="27"/>
+      <c r="F10" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="G10" s="32"/>
-      <c r="H10" s="32"/>
-      <c r="I10" s="32"/>
-      <c r="J10" s="32"/>
+      <c r="G10" s="28"/>
+      <c r="H10" s="28"/>
+      <c r="I10" s="28"/>
+      <c r="J10" s="28"/>
     </row>
     <row r="11" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="31"/>
-      <c r="B11" s="31"/>
-      <c r="C11" s="31"/>
-      <c r="D11" s="31"/>
-      <c r="E11" s="31"/>
-      <c r="F11" s="32"/>
-      <c r="G11" s="32"/>
-      <c r="H11" s="32"/>
-      <c r="I11" s="32"/>
-      <c r="J11" s="32"/>
+      <c r="A11" s="27"/>
+      <c r="B11" s="27"/>
+      <c r="C11" s="27"/>
+      <c r="D11" s="27"/>
+      <c r="E11" s="27"/>
+      <c r="F11" s="28"/>
+      <c r="G11" s="28"/>
+      <c r="H11" s="28"/>
+      <c r="I11" s="28"/>
+      <c r="J11" s="28"/>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="10">
     <mergeCell ref="B1:C1"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="G2:H2"/>
     <mergeCell ref="I2:J2"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B6:D6"/>
     <mergeCell ref="A8:E9"/>
     <mergeCell ref="F8:J9"/>
     <mergeCell ref="A10:E11"/>
@@ -4531,94 +4555,96 @@
       <c r="B5" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="C5" s="17"/>
-      <c r="D5" s="18"/>
-      <c r="E5" s="19"/>
-      <c r="F5" s="20"/>
-      <c r="G5" s="20"/>
-      <c r="H5" s="20"/>
-      <c r="I5" s="21"/>
-      <c r="J5" s="22"/>
+      <c r="C5" s="16"/>
+      <c r="D5" s="16"/>
+      <c r="E5" s="17"/>
+      <c r="F5" s="18"/>
+      <c r="G5" s="18"/>
+      <c r="H5" s="18"/>
+      <c r="I5" s="19"/>
+      <c r="J5" s="20"/>
     </row>
     <row r="6" ht="150" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="23" t="s">
+      <c r="A6" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="24" t="s">
+      <c r="B6" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="C6" s="25"/>
-      <c r="D6" s="26"/>
-      <c r="E6" s="27"/>
-      <c r="F6" s="28"/>
-      <c r="G6" s="28"/>
-      <c r="H6" s="28"/>
-      <c r="I6" s="29"/>
-      <c r="J6" s="30"/>
+      <c r="C6" s="22"/>
+      <c r="D6" s="22"/>
+      <c r="E6" s="23"/>
+      <c r="F6" s="24"/>
+      <c r="G6" s="24"/>
+      <c r="H6" s="24"/>
+      <c r="I6" s="25"/>
+      <c r="J6" s="26"/>
     </row>
     <row r="7" ht="78.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="8" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="31" t="s">
+      <c r="A8" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="31"/>
-      <c r="C8" s="31"/>
-      <c r="D8" s="31"/>
-      <c r="E8" s="31"/>
-      <c r="F8" s="32" t="s">
+      <c r="B8" s="27"/>
+      <c r="C8" s="27"/>
+      <c r="D8" s="27"/>
+      <c r="E8" s="27"/>
+      <c r="F8" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="G8" s="32"/>
-      <c r="H8" s="32"/>
-      <c r="I8" s="32"/>
-      <c r="J8" s="32"/>
+      <c r="G8" s="28"/>
+      <c r="H8" s="28"/>
+      <c r="I8" s="28"/>
+      <c r="J8" s="28"/>
     </row>
     <row r="9" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="31"/>
-      <c r="B9" s="31"/>
-      <c r="C9" s="31"/>
-      <c r="D9" s="31"/>
-      <c r="E9" s="31"/>
-      <c r="F9" s="32"/>
-      <c r="G9" s="32"/>
-      <c r="H9" s="32"/>
-      <c r="I9" s="32"/>
-      <c r="J9" s="32"/>
+      <c r="A9" s="27"/>
+      <c r="B9" s="27"/>
+      <c r="C9" s="27"/>
+      <c r="D9" s="27"/>
+      <c r="E9" s="27"/>
+      <c r="F9" s="28"/>
+      <c r="G9" s="28"/>
+      <c r="H9" s="28"/>
+      <c r="I9" s="28"/>
+      <c r="J9" s="28"/>
     </row>
     <row r="10" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="31" t="s">
+      <c r="A10" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="B10" s="31"/>
-      <c r="C10" s="31"/>
-      <c r="D10" s="31"/>
-      <c r="E10" s="31"/>
-      <c r="F10" s="32" t="s">
+      <c r="B10" s="27"/>
+      <c r="C10" s="27"/>
+      <c r="D10" s="27"/>
+      <c r="E10" s="27"/>
+      <c r="F10" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="G10" s="32"/>
-      <c r="H10" s="32"/>
-      <c r="I10" s="32"/>
-      <c r="J10" s="32"/>
+      <c r="G10" s="28"/>
+      <c r="H10" s="28"/>
+      <c r="I10" s="28"/>
+      <c r="J10" s="28"/>
     </row>
     <row r="11" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="31"/>
-      <c r="B11" s="31"/>
-      <c r="C11" s="31"/>
-      <c r="D11" s="31"/>
-      <c r="E11" s="31"/>
-      <c r="F11" s="32"/>
-      <c r="G11" s="32"/>
-      <c r="H11" s="32"/>
-      <c r="I11" s="32"/>
-      <c r="J11" s="32"/>
+      <c r="A11" s="27"/>
+      <c r="B11" s="27"/>
+      <c r="C11" s="27"/>
+      <c r="D11" s="27"/>
+      <c r="E11" s="27"/>
+      <c r="F11" s="28"/>
+      <c r="G11" s="28"/>
+      <c r="H11" s="28"/>
+      <c r="I11" s="28"/>
+      <c r="J11" s="28"/>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="10">
     <mergeCell ref="B1:C1"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="G2:H2"/>
     <mergeCell ref="I2:J2"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B6:D6"/>
     <mergeCell ref="A8:E9"/>
     <mergeCell ref="F8:J9"/>
     <mergeCell ref="A10:E11"/>
@@ -4723,94 +4749,96 @@
       <c r="B5" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="C5" s="17"/>
-      <c r="D5" s="18"/>
-      <c r="E5" s="19"/>
-      <c r="F5" s="20"/>
-      <c r="G5" s="20"/>
-      <c r="H5" s="20"/>
-      <c r="I5" s="21"/>
-      <c r="J5" s="22"/>
+      <c r="C5" s="16"/>
+      <c r="D5" s="16"/>
+      <c r="E5" s="17"/>
+      <c r="F5" s="18"/>
+      <c r="G5" s="18"/>
+      <c r="H5" s="18"/>
+      <c r="I5" s="19"/>
+      <c r="J5" s="20"/>
     </row>
     <row r="6" ht="150" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="23" t="s">
+      <c r="A6" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="24" t="s">
+      <c r="B6" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="C6" s="25"/>
-      <c r="D6" s="26"/>
-      <c r="E6" s="27"/>
-      <c r="F6" s="28"/>
-      <c r="G6" s="28"/>
-      <c r="H6" s="28"/>
-      <c r="I6" s="29"/>
-      <c r="J6" s="30"/>
+      <c r="C6" s="22"/>
+      <c r="D6" s="22"/>
+      <c r="E6" s="23"/>
+      <c r="F6" s="24"/>
+      <c r="G6" s="24"/>
+      <c r="H6" s="24"/>
+      <c r="I6" s="25"/>
+      <c r="J6" s="26"/>
     </row>
     <row r="7" ht="78.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="8" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="31" t="s">
+      <c r="A8" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="31"/>
-      <c r="C8" s="31"/>
-      <c r="D8" s="31"/>
-      <c r="E8" s="31"/>
-      <c r="F8" s="32" t="s">
+      <c r="B8" s="27"/>
+      <c r="C8" s="27"/>
+      <c r="D8" s="27"/>
+      <c r="E8" s="27"/>
+      <c r="F8" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="G8" s="32"/>
-      <c r="H8" s="32"/>
-      <c r="I8" s="32"/>
-      <c r="J8" s="32"/>
+      <c r="G8" s="28"/>
+      <c r="H8" s="28"/>
+      <c r="I8" s="28"/>
+      <c r="J8" s="28"/>
     </row>
     <row r="9" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="31"/>
-      <c r="B9" s="31"/>
-      <c r="C9" s="31"/>
-      <c r="D9" s="31"/>
-      <c r="E9" s="31"/>
-      <c r="F9" s="32"/>
-      <c r="G9" s="32"/>
-      <c r="H9" s="32"/>
-      <c r="I9" s="32"/>
-      <c r="J9" s="32"/>
+      <c r="A9" s="27"/>
+      <c r="B9" s="27"/>
+      <c r="C9" s="27"/>
+      <c r="D9" s="27"/>
+      <c r="E9" s="27"/>
+      <c r="F9" s="28"/>
+      <c r="G9" s="28"/>
+      <c r="H9" s="28"/>
+      <c r="I9" s="28"/>
+      <c r="J9" s="28"/>
     </row>
     <row r="10" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="31" t="s">
+      <c r="A10" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="B10" s="31"/>
-      <c r="C10" s="31"/>
-      <c r="D10" s="31"/>
-      <c r="E10" s="31"/>
-      <c r="F10" s="32" t="s">
+      <c r="B10" s="27"/>
+      <c r="C10" s="27"/>
+      <c r="D10" s="27"/>
+      <c r="E10" s="27"/>
+      <c r="F10" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="G10" s="32"/>
-      <c r="H10" s="32"/>
-      <c r="I10" s="32"/>
-      <c r="J10" s="32"/>
+      <c r="G10" s="28"/>
+      <c r="H10" s="28"/>
+      <c r="I10" s="28"/>
+      <c r="J10" s="28"/>
     </row>
     <row r="11" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="31"/>
-      <c r="B11" s="31"/>
-      <c r="C11" s="31"/>
-      <c r="D11" s="31"/>
-      <c r="E11" s="31"/>
-      <c r="F11" s="32"/>
-      <c r="G11" s="32"/>
-      <c r="H11" s="32"/>
-      <c r="I11" s="32"/>
-      <c r="J11" s="32"/>
+      <c r="A11" s="27"/>
+      <c r="B11" s="27"/>
+      <c r="C11" s="27"/>
+      <c r="D11" s="27"/>
+      <c r="E11" s="27"/>
+      <c r="F11" s="28"/>
+      <c r="G11" s="28"/>
+      <c r="H11" s="28"/>
+      <c r="I11" s="28"/>
+      <c r="J11" s="28"/>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="10">
     <mergeCell ref="B1:C1"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="G2:H2"/>
     <mergeCell ref="I2:J2"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B6:D6"/>
     <mergeCell ref="A8:E9"/>
     <mergeCell ref="F8:J9"/>
     <mergeCell ref="A10:E11"/>
@@ -4915,94 +4943,96 @@
       <c r="B5" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="C5" s="17"/>
-      <c r="D5" s="18"/>
-      <c r="E5" s="19"/>
-      <c r="F5" s="20"/>
-      <c r="G5" s="20"/>
-      <c r="H5" s="20"/>
-      <c r="I5" s="21"/>
-      <c r="J5" s="22"/>
+      <c r="C5" s="16"/>
+      <c r="D5" s="16"/>
+      <c r="E5" s="17"/>
+      <c r="F5" s="18"/>
+      <c r="G5" s="18"/>
+      <c r="H5" s="18"/>
+      <c r="I5" s="19"/>
+      <c r="J5" s="20"/>
     </row>
     <row r="6" ht="150" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="23" t="s">
+      <c r="A6" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="24" t="s">
+      <c r="B6" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="C6" s="25"/>
-      <c r="D6" s="26"/>
-      <c r="E6" s="27"/>
-      <c r="F6" s="28"/>
-      <c r="G6" s="28"/>
-      <c r="H6" s="28"/>
-      <c r="I6" s="29"/>
-      <c r="J6" s="30"/>
+      <c r="C6" s="22"/>
+      <c r="D6" s="22"/>
+      <c r="E6" s="23"/>
+      <c r="F6" s="24"/>
+      <c r="G6" s="24"/>
+      <c r="H6" s="24"/>
+      <c r="I6" s="25"/>
+      <c r="J6" s="26"/>
     </row>
     <row r="7" ht="78.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="8" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="31" t="s">
+      <c r="A8" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="31"/>
-      <c r="C8" s="31"/>
-      <c r="D8" s="31"/>
-      <c r="E8" s="31"/>
-      <c r="F8" s="32" t="s">
+      <c r="B8" s="27"/>
+      <c r="C8" s="27"/>
+      <c r="D8" s="27"/>
+      <c r="E8" s="27"/>
+      <c r="F8" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="G8" s="32"/>
-      <c r="H8" s="32"/>
-      <c r="I8" s="32"/>
-      <c r="J8" s="32"/>
+      <c r="G8" s="28"/>
+      <c r="H8" s="28"/>
+      <c r="I8" s="28"/>
+      <c r="J8" s="28"/>
     </row>
     <row r="9" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="31"/>
-      <c r="B9" s="31"/>
-      <c r="C9" s="31"/>
-      <c r="D9" s="31"/>
-      <c r="E9" s="31"/>
-      <c r="F9" s="32"/>
-      <c r="G9" s="32"/>
-      <c r="H9" s="32"/>
-      <c r="I9" s="32"/>
-      <c r="J9" s="32"/>
+      <c r="A9" s="27"/>
+      <c r="B9" s="27"/>
+      <c r="C9" s="27"/>
+      <c r="D9" s="27"/>
+      <c r="E9" s="27"/>
+      <c r="F9" s="28"/>
+      <c r="G9" s="28"/>
+      <c r="H9" s="28"/>
+      <c r="I9" s="28"/>
+      <c r="J9" s="28"/>
     </row>
     <row r="10" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="31" t="s">
+      <c r="A10" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="B10" s="31"/>
-      <c r="C10" s="31"/>
-      <c r="D10" s="31"/>
-      <c r="E10" s="31"/>
-      <c r="F10" s="32" t="s">
+      <c r="B10" s="27"/>
+      <c r="C10" s="27"/>
+      <c r="D10" s="27"/>
+      <c r="E10" s="27"/>
+      <c r="F10" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="G10" s="32"/>
-      <c r="H10" s="32"/>
-      <c r="I10" s="32"/>
-      <c r="J10" s="32"/>
+      <c r="G10" s="28"/>
+      <c r="H10" s="28"/>
+      <c r="I10" s="28"/>
+      <c r="J10" s="28"/>
     </row>
     <row r="11" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="31"/>
-      <c r="B11" s="31"/>
-      <c r="C11" s="31"/>
-      <c r="D11" s="31"/>
-      <c r="E11" s="31"/>
-      <c r="F11" s="32"/>
-      <c r="G11" s="32"/>
-      <c r="H11" s="32"/>
-      <c r="I11" s="32"/>
-      <c r="J11" s="32"/>
+      <c r="A11" s="27"/>
+      <c r="B11" s="27"/>
+      <c r="C11" s="27"/>
+      <c r="D11" s="27"/>
+      <c r="E11" s="27"/>
+      <c r="F11" s="28"/>
+      <c r="G11" s="28"/>
+      <c r="H11" s="28"/>
+      <c r="I11" s="28"/>
+      <c r="J11" s="28"/>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="10">
     <mergeCell ref="B1:C1"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="G2:H2"/>
     <mergeCell ref="I2:J2"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B6:D6"/>
     <mergeCell ref="A8:E9"/>
     <mergeCell ref="F8:J9"/>
     <mergeCell ref="A10:E11"/>
@@ -5107,94 +5137,96 @@
       <c r="B5" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="C5" s="17"/>
-      <c r="D5" s="18"/>
-      <c r="E5" s="19"/>
-      <c r="F5" s="20"/>
-      <c r="G5" s="20"/>
-      <c r="H5" s="20"/>
-      <c r="I5" s="21"/>
-      <c r="J5" s="22"/>
+      <c r="C5" s="16"/>
+      <c r="D5" s="16"/>
+      <c r="E5" s="17"/>
+      <c r="F5" s="18"/>
+      <c r="G5" s="18"/>
+      <c r="H5" s="18"/>
+      <c r="I5" s="19"/>
+      <c r="J5" s="20"/>
     </row>
     <row r="6" ht="150" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="23" t="s">
+      <c r="A6" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="24" t="s">
+      <c r="B6" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="C6" s="25"/>
-      <c r="D6" s="26"/>
-      <c r="E6" s="27"/>
-      <c r="F6" s="28"/>
-      <c r="G6" s="28"/>
-      <c r="H6" s="28"/>
-      <c r="I6" s="29"/>
-      <c r="J6" s="30"/>
+      <c r="C6" s="22"/>
+      <c r="D6" s="22"/>
+      <c r="E6" s="23"/>
+      <c r="F6" s="24"/>
+      <c r="G6" s="24"/>
+      <c r="H6" s="24"/>
+      <c r="I6" s="25"/>
+      <c r="J6" s="26"/>
     </row>
     <row r="7" ht="78.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="8" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="31" t="s">
+      <c r="A8" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="31"/>
-      <c r="C8" s="31"/>
-      <c r="D8" s="31"/>
-      <c r="E8" s="31"/>
-      <c r="F8" s="32" t="s">
+      <c r="B8" s="27"/>
+      <c r="C8" s="27"/>
+      <c r="D8" s="27"/>
+      <c r="E8" s="27"/>
+      <c r="F8" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="G8" s="32"/>
-      <c r="H8" s="32"/>
-      <c r="I8" s="32"/>
-      <c r="J8" s="32"/>
+      <c r="G8" s="28"/>
+      <c r="H8" s="28"/>
+      <c r="I8" s="28"/>
+      <c r="J8" s="28"/>
     </row>
     <row r="9" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="31"/>
-      <c r="B9" s="31"/>
-      <c r="C9" s="31"/>
-      <c r="D9" s="31"/>
-      <c r="E9" s="31"/>
-      <c r="F9" s="32"/>
-      <c r="G9" s="32"/>
-      <c r="H9" s="32"/>
-      <c r="I9" s="32"/>
-      <c r="J9" s="32"/>
+      <c r="A9" s="27"/>
+      <c r="B9" s="27"/>
+      <c r="C9" s="27"/>
+      <c r="D9" s="27"/>
+      <c r="E9" s="27"/>
+      <c r="F9" s="28"/>
+      <c r="G9" s="28"/>
+      <c r="H9" s="28"/>
+      <c r="I9" s="28"/>
+      <c r="J9" s="28"/>
     </row>
     <row r="10" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="31" t="s">
+      <c r="A10" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="B10" s="31"/>
-      <c r="C10" s="31"/>
-      <c r="D10" s="31"/>
-      <c r="E10" s="31"/>
-      <c r="F10" s="32" t="s">
+      <c r="B10" s="27"/>
+      <c r="C10" s="27"/>
+      <c r="D10" s="27"/>
+      <c r="E10" s="27"/>
+      <c r="F10" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="G10" s="32"/>
-      <c r="H10" s="32"/>
-      <c r="I10" s="32"/>
-      <c r="J10" s="32"/>
+      <c r="G10" s="28"/>
+      <c r="H10" s="28"/>
+      <c r="I10" s="28"/>
+      <c r="J10" s="28"/>
     </row>
     <row r="11" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="31"/>
-      <c r="B11" s="31"/>
-      <c r="C11" s="31"/>
-      <c r="D11" s="31"/>
-      <c r="E11" s="31"/>
-      <c r="F11" s="32"/>
-      <c r="G11" s="32"/>
-      <c r="H11" s="32"/>
-      <c r="I11" s="32"/>
-      <c r="J11" s="32"/>
+      <c r="A11" s="27"/>
+      <c r="B11" s="27"/>
+      <c r="C11" s="27"/>
+      <c r="D11" s="27"/>
+      <c r="E11" s="27"/>
+      <c r="F11" s="28"/>
+      <c r="G11" s="28"/>
+      <c r="H11" s="28"/>
+      <c r="I11" s="28"/>
+      <c r="J11" s="28"/>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="10">
     <mergeCell ref="B1:C1"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="G2:H2"/>
     <mergeCell ref="I2:J2"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B6:D6"/>
     <mergeCell ref="A8:E9"/>
     <mergeCell ref="F8:J9"/>
     <mergeCell ref="A10:E11"/>
@@ -5299,94 +5331,96 @@
       <c r="B5" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="C5" s="17"/>
-      <c r="D5" s="18"/>
-      <c r="E5" s="19"/>
-      <c r="F5" s="20"/>
-      <c r="G5" s="20"/>
-      <c r="H5" s="20"/>
-      <c r="I5" s="21"/>
-      <c r="J5" s="22"/>
+      <c r="C5" s="16"/>
+      <c r="D5" s="16"/>
+      <c r="E5" s="17"/>
+      <c r="F5" s="18"/>
+      <c r="G5" s="18"/>
+      <c r="H5" s="18"/>
+      <c r="I5" s="19"/>
+      <c r="J5" s="20"/>
     </row>
     <row r="6" ht="150" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="23" t="s">
+      <c r="A6" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="24" t="s">
+      <c r="B6" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="C6" s="25"/>
-      <c r="D6" s="26"/>
-      <c r="E6" s="27"/>
-      <c r="F6" s="28"/>
-      <c r="G6" s="28"/>
-      <c r="H6" s="28"/>
-      <c r="I6" s="29"/>
-      <c r="J6" s="30"/>
+      <c r="C6" s="22"/>
+      <c r="D6" s="22"/>
+      <c r="E6" s="23"/>
+      <c r="F6" s="24"/>
+      <c r="G6" s="24"/>
+      <c r="H6" s="24"/>
+      <c r="I6" s="25"/>
+      <c r="J6" s="26"/>
     </row>
     <row r="7" ht="78.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="8" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="31" t="s">
+      <c r="A8" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="31"/>
-      <c r="C8" s="31"/>
-      <c r="D8" s="31"/>
-      <c r="E8" s="31"/>
-      <c r="F8" s="32" t="s">
+      <c r="B8" s="27"/>
+      <c r="C8" s="27"/>
+      <c r="D8" s="27"/>
+      <c r="E8" s="27"/>
+      <c r="F8" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="G8" s="32"/>
-      <c r="H8" s="32"/>
-      <c r="I8" s="32"/>
-      <c r="J8" s="32"/>
+      <c r="G8" s="28"/>
+      <c r="H8" s="28"/>
+      <c r="I8" s="28"/>
+      <c r="J8" s="28"/>
     </row>
     <row r="9" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="31"/>
-      <c r="B9" s="31"/>
-      <c r="C9" s="31"/>
-      <c r="D9" s="31"/>
-      <c r="E9" s="31"/>
-      <c r="F9" s="32"/>
-      <c r="G9" s="32"/>
-      <c r="H9" s="32"/>
-      <c r="I9" s="32"/>
-      <c r="J9" s="32"/>
+      <c r="A9" s="27"/>
+      <c r="B9" s="27"/>
+      <c r="C9" s="27"/>
+      <c r="D9" s="27"/>
+      <c r="E9" s="27"/>
+      <c r="F9" s="28"/>
+      <c r="G9" s="28"/>
+      <c r="H9" s="28"/>
+      <c r="I9" s="28"/>
+      <c r="J9" s="28"/>
     </row>
     <row r="10" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="31" t="s">
+      <c r="A10" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="B10" s="31"/>
-      <c r="C10" s="31"/>
-      <c r="D10" s="31"/>
-      <c r="E10" s="31"/>
-      <c r="F10" s="32" t="s">
+      <c r="B10" s="27"/>
+      <c r="C10" s="27"/>
+      <c r="D10" s="27"/>
+      <c r="E10" s="27"/>
+      <c r="F10" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="G10" s="32"/>
-      <c r="H10" s="32"/>
-      <c r="I10" s="32"/>
-      <c r="J10" s="32"/>
+      <c r="G10" s="28"/>
+      <c r="H10" s="28"/>
+      <c r="I10" s="28"/>
+      <c r="J10" s="28"/>
     </row>
     <row r="11" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="31"/>
-      <c r="B11" s="31"/>
-      <c r="C11" s="31"/>
-      <c r="D11" s="31"/>
-      <c r="E11" s="31"/>
-      <c r="F11" s="32"/>
-      <c r="G11" s="32"/>
-      <c r="H11" s="32"/>
-      <c r="I11" s="32"/>
-      <c r="J11" s="32"/>
+      <c r="A11" s="27"/>
+      <c r="B11" s="27"/>
+      <c r="C11" s="27"/>
+      <c r="D11" s="27"/>
+      <c r="E11" s="27"/>
+      <c r="F11" s="28"/>
+      <c r="G11" s="28"/>
+      <c r="H11" s="28"/>
+      <c r="I11" s="28"/>
+      <c r="J11" s="28"/>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="10">
     <mergeCell ref="B1:C1"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="G2:H2"/>
     <mergeCell ref="I2:J2"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B6:D6"/>
     <mergeCell ref="A8:E9"/>
     <mergeCell ref="F8:J9"/>
     <mergeCell ref="A10:E11"/>
@@ -5491,94 +5525,96 @@
       <c r="B5" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="C5" s="17"/>
-      <c r="D5" s="18"/>
-      <c r="E5" s="19"/>
-      <c r="F5" s="20"/>
-      <c r="G5" s="20"/>
-      <c r="H5" s="20"/>
-      <c r="I5" s="21"/>
-      <c r="J5" s="22"/>
+      <c r="C5" s="16"/>
+      <c r="D5" s="16"/>
+      <c r="E5" s="17"/>
+      <c r="F5" s="18"/>
+      <c r="G5" s="18"/>
+      <c r="H5" s="18"/>
+      <c r="I5" s="19"/>
+      <c r="J5" s="20"/>
     </row>
     <row r="6" ht="150" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="23" t="s">
+      <c r="A6" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="24" t="s">
+      <c r="B6" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="C6" s="25"/>
-      <c r="D6" s="26"/>
-      <c r="E6" s="27"/>
-      <c r="F6" s="28"/>
-      <c r="G6" s="28"/>
-      <c r="H6" s="28"/>
-      <c r="I6" s="29"/>
-      <c r="J6" s="30"/>
+      <c r="C6" s="22"/>
+      <c r="D6" s="22"/>
+      <c r="E6" s="23"/>
+      <c r="F6" s="24"/>
+      <c r="G6" s="24"/>
+      <c r="H6" s="24"/>
+      <c r="I6" s="25"/>
+      <c r="J6" s="26"/>
     </row>
     <row r="7" ht="78.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="8" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="31" t="s">
+      <c r="A8" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="31"/>
-      <c r="C8" s="31"/>
-      <c r="D8" s="31"/>
-      <c r="E8" s="31"/>
-      <c r="F8" s="32" t="s">
+      <c r="B8" s="27"/>
+      <c r="C8" s="27"/>
+      <c r="D8" s="27"/>
+      <c r="E8" s="27"/>
+      <c r="F8" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="G8" s="32"/>
-      <c r="H8" s="32"/>
-      <c r="I8" s="32"/>
-      <c r="J8" s="32"/>
+      <c r="G8" s="28"/>
+      <c r="H8" s="28"/>
+      <c r="I8" s="28"/>
+      <c r="J8" s="28"/>
     </row>
     <row r="9" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="31"/>
-      <c r="B9" s="31"/>
-      <c r="C9" s="31"/>
-      <c r="D9" s="31"/>
-      <c r="E9" s="31"/>
-      <c r="F9" s="32"/>
-      <c r="G9" s="32"/>
-      <c r="H9" s="32"/>
-      <c r="I9" s="32"/>
-      <c r="J9" s="32"/>
+      <c r="A9" s="27"/>
+      <c r="B9" s="27"/>
+      <c r="C9" s="27"/>
+      <c r="D9" s="27"/>
+      <c r="E9" s="27"/>
+      <c r="F9" s="28"/>
+      <c r="G9" s="28"/>
+      <c r="H9" s="28"/>
+      <c r="I9" s="28"/>
+      <c r="J9" s="28"/>
     </row>
     <row r="10" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="31" t="s">
+      <c r="A10" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="B10" s="31"/>
-      <c r="C10" s="31"/>
-      <c r="D10" s="31"/>
-      <c r="E10" s="31"/>
-      <c r="F10" s="32" t="s">
+      <c r="B10" s="27"/>
+      <c r="C10" s="27"/>
+      <c r="D10" s="27"/>
+      <c r="E10" s="27"/>
+      <c r="F10" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="G10" s="32"/>
-      <c r="H10" s="32"/>
-      <c r="I10" s="32"/>
-      <c r="J10" s="32"/>
+      <c r="G10" s="28"/>
+      <c r="H10" s="28"/>
+      <c r="I10" s="28"/>
+      <c r="J10" s="28"/>
     </row>
     <row r="11" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="31"/>
-      <c r="B11" s="31"/>
-      <c r="C11" s="31"/>
-      <c r="D11" s="31"/>
-      <c r="E11" s="31"/>
-      <c r="F11" s="32"/>
-      <c r="G11" s="32"/>
-      <c r="H11" s="32"/>
-      <c r="I11" s="32"/>
-      <c r="J11" s="32"/>
+      <c r="A11" s="27"/>
+      <c r="B11" s="27"/>
+      <c r="C11" s="27"/>
+      <c r="D11" s="27"/>
+      <c r="E11" s="27"/>
+      <c r="F11" s="28"/>
+      <c r="G11" s="28"/>
+      <c r="H11" s="28"/>
+      <c r="I11" s="28"/>
+      <c r="J11" s="28"/>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="10">
     <mergeCell ref="B1:C1"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="G2:H2"/>
     <mergeCell ref="I2:J2"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B6:D6"/>
     <mergeCell ref="A8:E9"/>
     <mergeCell ref="F8:J9"/>
     <mergeCell ref="A10:E11"/>
@@ -5683,94 +5719,96 @@
       <c r="B5" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="C5" s="17"/>
-      <c r="D5" s="18"/>
-      <c r="E5" s="19"/>
-      <c r="F5" s="20"/>
-      <c r="G5" s="20"/>
-      <c r="H5" s="20"/>
-      <c r="I5" s="21"/>
-      <c r="J5" s="22"/>
+      <c r="C5" s="16"/>
+      <c r="D5" s="16"/>
+      <c r="E5" s="17"/>
+      <c r="F5" s="18"/>
+      <c r="G5" s="18"/>
+      <c r="H5" s="18"/>
+      <c r="I5" s="19"/>
+      <c r="J5" s="20"/>
     </row>
     <row r="6" ht="150" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="23" t="s">
+      <c r="A6" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="24" t="s">
+      <c r="B6" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="C6" s="25"/>
-      <c r="D6" s="26"/>
-      <c r="E6" s="27"/>
-      <c r="F6" s="28"/>
-      <c r="G6" s="28"/>
-      <c r="H6" s="28"/>
-      <c r="I6" s="29"/>
-      <c r="J6" s="30"/>
+      <c r="C6" s="22"/>
+      <c r="D6" s="22"/>
+      <c r="E6" s="23"/>
+      <c r="F6" s="24"/>
+      <c r="G6" s="24"/>
+      <c r="H6" s="24"/>
+      <c r="I6" s="25"/>
+      <c r="J6" s="26"/>
     </row>
     <row r="7" ht="78.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="8" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="31" t="s">
+      <c r="A8" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="31"/>
-      <c r="C8" s="31"/>
-      <c r="D8" s="31"/>
-      <c r="E8" s="31"/>
-      <c r="F8" s="32" t="s">
+      <c r="B8" s="27"/>
+      <c r="C8" s="27"/>
+      <c r="D8" s="27"/>
+      <c r="E8" s="27"/>
+      <c r="F8" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="G8" s="32"/>
-      <c r="H8" s="32"/>
-      <c r="I8" s="32"/>
-      <c r="J8" s="32"/>
+      <c r="G8" s="28"/>
+      <c r="H8" s="28"/>
+      <c r="I8" s="28"/>
+      <c r="J8" s="28"/>
     </row>
     <row r="9" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="31"/>
-      <c r="B9" s="31"/>
-      <c r="C9" s="31"/>
-      <c r="D9" s="31"/>
-      <c r="E9" s="31"/>
-      <c r="F9" s="32"/>
-      <c r="G9" s="32"/>
-      <c r="H9" s="32"/>
-      <c r="I9" s="32"/>
-      <c r="J9" s="32"/>
+      <c r="A9" s="27"/>
+      <c r="B9" s="27"/>
+      <c r="C9" s="27"/>
+      <c r="D9" s="27"/>
+      <c r="E9" s="27"/>
+      <c r="F9" s="28"/>
+      <c r="G9" s="28"/>
+      <c r="H9" s="28"/>
+      <c r="I9" s="28"/>
+      <c r="J9" s="28"/>
     </row>
     <row r="10" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="31" t="s">
+      <c r="A10" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="B10" s="31"/>
-      <c r="C10" s="31"/>
-      <c r="D10" s="31"/>
-      <c r="E10" s="31"/>
-      <c r="F10" s="32" t="s">
+      <c r="B10" s="27"/>
+      <c r="C10" s="27"/>
+      <c r="D10" s="27"/>
+      <c r="E10" s="27"/>
+      <c r="F10" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="G10" s="32"/>
-      <c r="H10" s="32"/>
-      <c r="I10" s="32"/>
-      <c r="J10" s="32"/>
+      <c r="G10" s="28"/>
+      <c r="H10" s="28"/>
+      <c r="I10" s="28"/>
+      <c r="J10" s="28"/>
     </row>
     <row r="11" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="31"/>
-      <c r="B11" s="31"/>
-      <c r="C11" s="31"/>
-      <c r="D11" s="31"/>
-      <c r="E11" s="31"/>
-      <c r="F11" s="32"/>
-      <c r="G11" s="32"/>
-      <c r="H11" s="32"/>
-      <c r="I11" s="32"/>
-      <c r="J11" s="32"/>
+      <c r="A11" s="27"/>
+      <c r="B11" s="27"/>
+      <c r="C11" s="27"/>
+      <c r="D11" s="27"/>
+      <c r="E11" s="27"/>
+      <c r="F11" s="28"/>
+      <c r="G11" s="28"/>
+      <c r="H11" s="28"/>
+      <c r="I11" s="28"/>
+      <c r="J11" s="28"/>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="10">
     <mergeCell ref="B1:C1"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="G2:H2"/>
     <mergeCell ref="I2:J2"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B6:D6"/>
     <mergeCell ref="A8:E9"/>
     <mergeCell ref="F8:J9"/>
     <mergeCell ref="A10:E11"/>
@@ -5797,29 +5835,21 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
+      <c r="B1" s="2"/>
       <c r="C1" s="2"/>
       <c r="D1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="4">
-        <v>1</v>
-      </c>
+      <c r="E1" s="4"/>
       <c r="F1" s="5"/>
       <c r="G1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>19</v>
-      </c>
+      <c r="H1" s="1"/>
       <c r="I1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="J1" s="6" t="s">
-        <v>19</v>
-      </c>
+      <c r="J1" s="6"/>
     </row>
     <row r="2" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
@@ -5834,9 +5864,7 @@
         <v>8</v>
       </c>
       <c r="H2" s="7"/>
-      <c r="I2" s="7" t="s">
-        <v>51</v>
-      </c>
+      <c r="I2" s="7"/>
       <c r="J2" s="7"/>
     </row>
     <row r="3" ht="78.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -5872,90 +5900,86 @@
       <c r="A5" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="C5" s="17"/>
-      <c r="D5" s="18"/>
-      <c r="E5" s="19"/>
-      <c r="F5" s="20"/>
-      <c r="G5" s="20"/>
-      <c r="H5" s="20"/>
-      <c r="I5" s="21"/>
-      <c r="J5" s="22"/>
+      <c r="B5" s="29"/>
+      <c r="C5" s="30"/>
+      <c r="D5" s="31"/>
+      <c r="E5" s="17"/>
+      <c r="F5" s="18"/>
+      <c r="G5" s="18"/>
+      <c r="H5" s="18"/>
+      <c r="I5" s="19"/>
+      <c r="J5" s="20"/>
     </row>
     <row r="6" ht="150" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="23" t="s">
+      <c r="A6" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="24" t="s">
-        <v>19</v>
-      </c>
-      <c r="C6" s="25"/>
-      <c r="D6" s="26"/>
-      <c r="E6" s="27"/>
-      <c r="F6" s="28"/>
-      <c r="G6" s="28"/>
-      <c r="H6" s="28"/>
-      <c r="I6" s="29"/>
-      <c r="J6" s="30"/>
+      <c r="B6" s="32"/>
+      <c r="C6" s="33"/>
+      <c r="D6" s="34"/>
+      <c r="E6" s="23"/>
+      <c r="F6" s="24"/>
+      <c r="G6" s="24"/>
+      <c r="H6" s="24"/>
+      <c r="I6" s="25"/>
+      <c r="J6" s="26"/>
     </row>
     <row r="7" ht="78.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="8" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="31" t="s">
+      <c r="A8" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="31"/>
-      <c r="C8" s="31"/>
-      <c r="D8" s="31"/>
-      <c r="E8" s="31"/>
-      <c r="F8" s="32" t="s">
+      <c r="B8" s="27"/>
+      <c r="C8" s="27"/>
+      <c r="D8" s="27"/>
+      <c r="E8" s="27"/>
+      <c r="F8" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="G8" s="32"/>
-      <c r="H8" s="32"/>
-      <c r="I8" s="32"/>
-      <c r="J8" s="32"/>
+      <c r="G8" s="28"/>
+      <c r="H8" s="28"/>
+      <c r="I8" s="28"/>
+      <c r="J8" s="28"/>
     </row>
     <row r="9" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="31"/>
-      <c r="B9" s="31"/>
-      <c r="C9" s="31"/>
-      <c r="D9" s="31"/>
-      <c r="E9" s="31"/>
-      <c r="F9" s="32"/>
-      <c r="G9" s="32"/>
-      <c r="H9" s="32"/>
-      <c r="I9" s="32"/>
-      <c r="J9" s="32"/>
+      <c r="A9" s="27"/>
+      <c r="B9" s="27"/>
+      <c r="C9" s="27"/>
+      <c r="D9" s="27"/>
+      <c r="E9" s="27"/>
+      <c r="F9" s="28"/>
+      <c r="G9" s="28"/>
+      <c r="H9" s="28"/>
+      <c r="I9" s="28"/>
+      <c r="J9" s="28"/>
     </row>
     <row r="10" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="31" t="s">
+      <c r="A10" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="B10" s="31"/>
-      <c r="C10" s="31"/>
-      <c r="D10" s="31"/>
-      <c r="E10" s="31"/>
-      <c r="F10" s="32" t="s">
+      <c r="B10" s="27"/>
+      <c r="C10" s="27"/>
+      <c r="D10" s="27"/>
+      <c r="E10" s="27"/>
+      <c r="F10" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="G10" s="32"/>
-      <c r="H10" s="32"/>
-      <c r="I10" s="32"/>
-      <c r="J10" s="32"/>
+      <c r="G10" s="28"/>
+      <c r="H10" s="28"/>
+      <c r="I10" s="28"/>
+      <c r="J10" s="28"/>
     </row>
     <row r="11" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="31"/>
-      <c r="B11" s="31"/>
-      <c r="C11" s="31"/>
-      <c r="D11" s="31"/>
-      <c r="E11" s="31"/>
-      <c r="F11" s="32"/>
-      <c r="G11" s="32"/>
-      <c r="H11" s="32"/>
-      <c r="I11" s="32"/>
-      <c r="J11" s="32"/>
+      <c r="A11" s="27"/>
+      <c r="B11" s="27"/>
+      <c r="C11" s="27"/>
+      <c r="D11" s="27"/>
+      <c r="E11" s="27"/>
+      <c r="F11" s="28"/>
+      <c r="G11" s="28"/>
+      <c r="H11" s="28"/>
+      <c r="I11" s="28"/>
+      <c r="J11" s="28"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -5989,29 +6013,21 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
+      <c r="B1" s="2"/>
       <c r="C1" s="2"/>
       <c r="D1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="4">
-        <v>2</v>
-      </c>
+      <c r="E1" s="4"/>
       <c r="F1" s="5"/>
       <c r="G1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>19</v>
-      </c>
+      <c r="H1" s="1"/>
       <c r="I1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="J1" s="6" t="s">
-        <v>19</v>
-      </c>
+      <c r="J1" s="6"/>
     </row>
     <row r="2" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
@@ -6026,9 +6042,7 @@
         <v>8</v>
       </c>
       <c r="H2" s="7"/>
-      <c r="I2" s="7" t="s">
-        <v>51</v>
-      </c>
+      <c r="I2" s="7"/>
       <c r="J2" s="7"/>
     </row>
     <row r="3" ht="78.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -6064,90 +6078,86 @@
       <c r="A5" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="C5" s="17"/>
-      <c r="D5" s="18"/>
-      <c r="E5" s="19"/>
-      <c r="F5" s="20"/>
-      <c r="G5" s="20"/>
-      <c r="H5" s="20"/>
-      <c r="I5" s="21"/>
-      <c r="J5" s="22"/>
+      <c r="B5" s="29"/>
+      <c r="C5" s="30"/>
+      <c r="D5" s="31"/>
+      <c r="E5" s="17"/>
+      <c r="F5" s="18"/>
+      <c r="G5" s="18"/>
+      <c r="H5" s="18"/>
+      <c r="I5" s="19"/>
+      <c r="J5" s="20"/>
     </row>
     <row r="6" ht="150" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="23" t="s">
+      <c r="A6" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="24" t="s">
-        <v>19</v>
-      </c>
-      <c r="C6" s="25"/>
-      <c r="D6" s="26"/>
-      <c r="E6" s="27"/>
-      <c r="F6" s="28"/>
-      <c r="G6" s="28"/>
-      <c r="H6" s="28"/>
-      <c r="I6" s="29"/>
-      <c r="J6" s="30"/>
+      <c r="B6" s="32"/>
+      <c r="C6" s="33"/>
+      <c r="D6" s="34"/>
+      <c r="E6" s="23"/>
+      <c r="F6" s="24"/>
+      <c r="G6" s="24"/>
+      <c r="H6" s="24"/>
+      <c r="I6" s="25"/>
+      <c r="J6" s="26"/>
     </row>
     <row r="7" ht="78.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="8" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="31" t="s">
+      <c r="A8" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="31"/>
-      <c r="C8" s="31"/>
-      <c r="D8" s="31"/>
-      <c r="E8" s="31"/>
-      <c r="F8" s="32" t="s">
+      <c r="B8" s="27"/>
+      <c r="C8" s="27"/>
+      <c r="D8" s="27"/>
+      <c r="E8" s="27"/>
+      <c r="F8" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="G8" s="32"/>
-      <c r="H8" s="32"/>
-      <c r="I8" s="32"/>
-      <c r="J8" s="32"/>
+      <c r="G8" s="28"/>
+      <c r="H8" s="28"/>
+      <c r="I8" s="28"/>
+      <c r="J8" s="28"/>
     </row>
     <row r="9" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="31"/>
-      <c r="B9" s="31"/>
-      <c r="C9" s="31"/>
-      <c r="D9" s="31"/>
-      <c r="E9" s="31"/>
-      <c r="F9" s="32"/>
-      <c r="G9" s="32"/>
-      <c r="H9" s="32"/>
-      <c r="I9" s="32"/>
-      <c r="J9" s="32"/>
+      <c r="A9" s="27"/>
+      <c r="B9" s="27"/>
+      <c r="C9" s="27"/>
+      <c r="D9" s="27"/>
+      <c r="E9" s="27"/>
+      <c r="F9" s="28"/>
+      <c r="G9" s="28"/>
+      <c r="H9" s="28"/>
+      <c r="I9" s="28"/>
+      <c r="J9" s="28"/>
     </row>
     <row r="10" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="31" t="s">
+      <c r="A10" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="B10" s="31"/>
-      <c r="C10" s="31"/>
-      <c r="D10" s="31"/>
-      <c r="E10" s="31"/>
-      <c r="F10" s="32" t="s">
+      <c r="B10" s="27"/>
+      <c r="C10" s="27"/>
+      <c r="D10" s="27"/>
+      <c r="E10" s="27"/>
+      <c r="F10" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="G10" s="32"/>
-      <c r="H10" s="32"/>
-      <c r="I10" s="32"/>
-      <c r="J10" s="32"/>
+      <c r="G10" s="28"/>
+      <c r="H10" s="28"/>
+      <c r="I10" s="28"/>
+      <c r="J10" s="28"/>
     </row>
     <row r="11" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="31"/>
-      <c r="B11" s="31"/>
-      <c r="C11" s="31"/>
-      <c r="D11" s="31"/>
-      <c r="E11" s="31"/>
-      <c r="F11" s="32"/>
-      <c r="G11" s="32"/>
-      <c r="H11" s="32"/>
-      <c r="I11" s="32"/>
-      <c r="J11" s="32"/>
+      <c r="A11" s="27"/>
+      <c r="B11" s="27"/>
+      <c r="C11" s="27"/>
+      <c r="D11" s="27"/>
+      <c r="E11" s="27"/>
+      <c r="F11" s="28"/>
+      <c r="G11" s="28"/>
+      <c r="H11" s="28"/>
+      <c r="I11" s="28"/>
+      <c r="J11" s="28"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -6181,29 +6191,21 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
+      <c r="B1" s="2"/>
       <c r="C1" s="2"/>
       <c r="D1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="4">
-        <v>3</v>
-      </c>
+      <c r="E1" s="4"/>
       <c r="F1" s="5"/>
       <c r="G1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>19</v>
-      </c>
+      <c r="H1" s="1"/>
       <c r="I1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="J1" s="6" t="s">
-        <v>19</v>
-      </c>
+      <c r="J1" s="6"/>
     </row>
     <row r="2" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
@@ -6218,9 +6220,7 @@
         <v>8</v>
       </c>
       <c r="H2" s="7"/>
-      <c r="I2" s="7" t="s">
-        <v>51</v>
-      </c>
+      <c r="I2" s="7"/>
       <c r="J2" s="7"/>
     </row>
     <row r="3" ht="78.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -6256,90 +6256,86 @@
       <c r="A5" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="C5" s="17"/>
-      <c r="D5" s="18"/>
-      <c r="E5" s="19"/>
-      <c r="F5" s="20"/>
-      <c r="G5" s="20"/>
-      <c r="H5" s="20"/>
-      <c r="I5" s="21"/>
-      <c r="J5" s="22"/>
+      <c r="B5" s="29"/>
+      <c r="C5" s="30"/>
+      <c r="D5" s="31"/>
+      <c r="E5" s="17"/>
+      <c r="F5" s="18"/>
+      <c r="G5" s="18"/>
+      <c r="H5" s="18"/>
+      <c r="I5" s="19"/>
+      <c r="J5" s="20"/>
     </row>
     <row r="6" ht="150" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="23" t="s">
+      <c r="A6" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="24" t="s">
-        <v>19</v>
-      </c>
-      <c r="C6" s="25"/>
-      <c r="D6" s="26"/>
-      <c r="E6" s="27"/>
-      <c r="F6" s="28"/>
-      <c r="G6" s="28"/>
-      <c r="H6" s="28"/>
-      <c r="I6" s="29"/>
-      <c r="J6" s="30"/>
+      <c r="B6" s="32"/>
+      <c r="C6" s="33"/>
+      <c r="D6" s="34"/>
+      <c r="E6" s="23"/>
+      <c r="F6" s="24"/>
+      <c r="G6" s="24"/>
+      <c r="H6" s="24"/>
+      <c r="I6" s="25"/>
+      <c r="J6" s="26"/>
     </row>
     <row r="7" ht="78.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="8" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="31" t="s">
+      <c r="A8" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="31"/>
-      <c r="C8" s="31"/>
-      <c r="D8" s="31"/>
-      <c r="E8" s="31"/>
-      <c r="F8" s="32" t="s">
+      <c r="B8" s="27"/>
+      <c r="C8" s="27"/>
+      <c r="D8" s="27"/>
+      <c r="E8" s="27"/>
+      <c r="F8" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="G8" s="32"/>
-      <c r="H8" s="32"/>
-      <c r="I8" s="32"/>
-      <c r="J8" s="32"/>
+      <c r="G8" s="28"/>
+      <c r="H8" s="28"/>
+      <c r="I8" s="28"/>
+      <c r="J8" s="28"/>
     </row>
     <row r="9" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="31"/>
-      <c r="B9" s="31"/>
-      <c r="C9" s="31"/>
-      <c r="D9" s="31"/>
-      <c r="E9" s="31"/>
-      <c r="F9" s="32"/>
-      <c r="G9" s="32"/>
-      <c r="H9" s="32"/>
-      <c r="I9" s="32"/>
-      <c r="J9" s="32"/>
+      <c r="A9" s="27"/>
+      <c r="B9" s="27"/>
+      <c r="C9" s="27"/>
+      <c r="D9" s="27"/>
+      <c r="E9" s="27"/>
+      <c r="F9" s="28"/>
+      <c r="G9" s="28"/>
+      <c r="H9" s="28"/>
+      <c r="I9" s="28"/>
+      <c r="J9" s="28"/>
     </row>
     <row r="10" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="31" t="s">
+      <c r="A10" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="B10" s="31"/>
-      <c r="C10" s="31"/>
-      <c r="D10" s="31"/>
-      <c r="E10" s="31"/>
-      <c r="F10" s="32" t="s">
+      <c r="B10" s="27"/>
+      <c r="C10" s="27"/>
+      <c r="D10" s="27"/>
+      <c r="E10" s="27"/>
+      <c r="F10" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="G10" s="32"/>
-      <c r="H10" s="32"/>
-      <c r="I10" s="32"/>
-      <c r="J10" s="32"/>
+      <c r="G10" s="28"/>
+      <c r="H10" s="28"/>
+      <c r="I10" s="28"/>
+      <c r="J10" s="28"/>
     </row>
     <row r="11" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="31"/>
-      <c r="B11" s="31"/>
-      <c r="C11" s="31"/>
-      <c r="D11" s="31"/>
-      <c r="E11" s="31"/>
-      <c r="F11" s="32"/>
-      <c r="G11" s="32"/>
-      <c r="H11" s="32"/>
-      <c r="I11" s="32"/>
-      <c r="J11" s="32"/>
+      <c r="A11" s="27"/>
+      <c r="B11" s="27"/>
+      <c r="C11" s="27"/>
+      <c r="D11" s="27"/>
+      <c r="E11" s="27"/>
+      <c r="F11" s="28"/>
+      <c r="G11" s="28"/>
+      <c r="H11" s="28"/>
+      <c r="I11" s="28"/>
+      <c r="J11" s="28"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -6373,29 +6369,21 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
+      <c r="B1" s="2"/>
       <c r="C1" s="2"/>
       <c r="D1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="4">
-        <v>4</v>
-      </c>
+      <c r="E1" s="4"/>
       <c r="F1" s="5"/>
       <c r="G1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>19</v>
-      </c>
+      <c r="H1" s="1"/>
       <c r="I1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="J1" s="6" t="s">
-        <v>19</v>
-      </c>
+      <c r="J1" s="6"/>
     </row>
     <row r="2" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
@@ -6410,9 +6398,7 @@
         <v>8</v>
       </c>
       <c r="H2" s="7"/>
-      <c r="I2" s="7" t="s">
-        <v>51</v>
-      </c>
+      <c r="I2" s="7"/>
       <c r="J2" s="7"/>
     </row>
     <row r="3" ht="78.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -6448,90 +6434,86 @@
       <c r="A5" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="C5" s="17"/>
-      <c r="D5" s="18"/>
-      <c r="E5" s="19"/>
-      <c r="F5" s="20"/>
-      <c r="G5" s="20"/>
-      <c r="H5" s="20"/>
-      <c r="I5" s="21"/>
-      <c r="J5" s="22"/>
+      <c r="B5" s="29"/>
+      <c r="C5" s="30"/>
+      <c r="D5" s="31"/>
+      <c r="E5" s="17"/>
+      <c r="F5" s="18"/>
+      <c r="G5" s="18"/>
+      <c r="H5" s="18"/>
+      <c r="I5" s="19"/>
+      <c r="J5" s="20"/>
     </row>
     <row r="6" ht="150" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="23" t="s">
+      <c r="A6" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="24" t="s">
-        <v>19</v>
-      </c>
-      <c r="C6" s="25"/>
-      <c r="D6" s="26"/>
-      <c r="E6" s="27"/>
-      <c r="F6" s="28"/>
-      <c r="G6" s="28"/>
-      <c r="H6" s="28"/>
-      <c r="I6" s="29"/>
-      <c r="J6" s="30"/>
+      <c r="B6" s="32"/>
+      <c r="C6" s="33"/>
+      <c r="D6" s="34"/>
+      <c r="E6" s="23"/>
+      <c r="F6" s="24"/>
+      <c r="G6" s="24"/>
+      <c r="H6" s="24"/>
+      <c r="I6" s="25"/>
+      <c r="J6" s="26"/>
     </row>
     <row r="7" ht="78.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="8" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="31" t="s">
+      <c r="A8" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="31"/>
-      <c r="C8" s="31"/>
-      <c r="D8" s="31"/>
-      <c r="E8" s="31"/>
-      <c r="F8" s="32" t="s">
+      <c r="B8" s="27"/>
+      <c r="C8" s="27"/>
+      <c r="D8" s="27"/>
+      <c r="E8" s="27"/>
+      <c r="F8" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="G8" s="32"/>
-      <c r="H8" s="32"/>
-      <c r="I8" s="32"/>
-      <c r="J8" s="32"/>
+      <c r="G8" s="28"/>
+      <c r="H8" s="28"/>
+      <c r="I8" s="28"/>
+      <c r="J8" s="28"/>
     </row>
     <row r="9" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="31"/>
-      <c r="B9" s="31"/>
-      <c r="C9" s="31"/>
-      <c r="D9" s="31"/>
-      <c r="E9" s="31"/>
-      <c r="F9" s="32"/>
-      <c r="G9" s="32"/>
-      <c r="H9" s="32"/>
-      <c r="I9" s="32"/>
-      <c r="J9" s="32"/>
+      <c r="A9" s="27"/>
+      <c r="B9" s="27"/>
+      <c r="C9" s="27"/>
+      <c r="D9" s="27"/>
+      <c r="E9" s="27"/>
+      <c r="F9" s="28"/>
+      <c r="G9" s="28"/>
+      <c r="H9" s="28"/>
+      <c r="I9" s="28"/>
+      <c r="J9" s="28"/>
     </row>
     <row r="10" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="31" t="s">
+      <c r="A10" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="B10" s="31"/>
-      <c r="C10" s="31"/>
-      <c r="D10" s="31"/>
-      <c r="E10" s="31"/>
-      <c r="F10" s="32" t="s">
+      <c r="B10" s="27"/>
+      <c r="C10" s="27"/>
+      <c r="D10" s="27"/>
+      <c r="E10" s="27"/>
+      <c r="F10" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="G10" s="32"/>
-      <c r="H10" s="32"/>
-      <c r="I10" s="32"/>
-      <c r="J10" s="32"/>
+      <c r="G10" s="28"/>
+      <c r="H10" s="28"/>
+      <c r="I10" s="28"/>
+      <c r="J10" s="28"/>
     </row>
     <row r="11" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="31"/>
-      <c r="B11" s="31"/>
-      <c r="C11" s="31"/>
-      <c r="D11" s="31"/>
-      <c r="E11" s="31"/>
-      <c r="F11" s="32"/>
-      <c r="G11" s="32"/>
-      <c r="H11" s="32"/>
-      <c r="I11" s="32"/>
-      <c r="J11" s="32"/>
+      <c r="A11" s="27"/>
+      <c r="B11" s="27"/>
+      <c r="C11" s="27"/>
+      <c r="D11" s="27"/>
+      <c r="E11" s="27"/>
+      <c r="F11" s="28"/>
+      <c r="G11" s="28"/>
+      <c r="H11" s="28"/>
+      <c r="I11" s="28"/>
+      <c r="J11" s="28"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -6565,29 +6547,21 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
+      <c r="B1" s="2"/>
       <c r="C1" s="2"/>
       <c r="D1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="4">
-        <v>5</v>
-      </c>
+      <c r="E1" s="4"/>
       <c r="F1" s="5"/>
       <c r="G1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>19</v>
-      </c>
+      <c r="H1" s="1"/>
       <c r="I1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="J1" s="6" t="s">
-        <v>19</v>
-      </c>
+      <c r="J1" s="6"/>
     </row>
     <row r="2" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
@@ -6602,9 +6576,7 @@
         <v>8</v>
       </c>
       <c r="H2" s="7"/>
-      <c r="I2" s="7" t="s">
-        <v>51</v>
-      </c>
+      <c r="I2" s="7"/>
       <c r="J2" s="7"/>
     </row>
     <row r="3" ht="78.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -6640,90 +6612,86 @@
       <c r="A5" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="C5" s="17"/>
-      <c r="D5" s="18"/>
-      <c r="E5" s="19"/>
-      <c r="F5" s="20"/>
-      <c r="G5" s="20"/>
-      <c r="H5" s="20"/>
-      <c r="I5" s="21"/>
-      <c r="J5" s="22"/>
+      <c r="B5" s="29"/>
+      <c r="C5" s="30"/>
+      <c r="D5" s="31"/>
+      <c r="E5" s="17"/>
+      <c r="F5" s="18"/>
+      <c r="G5" s="18"/>
+      <c r="H5" s="18"/>
+      <c r="I5" s="19"/>
+      <c r="J5" s="20"/>
     </row>
     <row r="6" ht="150" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="23" t="s">
+      <c r="A6" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="24" t="s">
-        <v>19</v>
-      </c>
-      <c r="C6" s="25"/>
-      <c r="D6" s="26"/>
-      <c r="E6" s="27"/>
-      <c r="F6" s="28"/>
-      <c r="G6" s="28"/>
-      <c r="H6" s="28"/>
-      <c r="I6" s="29"/>
-      <c r="J6" s="30"/>
+      <c r="B6" s="32"/>
+      <c r="C6" s="33"/>
+      <c r="D6" s="34"/>
+      <c r="E6" s="23"/>
+      <c r="F6" s="24"/>
+      <c r="G6" s="24"/>
+      <c r="H6" s="24"/>
+      <c r="I6" s="25"/>
+      <c r="J6" s="26"/>
     </row>
     <row r="7" ht="78.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="8" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="31" t="s">
+      <c r="A8" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="31"/>
-      <c r="C8" s="31"/>
-      <c r="D8" s="31"/>
-      <c r="E8" s="31"/>
-      <c r="F8" s="32" t="s">
+      <c r="B8" s="27"/>
+      <c r="C8" s="27"/>
+      <c r="D8" s="27"/>
+      <c r="E8" s="27"/>
+      <c r="F8" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="G8" s="32"/>
-      <c r="H8" s="32"/>
-      <c r="I8" s="32"/>
-      <c r="J8" s="32"/>
+      <c r="G8" s="28"/>
+      <c r="H8" s="28"/>
+      <c r="I8" s="28"/>
+      <c r="J8" s="28"/>
     </row>
     <row r="9" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="31"/>
-      <c r="B9" s="31"/>
-      <c r="C9" s="31"/>
-      <c r="D9" s="31"/>
-      <c r="E9" s="31"/>
-      <c r="F9" s="32"/>
-      <c r="G9" s="32"/>
-      <c r="H9" s="32"/>
-      <c r="I9" s="32"/>
-      <c r="J9" s="32"/>
+      <c r="A9" s="27"/>
+      <c r="B9" s="27"/>
+      <c r="C9" s="27"/>
+      <c r="D9" s="27"/>
+      <c r="E9" s="27"/>
+      <c r="F9" s="28"/>
+      <c r="G9" s="28"/>
+      <c r="H9" s="28"/>
+      <c r="I9" s="28"/>
+      <c r="J9" s="28"/>
     </row>
     <row r="10" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="31" t="s">
+      <c r="A10" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="B10" s="31"/>
-      <c r="C10" s="31"/>
-      <c r="D10" s="31"/>
-      <c r="E10" s="31"/>
-      <c r="F10" s="32" t="s">
+      <c r="B10" s="27"/>
+      <c r="C10" s="27"/>
+      <c r="D10" s="27"/>
+      <c r="E10" s="27"/>
+      <c r="F10" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="G10" s="32"/>
-      <c r="H10" s="32"/>
-      <c r="I10" s="32"/>
-      <c r="J10" s="32"/>
+      <c r="G10" s="28"/>
+      <c r="H10" s="28"/>
+      <c r="I10" s="28"/>
+      <c r="J10" s="28"/>
     </row>
     <row r="11" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="31"/>
-      <c r="B11" s="31"/>
-      <c r="C11" s="31"/>
-      <c r="D11" s="31"/>
-      <c r="E11" s="31"/>
-      <c r="F11" s="32"/>
-      <c r="G11" s="32"/>
-      <c r="H11" s="32"/>
-      <c r="I11" s="32"/>
-      <c r="J11" s="32"/>
+      <c r="A11" s="27"/>
+      <c r="B11" s="27"/>
+      <c r="C11" s="27"/>
+      <c r="D11" s="27"/>
+      <c r="E11" s="27"/>
+      <c r="F11" s="28"/>
+      <c r="G11" s="28"/>
+      <c r="H11" s="28"/>
+      <c r="I11" s="28"/>
+      <c r="J11" s="28"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -6757,29 +6725,21 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
+      <c r="B1" s="2"/>
       <c r="C1" s="2"/>
       <c r="D1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="4">
-        <v>6</v>
-      </c>
+      <c r="E1" s="4"/>
       <c r="F1" s="5"/>
       <c r="G1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>19</v>
-      </c>
+      <c r="H1" s="1"/>
       <c r="I1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="J1" s="6" t="s">
-        <v>19</v>
-      </c>
+      <c r="J1" s="6"/>
     </row>
     <row r="2" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
@@ -6794,9 +6754,7 @@
         <v>8</v>
       </c>
       <c r="H2" s="7"/>
-      <c r="I2" s="7" t="s">
-        <v>51</v>
-      </c>
+      <c r="I2" s="7"/>
       <c r="J2" s="7"/>
     </row>
     <row r="3" ht="78.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -6832,90 +6790,86 @@
       <c r="A5" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="C5" s="17"/>
-      <c r="D5" s="18"/>
-      <c r="E5" s="19"/>
-      <c r="F5" s="20"/>
-      <c r="G5" s="20"/>
-      <c r="H5" s="20"/>
-      <c r="I5" s="21"/>
-      <c r="J5" s="22"/>
+      <c r="B5" s="29"/>
+      <c r="C5" s="30"/>
+      <c r="D5" s="31"/>
+      <c r="E5" s="17"/>
+      <c r="F5" s="18"/>
+      <c r="G5" s="18"/>
+      <c r="H5" s="18"/>
+      <c r="I5" s="19"/>
+      <c r="J5" s="20"/>
     </row>
     <row r="6" ht="150" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="23" t="s">
+      <c r="A6" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="24" t="s">
-        <v>19</v>
-      </c>
-      <c r="C6" s="25"/>
-      <c r="D6" s="26"/>
-      <c r="E6" s="27"/>
-      <c r="F6" s="28"/>
-      <c r="G6" s="28"/>
-      <c r="H6" s="28"/>
-      <c r="I6" s="29"/>
-      <c r="J6" s="30"/>
+      <c r="B6" s="32"/>
+      <c r="C6" s="33"/>
+      <c r="D6" s="34"/>
+      <c r="E6" s="23"/>
+      <c r="F6" s="24"/>
+      <c r="G6" s="24"/>
+      <c r="H6" s="24"/>
+      <c r="I6" s="25"/>
+      <c r="J6" s="26"/>
     </row>
     <row r="7" ht="78.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="8" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="31" t="s">
+      <c r="A8" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="31"/>
-      <c r="C8" s="31"/>
-      <c r="D8" s="31"/>
-      <c r="E8" s="31"/>
-      <c r="F8" s="32" t="s">
+      <c r="B8" s="27"/>
+      <c r="C8" s="27"/>
+      <c r="D8" s="27"/>
+      <c r="E8" s="27"/>
+      <c r="F8" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="G8" s="32"/>
-      <c r="H8" s="32"/>
-      <c r="I8" s="32"/>
-      <c r="J8" s="32"/>
+      <c r="G8" s="28"/>
+      <c r="H8" s="28"/>
+      <c r="I8" s="28"/>
+      <c r="J8" s="28"/>
     </row>
     <row r="9" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="31"/>
-      <c r="B9" s="31"/>
-      <c r="C9" s="31"/>
-      <c r="D9" s="31"/>
-      <c r="E9" s="31"/>
-      <c r="F9" s="32"/>
-      <c r="G9" s="32"/>
-      <c r="H9" s="32"/>
-      <c r="I9" s="32"/>
-      <c r="J9" s="32"/>
+      <c r="A9" s="27"/>
+      <c r="B9" s="27"/>
+      <c r="C9" s="27"/>
+      <c r="D9" s="27"/>
+      <c r="E9" s="27"/>
+      <c r="F9" s="28"/>
+      <c r="G9" s="28"/>
+      <c r="H9" s="28"/>
+      <c r="I9" s="28"/>
+      <c r="J9" s="28"/>
     </row>
     <row r="10" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="31" t="s">
+      <c r="A10" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="B10" s="31"/>
-      <c r="C10" s="31"/>
-      <c r="D10" s="31"/>
-      <c r="E10" s="31"/>
-      <c r="F10" s="32" t="s">
+      <c r="B10" s="27"/>
+      <c r="C10" s="27"/>
+      <c r="D10" s="27"/>
+      <c r="E10" s="27"/>
+      <c r="F10" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="G10" s="32"/>
-      <c r="H10" s="32"/>
-      <c r="I10" s="32"/>
-      <c r="J10" s="32"/>
+      <c r="G10" s="28"/>
+      <c r="H10" s="28"/>
+      <c r="I10" s="28"/>
+      <c r="J10" s="28"/>
     </row>
     <row r="11" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="31"/>
-      <c r="B11" s="31"/>
-      <c r="C11" s="31"/>
-      <c r="D11" s="31"/>
-      <c r="E11" s="31"/>
-      <c r="F11" s="32"/>
-      <c r="G11" s="32"/>
-      <c r="H11" s="32"/>
-      <c r="I11" s="32"/>
-      <c r="J11" s="32"/>
+      <c r="A11" s="27"/>
+      <c r="B11" s="27"/>
+      <c r="C11" s="27"/>
+      <c r="D11" s="27"/>
+      <c r="E11" s="27"/>
+      <c r="F11" s="28"/>
+      <c r="G11" s="28"/>
+      <c r="H11" s="28"/>
+      <c r="I11" s="28"/>
+      <c r="J11" s="28"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -6949,29 +6903,21 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
+      <c r="B1" s="2"/>
       <c r="C1" s="2"/>
       <c r="D1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="4">
-        <v>7</v>
-      </c>
+      <c r="E1" s="4"/>
       <c r="F1" s="5"/>
       <c r="G1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>19</v>
-      </c>
+      <c r="H1" s="1"/>
       <c r="I1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="J1" s="6" t="s">
-        <v>19</v>
-      </c>
+      <c r="J1" s="6"/>
     </row>
     <row r="2" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
@@ -6986,9 +6932,7 @@
         <v>8</v>
       </c>
       <c r="H2" s="7"/>
-      <c r="I2" s="7" t="s">
-        <v>51</v>
-      </c>
+      <c r="I2" s="7"/>
       <c r="J2" s="7"/>
     </row>
     <row r="3" ht="78.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -7024,90 +6968,86 @@
       <c r="A5" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="C5" s="17"/>
-      <c r="D5" s="18"/>
-      <c r="E5" s="19"/>
-      <c r="F5" s="20"/>
-      <c r="G5" s="20"/>
-      <c r="H5" s="20"/>
-      <c r="I5" s="21"/>
-      <c r="J5" s="22"/>
+      <c r="B5" s="29"/>
+      <c r="C5" s="30"/>
+      <c r="D5" s="31"/>
+      <c r="E5" s="17"/>
+      <c r="F5" s="18"/>
+      <c r="G5" s="18"/>
+      <c r="H5" s="18"/>
+      <c r="I5" s="19"/>
+      <c r="J5" s="20"/>
     </row>
     <row r="6" ht="150" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="23" t="s">
+      <c r="A6" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="24" t="s">
-        <v>19</v>
-      </c>
-      <c r="C6" s="25"/>
-      <c r="D6" s="26"/>
-      <c r="E6" s="27"/>
-      <c r="F6" s="28"/>
-      <c r="G6" s="28"/>
-      <c r="H6" s="28"/>
-      <c r="I6" s="29"/>
-      <c r="J6" s="30"/>
+      <c r="B6" s="32"/>
+      <c r="C6" s="33"/>
+      <c r="D6" s="34"/>
+      <c r="E6" s="23"/>
+      <c r="F6" s="24"/>
+      <c r="G6" s="24"/>
+      <c r="H6" s="24"/>
+      <c r="I6" s="25"/>
+      <c r="J6" s="26"/>
     </row>
     <row r="7" ht="78.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="8" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="31" t="s">
+      <c r="A8" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="31"/>
-      <c r="C8" s="31"/>
-      <c r="D8" s="31"/>
-      <c r="E8" s="31"/>
-      <c r="F8" s="32" t="s">
+      <c r="B8" s="27"/>
+      <c r="C8" s="27"/>
+      <c r="D8" s="27"/>
+      <c r="E8" s="27"/>
+      <c r="F8" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="G8" s="32"/>
-      <c r="H8" s="32"/>
-      <c r="I8" s="32"/>
-      <c r="J8" s="32"/>
+      <c r="G8" s="28"/>
+      <c r="H8" s="28"/>
+      <c r="I8" s="28"/>
+      <c r="J8" s="28"/>
     </row>
     <row r="9" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="31"/>
-      <c r="B9" s="31"/>
-      <c r="C9" s="31"/>
-      <c r="D9" s="31"/>
-      <c r="E9" s="31"/>
-      <c r="F9" s="32"/>
-      <c r="G9" s="32"/>
-      <c r="H9" s="32"/>
-      <c r="I9" s="32"/>
-      <c r="J9" s="32"/>
+      <c r="A9" s="27"/>
+      <c r="B9" s="27"/>
+      <c r="C9" s="27"/>
+      <c r="D9" s="27"/>
+      <c r="E9" s="27"/>
+      <c r="F9" s="28"/>
+      <c r="G9" s="28"/>
+      <c r="H9" s="28"/>
+      <c r="I9" s="28"/>
+      <c r="J9" s="28"/>
     </row>
     <row r="10" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="31" t="s">
+      <c r="A10" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="B10" s="31"/>
-      <c r="C10" s="31"/>
-      <c r="D10" s="31"/>
-      <c r="E10" s="31"/>
-      <c r="F10" s="32" t="s">
+      <c r="B10" s="27"/>
+      <c r="C10" s="27"/>
+      <c r="D10" s="27"/>
+      <c r="E10" s="27"/>
+      <c r="F10" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="G10" s="32"/>
-      <c r="H10" s="32"/>
-      <c r="I10" s="32"/>
-      <c r="J10" s="32"/>
+      <c r="G10" s="28"/>
+      <c r="H10" s="28"/>
+      <c r="I10" s="28"/>
+      <c r="J10" s="28"/>
     </row>
     <row r="11" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="31"/>
-      <c r="B11" s="31"/>
-      <c r="C11" s="31"/>
-      <c r="D11" s="31"/>
-      <c r="E11" s="31"/>
-      <c r="F11" s="32"/>
-      <c r="G11" s="32"/>
-      <c r="H11" s="32"/>
-      <c r="I11" s="32"/>
-      <c r="J11" s="32"/>
+      <c r="A11" s="27"/>
+      <c r="B11" s="27"/>
+      <c r="C11" s="27"/>
+      <c r="D11" s="27"/>
+      <c r="E11" s="27"/>
+      <c r="F11" s="28"/>
+      <c r="G11" s="28"/>
+      <c r="H11" s="28"/>
+      <c r="I11" s="28"/>
+      <c r="J11" s="28"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -7141,29 +7081,21 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
+      <c r="B1" s="2"/>
       <c r="C1" s="2"/>
       <c r="D1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="4">
-        <v>8</v>
-      </c>
+      <c r="E1" s="4"/>
       <c r="F1" s="5"/>
       <c r="G1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>19</v>
-      </c>
+      <c r="H1" s="1"/>
       <c r="I1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="J1" s="6" t="s">
-        <v>19</v>
-      </c>
+      <c r="J1" s="6"/>
     </row>
     <row r="2" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
@@ -7178,9 +7110,7 @@
         <v>8</v>
       </c>
       <c r="H2" s="7"/>
-      <c r="I2" s="7" t="s">
-        <v>51</v>
-      </c>
+      <c r="I2" s="7"/>
       <c r="J2" s="7"/>
     </row>
     <row r="3" ht="78.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -7216,90 +7146,86 @@
       <c r="A5" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="C5" s="17"/>
-      <c r="D5" s="18"/>
-      <c r="E5" s="19"/>
-      <c r="F5" s="20"/>
-      <c r="G5" s="20"/>
-      <c r="H5" s="20"/>
-      <c r="I5" s="21"/>
-      <c r="J5" s="22"/>
+      <c r="B5" s="29"/>
+      <c r="C5" s="30"/>
+      <c r="D5" s="31"/>
+      <c r="E5" s="17"/>
+      <c r="F5" s="18"/>
+      <c r="G5" s="18"/>
+      <c r="H5" s="18"/>
+      <c r="I5" s="19"/>
+      <c r="J5" s="20"/>
     </row>
     <row r="6" ht="150" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="23" t="s">
+      <c r="A6" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="24" t="s">
-        <v>19</v>
-      </c>
-      <c r="C6" s="25"/>
-      <c r="D6" s="26"/>
-      <c r="E6" s="27"/>
-      <c r="F6" s="28"/>
-      <c r="G6" s="28"/>
-      <c r="H6" s="28"/>
-      <c r="I6" s="29"/>
-      <c r="J6" s="30"/>
+      <c r="B6" s="32"/>
+      <c r="C6" s="33"/>
+      <c r="D6" s="34"/>
+      <c r="E6" s="23"/>
+      <c r="F6" s="24"/>
+      <c r="G6" s="24"/>
+      <c r="H6" s="24"/>
+      <c r="I6" s="25"/>
+      <c r="J6" s="26"/>
     </row>
     <row r="7" ht="78.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="8" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="31" t="s">
+      <c r="A8" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="31"/>
-      <c r="C8" s="31"/>
-      <c r="D8" s="31"/>
-      <c r="E8" s="31"/>
-      <c r="F8" s="32" t="s">
+      <c r="B8" s="27"/>
+      <c r="C8" s="27"/>
+      <c r="D8" s="27"/>
+      <c r="E8" s="27"/>
+      <c r="F8" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="G8" s="32"/>
-      <c r="H8" s="32"/>
-      <c r="I8" s="32"/>
-      <c r="J8" s="32"/>
+      <c r="G8" s="28"/>
+      <c r="H8" s="28"/>
+      <c r="I8" s="28"/>
+      <c r="J8" s="28"/>
     </row>
     <row r="9" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="31"/>
-      <c r="B9" s="31"/>
-      <c r="C9" s="31"/>
-      <c r="D9" s="31"/>
-      <c r="E9" s="31"/>
-      <c r="F9" s="32"/>
-      <c r="G9" s="32"/>
-      <c r="H9" s="32"/>
-      <c r="I9" s="32"/>
-      <c r="J9" s="32"/>
+      <c r="A9" s="27"/>
+      <c r="B9" s="27"/>
+      <c r="C9" s="27"/>
+      <c r="D9" s="27"/>
+      <c r="E9" s="27"/>
+      <c r="F9" s="28"/>
+      <c r="G9" s="28"/>
+      <c r="H9" s="28"/>
+      <c r="I9" s="28"/>
+      <c r="J9" s="28"/>
     </row>
     <row r="10" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="31" t="s">
+      <c r="A10" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="B10" s="31"/>
-      <c r="C10" s="31"/>
-      <c r="D10" s="31"/>
-      <c r="E10" s="31"/>
-      <c r="F10" s="32" t="s">
+      <c r="B10" s="27"/>
+      <c r="C10" s="27"/>
+      <c r="D10" s="27"/>
+      <c r="E10" s="27"/>
+      <c r="F10" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="G10" s="32"/>
-      <c r="H10" s="32"/>
-      <c r="I10" s="32"/>
-      <c r="J10" s="32"/>
+      <c r="G10" s="28"/>
+      <c r="H10" s="28"/>
+      <c r="I10" s="28"/>
+      <c r="J10" s="28"/>
     </row>
     <row r="11" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="31"/>
-      <c r="B11" s="31"/>
-      <c r="C11" s="31"/>
-      <c r="D11" s="31"/>
-      <c r="E11" s="31"/>
-      <c r="F11" s="32"/>
-      <c r="G11" s="32"/>
-      <c r="H11" s="32"/>
-      <c r="I11" s="32"/>
-      <c r="J11" s="32"/>
+      <c r="A11" s="27"/>
+      <c r="B11" s="27"/>
+      <c r="C11" s="27"/>
+      <c r="D11" s="27"/>
+      <c r="E11" s="27"/>
+      <c r="F11" s="28"/>
+      <c r="G11" s="28"/>
+      <c r="H11" s="28"/>
+      <c r="I11" s="28"/>
+      <c r="J11" s="28"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -7411,94 +7337,96 @@
       <c r="B5" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="C5" s="17"/>
-      <c r="D5" s="18"/>
-      <c r="E5" s="19"/>
-      <c r="F5" s="20"/>
-      <c r="G5" s="20"/>
-      <c r="H5" s="20"/>
-      <c r="I5" s="21"/>
-      <c r="J5" s="22"/>
+      <c r="C5" s="16"/>
+      <c r="D5" s="16"/>
+      <c r="E5" s="17"/>
+      <c r="F5" s="18"/>
+      <c r="G5" s="18"/>
+      <c r="H5" s="18"/>
+      <c r="I5" s="19"/>
+      <c r="J5" s="20"/>
     </row>
     <row r="6" ht="150" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="23" t="s">
+      <c r="A6" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="24" t="s">
+      <c r="B6" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="C6" s="25"/>
-      <c r="D6" s="26"/>
-      <c r="E6" s="27"/>
-      <c r="F6" s="28"/>
-      <c r="G6" s="28"/>
-      <c r="H6" s="28"/>
-      <c r="I6" s="29"/>
-      <c r="J6" s="30"/>
+      <c r="C6" s="22"/>
+      <c r="D6" s="22"/>
+      <c r="E6" s="23"/>
+      <c r="F6" s="24"/>
+      <c r="G6" s="24"/>
+      <c r="H6" s="24"/>
+      <c r="I6" s="25"/>
+      <c r="J6" s="26"/>
     </row>
     <row r="7" ht="78.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="8" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="31" t="s">
+      <c r="A8" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="31"/>
-      <c r="C8" s="31"/>
-      <c r="D8" s="31"/>
-      <c r="E8" s="31"/>
-      <c r="F8" s="32" t="s">
+      <c r="B8" s="27"/>
+      <c r="C8" s="27"/>
+      <c r="D8" s="27"/>
+      <c r="E8" s="27"/>
+      <c r="F8" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="G8" s="32"/>
-      <c r="H8" s="32"/>
-      <c r="I8" s="32"/>
-      <c r="J8" s="32"/>
+      <c r="G8" s="28"/>
+      <c r="H8" s="28"/>
+      <c r="I8" s="28"/>
+      <c r="J8" s="28"/>
     </row>
     <row r="9" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="31"/>
-      <c r="B9" s="31"/>
-      <c r="C9" s="31"/>
-      <c r="D9" s="31"/>
-      <c r="E9" s="31"/>
-      <c r="F9" s="32"/>
-      <c r="G9" s="32"/>
-      <c r="H9" s="32"/>
-      <c r="I9" s="32"/>
-      <c r="J9" s="32"/>
+      <c r="A9" s="27"/>
+      <c r="B9" s="27"/>
+      <c r="C9" s="27"/>
+      <c r="D9" s="27"/>
+      <c r="E9" s="27"/>
+      <c r="F9" s="28"/>
+      <c r="G9" s="28"/>
+      <c r="H9" s="28"/>
+      <c r="I9" s="28"/>
+      <c r="J9" s="28"/>
     </row>
     <row r="10" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="31" t="s">
+      <c r="A10" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="B10" s="31"/>
-      <c r="C10" s="31"/>
-      <c r="D10" s="31"/>
-      <c r="E10" s="31"/>
-      <c r="F10" s="32" t="s">
+      <c r="B10" s="27"/>
+      <c r="C10" s="27"/>
+      <c r="D10" s="27"/>
+      <c r="E10" s="27"/>
+      <c r="F10" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="G10" s="32"/>
-      <c r="H10" s="32"/>
-      <c r="I10" s="32"/>
-      <c r="J10" s="32"/>
+      <c r="G10" s="28"/>
+      <c r="H10" s="28"/>
+      <c r="I10" s="28"/>
+      <c r="J10" s="28"/>
     </row>
     <row r="11" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="31"/>
-      <c r="B11" s="31"/>
-      <c r="C11" s="31"/>
-      <c r="D11" s="31"/>
-      <c r="E11" s="31"/>
-      <c r="F11" s="32"/>
-      <c r="G11" s="32"/>
-      <c r="H11" s="32"/>
-      <c r="I11" s="32"/>
-      <c r="J11" s="32"/>
+      <c r="A11" s="27"/>
+      <c r="B11" s="27"/>
+      <c r="C11" s="27"/>
+      <c r="D11" s="27"/>
+      <c r="E11" s="27"/>
+      <c r="F11" s="28"/>
+      <c r="G11" s="28"/>
+      <c r="H11" s="28"/>
+      <c r="I11" s="28"/>
+      <c r="J11" s="28"/>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="10">
     <mergeCell ref="B1:C1"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="G2:H2"/>
     <mergeCell ref="I2:J2"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B6:D6"/>
     <mergeCell ref="A8:E9"/>
     <mergeCell ref="F8:J9"/>
     <mergeCell ref="A10:E11"/>
@@ -7525,29 +7453,21 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>28</v>
-      </c>
+      <c r="B1" s="2"/>
       <c r="C1" s="2"/>
       <c r="D1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="4">
-        <v>1</v>
-      </c>
+      <c r="E1" s="4"/>
       <c r="F1" s="5"/>
       <c r="G1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>19</v>
-      </c>
+      <c r="H1" s="1"/>
       <c r="I1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="J1" s="6" t="s">
-        <v>19</v>
-      </c>
+      <c r="J1" s="6"/>
     </row>
     <row r="2" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
@@ -7562,9 +7482,7 @@
         <v>8</v>
       </c>
       <c r="H2" s="7"/>
-      <c r="I2" s="7" t="s">
-        <v>51</v>
-      </c>
+      <c r="I2" s="7"/>
       <c r="J2" s="7"/>
     </row>
     <row r="3" ht="78.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -7600,90 +7518,86 @@
       <c r="A5" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="C5" s="17"/>
-      <c r="D5" s="18"/>
-      <c r="E5" s="19"/>
-      <c r="F5" s="20"/>
-      <c r="G5" s="20"/>
-      <c r="H5" s="20"/>
-      <c r="I5" s="21"/>
-      <c r="J5" s="22"/>
+      <c r="B5" s="29"/>
+      <c r="C5" s="30"/>
+      <c r="D5" s="31"/>
+      <c r="E5" s="17"/>
+      <c r="F5" s="18"/>
+      <c r="G5" s="18"/>
+      <c r="H5" s="18"/>
+      <c r="I5" s="19"/>
+      <c r="J5" s="20"/>
     </row>
     <row r="6" ht="150" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="23" t="s">
+      <c r="A6" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="24" t="s">
-        <v>19</v>
-      </c>
-      <c r="C6" s="25"/>
-      <c r="D6" s="26"/>
-      <c r="E6" s="27"/>
-      <c r="F6" s="28"/>
-      <c r="G6" s="28"/>
-      <c r="H6" s="28"/>
-      <c r="I6" s="29"/>
-      <c r="J6" s="30"/>
+      <c r="B6" s="32"/>
+      <c r="C6" s="33"/>
+      <c r="D6" s="34"/>
+      <c r="E6" s="23"/>
+      <c r="F6" s="24"/>
+      <c r="G6" s="24"/>
+      <c r="H6" s="24"/>
+      <c r="I6" s="25"/>
+      <c r="J6" s="26"/>
     </row>
     <row r="7" ht="78.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="8" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="31" t="s">
+      <c r="A8" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="31"/>
-      <c r="C8" s="31"/>
-      <c r="D8" s="31"/>
-      <c r="E8" s="31"/>
-      <c r="F8" s="32" t="s">
+      <c r="B8" s="27"/>
+      <c r="C8" s="27"/>
+      <c r="D8" s="27"/>
+      <c r="E8" s="27"/>
+      <c r="F8" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="G8" s="32"/>
-      <c r="H8" s="32"/>
-      <c r="I8" s="32"/>
-      <c r="J8" s="32"/>
+      <c r="G8" s="28"/>
+      <c r="H8" s="28"/>
+      <c r="I8" s="28"/>
+      <c r="J8" s="28"/>
     </row>
     <row r="9" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="31"/>
-      <c r="B9" s="31"/>
-      <c r="C9" s="31"/>
-      <c r="D9" s="31"/>
-      <c r="E9" s="31"/>
-      <c r="F9" s="32"/>
-      <c r="G9" s="32"/>
-      <c r="H9" s="32"/>
-      <c r="I9" s="32"/>
-      <c r="J9" s="32"/>
+      <c r="A9" s="27"/>
+      <c r="B9" s="27"/>
+      <c r="C9" s="27"/>
+      <c r="D9" s="27"/>
+      <c r="E9" s="27"/>
+      <c r="F9" s="28"/>
+      <c r="G9" s="28"/>
+      <c r="H9" s="28"/>
+      <c r="I9" s="28"/>
+      <c r="J9" s="28"/>
     </row>
     <row r="10" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="31" t="s">
+      <c r="A10" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="B10" s="31"/>
-      <c r="C10" s="31"/>
-      <c r="D10" s="31"/>
-      <c r="E10" s="31"/>
-      <c r="F10" s="32" t="s">
+      <c r="B10" s="27"/>
+      <c r="C10" s="27"/>
+      <c r="D10" s="27"/>
+      <c r="E10" s="27"/>
+      <c r="F10" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="G10" s="32"/>
-      <c r="H10" s="32"/>
-      <c r="I10" s="32"/>
-      <c r="J10" s="32"/>
+      <c r="G10" s="28"/>
+      <c r="H10" s="28"/>
+      <c r="I10" s="28"/>
+      <c r="J10" s="28"/>
     </row>
     <row r="11" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="31"/>
-      <c r="B11" s="31"/>
-      <c r="C11" s="31"/>
-      <c r="D11" s="31"/>
-      <c r="E11" s="31"/>
-      <c r="F11" s="32"/>
-      <c r="G11" s="32"/>
-      <c r="H11" s="32"/>
-      <c r="I11" s="32"/>
-      <c r="J11" s="32"/>
+      <c r="A11" s="27"/>
+      <c r="B11" s="27"/>
+      <c r="C11" s="27"/>
+      <c r="D11" s="27"/>
+      <c r="E11" s="27"/>
+      <c r="F11" s="28"/>
+      <c r="G11" s="28"/>
+      <c r="H11" s="28"/>
+      <c r="I11" s="28"/>
+      <c r="J11" s="28"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -7717,29 +7631,21 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>28</v>
-      </c>
+      <c r="B1" s="2"/>
       <c r="C1" s="2"/>
       <c r="D1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="4">
-        <v>2</v>
-      </c>
+      <c r="E1" s="4"/>
       <c r="F1" s="5"/>
       <c r="G1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>19</v>
-      </c>
+      <c r="H1" s="1"/>
       <c r="I1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="J1" s="6" t="s">
-        <v>19</v>
-      </c>
+      <c r="J1" s="6"/>
     </row>
     <row r="2" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
@@ -7754,9 +7660,7 @@
         <v>8</v>
       </c>
       <c r="H2" s="7"/>
-      <c r="I2" s="7" t="s">
-        <v>51</v>
-      </c>
+      <c r="I2" s="7"/>
       <c r="J2" s="7"/>
     </row>
     <row r="3" ht="78.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -7792,1584 +7696,86 @@
       <c r="A5" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="C5" s="17"/>
-      <c r="D5" s="18"/>
-      <c r="E5" s="19"/>
-      <c r="F5" s="20"/>
-      <c r="G5" s="20"/>
-      <c r="H5" s="20"/>
-      <c r="I5" s="21"/>
-      <c r="J5" s="22"/>
+      <c r="B5" s="29"/>
+      <c r="C5" s="30"/>
+      <c r="D5" s="31"/>
+      <c r="E5" s="17"/>
+      <c r="F5" s="18"/>
+      <c r="G5" s="18"/>
+      <c r="H5" s="18"/>
+      <c r="I5" s="19"/>
+      <c r="J5" s="20"/>
     </row>
     <row r="6" ht="150" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="23" t="s">
+      <c r="A6" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="24" t="s">
-        <v>19</v>
-      </c>
-      <c r="C6" s="25"/>
-      <c r="D6" s="26"/>
-      <c r="E6" s="27"/>
-      <c r="F6" s="28"/>
-      <c r="G6" s="28"/>
-      <c r="H6" s="28"/>
-      <c r="I6" s="29"/>
-      <c r="J6" s="30"/>
+      <c r="B6" s="32"/>
+      <c r="C6" s="33"/>
+      <c r="D6" s="34"/>
+      <c r="E6" s="23"/>
+      <c r="F6" s="24"/>
+      <c r="G6" s="24"/>
+      <c r="H6" s="24"/>
+      <c r="I6" s="25"/>
+      <c r="J6" s="26"/>
     </row>
     <row r="7" ht="78.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="8" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="31" t="s">
+      <c r="A8" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="31"/>
-      <c r="C8" s="31"/>
-      <c r="D8" s="31"/>
-      <c r="E8" s="31"/>
-      <c r="F8" s="32" t="s">
+      <c r="B8" s="27"/>
+      <c r="C8" s="27"/>
+      <c r="D8" s="27"/>
+      <c r="E8" s="27"/>
+      <c r="F8" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="G8" s="32"/>
-      <c r="H8" s="32"/>
-      <c r="I8" s="32"/>
-      <c r="J8" s="32"/>
+      <c r="G8" s="28"/>
+      <c r="H8" s="28"/>
+      <c r="I8" s="28"/>
+      <c r="J8" s="28"/>
     </row>
     <row r="9" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="31"/>
-      <c r="B9" s="31"/>
-      <c r="C9" s="31"/>
-      <c r="D9" s="31"/>
-      <c r="E9" s="31"/>
-      <c r="F9" s="32"/>
-      <c r="G9" s="32"/>
-      <c r="H9" s="32"/>
-      <c r="I9" s="32"/>
-      <c r="J9" s="32"/>
+      <c r="A9" s="27"/>
+      <c r="B9" s="27"/>
+      <c r="C9" s="27"/>
+      <c r="D9" s="27"/>
+      <c r="E9" s="27"/>
+      <c r="F9" s="28"/>
+      <c r="G9" s="28"/>
+      <c r="H9" s="28"/>
+      <c r="I9" s="28"/>
+      <c r="J9" s="28"/>
     </row>
     <row r="10" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="31" t="s">
+      <c r="A10" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="B10" s="31"/>
-      <c r="C10" s="31"/>
-      <c r="D10" s="31"/>
-      <c r="E10" s="31"/>
-      <c r="F10" s="32" t="s">
+      <c r="B10" s="27"/>
+      <c r="C10" s="27"/>
+      <c r="D10" s="27"/>
+      <c r="E10" s="27"/>
+      <c r="F10" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="G10" s="32"/>
-      <c r="H10" s="32"/>
-      <c r="I10" s="32"/>
-      <c r="J10" s="32"/>
+      <c r="G10" s="28"/>
+      <c r="H10" s="28"/>
+      <c r="I10" s="28"/>
+      <c r="J10" s="28"/>
     </row>
     <row r="11" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="31"/>
-      <c r="B11" s="31"/>
-      <c r="C11" s="31"/>
-      <c r="D11" s="31"/>
-      <c r="E11" s="31"/>
-      <c r="F11" s="32"/>
-      <c r="G11" s="32"/>
-      <c r="H11" s="32"/>
-      <c r="I11" s="32"/>
-      <c r="J11" s="32"/>
-    </row>
-  </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="B1:C1"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="I2:J2"/>
-    <mergeCell ref="A8:E9"/>
-    <mergeCell ref="F8:J9"/>
-    <mergeCell ref="A10:E11"/>
-    <mergeCell ref="F10:J11"/>
-  </mergeCells>
-  <printOptions horizontalCentered="1" verticalCentered="1"/>
-  <pageMargins left="0.7086614173228347" right="0.7086614173228347" top="0.7480314960629921" bottom="0.7480314960629921" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:J11"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="10" width="42.15" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C1" s="2"/>
-      <c r="D1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="4">
-        <v>3</v>
-      </c>
-      <c r="F1" s="5"/>
-      <c r="G1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="J1" s="6" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="2" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="J2" s="7"/>
-    </row>
-    <row r="3" ht="78.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="10"/>
-      <c r="D4" s="11"/>
-      <c r="E4" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="F4" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="G4" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="H4" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="I4" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J4" s="14" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" ht="150" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="B5" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="C5" s="17"/>
-      <c r="D5" s="18"/>
-      <c r="E5" s="19"/>
-      <c r="F5" s="20"/>
-      <c r="G5" s="20"/>
-      <c r="H5" s="20"/>
-      <c r="I5" s="21"/>
-      <c r="J5" s="22"/>
-    </row>
-    <row r="6" ht="150" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="23" t="s">
-        <v>20</v>
-      </c>
-      <c r="B6" s="24" t="s">
-        <v>19</v>
-      </c>
-      <c r="C6" s="25"/>
-      <c r="D6" s="26"/>
-      <c r="E6" s="27"/>
-      <c r="F6" s="28"/>
-      <c r="G6" s="28"/>
-      <c r="H6" s="28"/>
-      <c r="I6" s="29"/>
-      <c r="J6" s="30"/>
-    </row>
-    <row r="7" ht="78.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="31" t="s">
-        <v>21</v>
-      </c>
-      <c r="B8" s="31"/>
-      <c r="C8" s="31"/>
-      <c r="D8" s="31"/>
-      <c r="E8" s="31"/>
-      <c r="F8" s="32" t="s">
-        <v>22</v>
-      </c>
-      <c r="G8" s="32"/>
-      <c r="H8" s="32"/>
-      <c r="I8" s="32"/>
-      <c r="J8" s="32"/>
-    </row>
-    <row r="9" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="31"/>
-      <c r="B9" s="31"/>
-      <c r="C9" s="31"/>
-      <c r="D9" s="31"/>
-      <c r="E9" s="31"/>
-      <c r="F9" s="32"/>
-      <c r="G9" s="32"/>
-      <c r="H9" s="32"/>
-      <c r="I9" s="32"/>
-      <c r="J9" s="32"/>
-    </row>
-    <row r="10" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="31" t="s">
-        <v>23</v>
-      </c>
-      <c r="B10" s="31"/>
-      <c r="C10" s="31"/>
-      <c r="D10" s="31"/>
-      <c r="E10" s="31"/>
-      <c r="F10" s="32" t="s">
-        <v>24</v>
-      </c>
-      <c r="G10" s="32"/>
-      <c r="H10" s="32"/>
-      <c r="I10" s="32"/>
-      <c r="J10" s="32"/>
-    </row>
-    <row r="11" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="31"/>
-      <c r="B11" s="31"/>
-      <c r="C11" s="31"/>
-      <c r="D11" s="31"/>
-      <c r="E11" s="31"/>
-      <c r="F11" s="32"/>
-      <c r="G11" s="32"/>
-      <c r="H11" s="32"/>
-      <c r="I11" s="32"/>
-      <c r="J11" s="32"/>
-    </row>
-  </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="B1:C1"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="I2:J2"/>
-    <mergeCell ref="A8:E9"/>
-    <mergeCell ref="F8:J9"/>
-    <mergeCell ref="A10:E11"/>
-    <mergeCell ref="F10:J11"/>
-  </mergeCells>
-  <printOptions horizontalCentered="1" verticalCentered="1"/>
-  <pageMargins left="0.7086614173228347" right="0.7086614173228347" top="0.7480314960629921" bottom="0.7480314960629921" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:J11"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="10" width="42.15" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C1" s="2"/>
-      <c r="D1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="4">
-        <v>4</v>
-      </c>
-      <c r="F1" s="5"/>
-      <c r="G1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="J1" s="6" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="2" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="J2" s="7"/>
-    </row>
-    <row r="3" ht="78.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="10"/>
-      <c r="D4" s="11"/>
-      <c r="E4" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="F4" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="G4" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="H4" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="I4" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J4" s="14" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" ht="150" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="B5" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="C5" s="17"/>
-      <c r="D5" s="18"/>
-      <c r="E5" s="19"/>
-      <c r="F5" s="20"/>
-      <c r="G5" s="20"/>
-      <c r="H5" s="20"/>
-      <c r="I5" s="21"/>
-      <c r="J5" s="22"/>
-    </row>
-    <row r="6" ht="150" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="23" t="s">
-        <v>20</v>
-      </c>
-      <c r="B6" s="24" t="s">
-        <v>19</v>
-      </c>
-      <c r="C6" s="25"/>
-      <c r="D6" s="26"/>
-      <c r="E6" s="27"/>
-      <c r="F6" s="28"/>
-      <c r="G6" s="28"/>
-      <c r="H6" s="28"/>
-      <c r="I6" s="29"/>
-      <c r="J6" s="30"/>
-    </row>
-    <row r="7" ht="78.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="31" t="s">
-        <v>21</v>
-      </c>
-      <c r="B8" s="31"/>
-      <c r="C8" s="31"/>
-      <c r="D8" s="31"/>
-      <c r="E8" s="31"/>
-      <c r="F8" s="32" t="s">
-        <v>22</v>
-      </c>
-      <c r="G8" s="32"/>
-      <c r="H8" s="32"/>
-      <c r="I8" s="32"/>
-      <c r="J8" s="32"/>
-    </row>
-    <row r="9" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="31"/>
-      <c r="B9" s="31"/>
-      <c r="C9" s="31"/>
-      <c r="D9" s="31"/>
-      <c r="E9" s="31"/>
-      <c r="F9" s="32"/>
-      <c r="G9" s="32"/>
-      <c r="H9" s="32"/>
-      <c r="I9" s="32"/>
-      <c r="J9" s="32"/>
-    </row>
-    <row r="10" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="31" t="s">
-        <v>23</v>
-      </c>
-      <c r="B10" s="31"/>
-      <c r="C10" s="31"/>
-      <c r="D10" s="31"/>
-      <c r="E10" s="31"/>
-      <c r="F10" s="32" t="s">
-        <v>24</v>
-      </c>
-      <c r="G10" s="32"/>
-      <c r="H10" s="32"/>
-      <c r="I10" s="32"/>
-      <c r="J10" s="32"/>
-    </row>
-    <row r="11" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="31"/>
-      <c r="B11" s="31"/>
-      <c r="C11" s="31"/>
-      <c r="D11" s="31"/>
-      <c r="E11" s="31"/>
-      <c r="F11" s="32"/>
-      <c r="G11" s="32"/>
-      <c r="H11" s="32"/>
-      <c r="I11" s="32"/>
-      <c r="J11" s="32"/>
-    </row>
-  </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="B1:C1"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="I2:J2"/>
-    <mergeCell ref="A8:E9"/>
-    <mergeCell ref="F8:J9"/>
-    <mergeCell ref="A10:E11"/>
-    <mergeCell ref="F10:J11"/>
-  </mergeCells>
-  <printOptions horizontalCentered="1" verticalCentered="1"/>
-  <pageMargins left="0.7086614173228347" right="0.7086614173228347" top="0.7480314960629921" bottom="0.7480314960629921" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:J11"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="10" width="42.15" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C1" s="2"/>
-      <c r="D1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="4">
-        <v>1</v>
-      </c>
-      <c r="F1" s="5"/>
-      <c r="G1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="J1" s="6" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="2" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="J2" s="7"/>
-    </row>
-    <row r="3" ht="78.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="10"/>
-      <c r="D4" s="11"/>
-      <c r="E4" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="F4" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="G4" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="H4" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="I4" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J4" s="14" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" ht="150" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="B5" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="C5" s="17"/>
-      <c r="D5" s="18"/>
-      <c r="E5" s="19"/>
-      <c r="F5" s="20"/>
-      <c r="G5" s="20"/>
-      <c r="H5" s="20"/>
-      <c r="I5" s="21"/>
-      <c r="J5" s="22"/>
-    </row>
-    <row r="6" ht="150" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="23" t="s">
-        <v>20</v>
-      </c>
-      <c r="B6" s="24" t="s">
-        <v>19</v>
-      </c>
-      <c r="C6" s="25"/>
-      <c r="D6" s="26"/>
-      <c r="E6" s="27"/>
-      <c r="F6" s="28"/>
-      <c r="G6" s="28"/>
-      <c r="H6" s="28"/>
-      <c r="I6" s="29"/>
-      <c r="J6" s="30"/>
-    </row>
-    <row r="7" ht="78.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="31" t="s">
-        <v>21</v>
-      </c>
-      <c r="B8" s="31"/>
-      <c r="C8" s="31"/>
-      <c r="D8" s="31"/>
-      <c r="E8" s="31"/>
-      <c r="F8" s="32" t="s">
-        <v>22</v>
-      </c>
-      <c r="G8" s="32"/>
-      <c r="H8" s="32"/>
-      <c r="I8" s="32"/>
-      <c r="J8" s="32"/>
-    </row>
-    <row r="9" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="31"/>
-      <c r="B9" s="31"/>
-      <c r="C9" s="31"/>
-      <c r="D9" s="31"/>
-      <c r="E9" s="31"/>
-      <c r="F9" s="32"/>
-      <c r="G9" s="32"/>
-      <c r="H9" s="32"/>
-      <c r="I9" s="32"/>
-      <c r="J9" s="32"/>
-    </row>
-    <row r="10" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="31" t="s">
-        <v>23</v>
-      </c>
-      <c r="B10" s="31"/>
-      <c r="C10" s="31"/>
-      <c r="D10" s="31"/>
-      <c r="E10" s="31"/>
-      <c r="F10" s="32" t="s">
-        <v>24</v>
-      </c>
-      <c r="G10" s="32"/>
-      <c r="H10" s="32"/>
-      <c r="I10" s="32"/>
-      <c r="J10" s="32"/>
-    </row>
-    <row r="11" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="31"/>
-      <c r="B11" s="31"/>
-      <c r="C11" s="31"/>
-      <c r="D11" s="31"/>
-      <c r="E11" s="31"/>
-      <c r="F11" s="32"/>
-      <c r="G11" s="32"/>
-      <c r="H11" s="32"/>
-      <c r="I11" s="32"/>
-      <c r="J11" s="32"/>
-    </row>
-  </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="B1:C1"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="I2:J2"/>
-    <mergeCell ref="A8:E9"/>
-    <mergeCell ref="F8:J9"/>
-    <mergeCell ref="A10:E11"/>
-    <mergeCell ref="F10:J11"/>
-  </mergeCells>
-  <printOptions horizontalCentered="1" verticalCentered="1"/>
-  <pageMargins left="0.7086614173228347" right="0.7086614173228347" top="0.7480314960629921" bottom="0.7480314960629921" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:J11"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="10" width="42.15" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C1" s="2"/>
-      <c r="D1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="4">
-        <v>2</v>
-      </c>
-      <c r="F1" s="5"/>
-      <c r="G1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="J1" s="6" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="2" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="J2" s="7"/>
-    </row>
-    <row r="3" ht="78.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="10"/>
-      <c r="D4" s="11"/>
-      <c r="E4" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="F4" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="G4" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="H4" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="I4" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J4" s="14" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" ht="150" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="B5" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="C5" s="17"/>
-      <c r="D5" s="18"/>
-      <c r="E5" s="19"/>
-      <c r="F5" s="20"/>
-      <c r="G5" s="20"/>
-      <c r="H5" s="20"/>
-      <c r="I5" s="21"/>
-      <c r="J5" s="22"/>
-    </row>
-    <row r="6" ht="150" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="23" t="s">
-        <v>20</v>
-      </c>
-      <c r="B6" s="24" t="s">
-        <v>19</v>
-      </c>
-      <c r="C6" s="25"/>
-      <c r="D6" s="26"/>
-      <c r="E6" s="27"/>
-      <c r="F6" s="28"/>
-      <c r="G6" s="28"/>
-      <c r="H6" s="28"/>
-      <c r="I6" s="29"/>
-      <c r="J6" s="30"/>
-    </row>
-    <row r="7" ht="78.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="31" t="s">
-        <v>21</v>
-      </c>
-      <c r="B8" s="31"/>
-      <c r="C8" s="31"/>
-      <c r="D8" s="31"/>
-      <c r="E8" s="31"/>
-      <c r="F8" s="32" t="s">
-        <v>22</v>
-      </c>
-      <c r="G8" s="32"/>
-      <c r="H8" s="32"/>
-      <c r="I8" s="32"/>
-      <c r="J8" s="32"/>
-    </row>
-    <row r="9" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="31"/>
-      <c r="B9" s="31"/>
-      <c r="C9" s="31"/>
-      <c r="D9" s="31"/>
-      <c r="E9" s="31"/>
-      <c r="F9" s="32"/>
-      <c r="G9" s="32"/>
-      <c r="H9" s="32"/>
-      <c r="I9" s="32"/>
-      <c r="J9" s="32"/>
-    </row>
-    <row r="10" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="31" t="s">
-        <v>23</v>
-      </c>
-      <c r="B10" s="31"/>
-      <c r="C10" s="31"/>
-      <c r="D10" s="31"/>
-      <c r="E10" s="31"/>
-      <c r="F10" s="32" t="s">
-        <v>24</v>
-      </c>
-      <c r="G10" s="32"/>
-      <c r="H10" s="32"/>
-      <c r="I10" s="32"/>
-      <c r="J10" s="32"/>
-    </row>
-    <row r="11" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="31"/>
-      <c r="B11" s="31"/>
-      <c r="C11" s="31"/>
-      <c r="D11" s="31"/>
-      <c r="E11" s="31"/>
-      <c r="F11" s="32"/>
-      <c r="G11" s="32"/>
-      <c r="H11" s="32"/>
-      <c r="I11" s="32"/>
-      <c r="J11" s="32"/>
-    </row>
-  </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="B1:C1"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="I2:J2"/>
-    <mergeCell ref="A8:E9"/>
-    <mergeCell ref="F8:J9"/>
-    <mergeCell ref="A10:E11"/>
-    <mergeCell ref="F10:J11"/>
-  </mergeCells>
-  <printOptions horizontalCentered="1" verticalCentered="1"/>
-  <pageMargins left="0.7086614173228347" right="0.7086614173228347" top="0.7480314960629921" bottom="0.7480314960629921" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:J11"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="10" width="42.15" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="C1" s="2"/>
-      <c r="D1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="4">
-        <v>1</v>
-      </c>
-      <c r="F1" s="5"/>
-      <c r="G1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="J1" s="6" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="2" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="J2" s="7"/>
-    </row>
-    <row r="3" ht="78.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="10"/>
-      <c r="D4" s="11"/>
-      <c r="E4" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="F4" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="G4" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="H4" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="I4" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J4" s="14" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" ht="150" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="B5" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="C5" s="17"/>
-      <c r="D5" s="18"/>
-      <c r="E5" s="19"/>
-      <c r="F5" s="20"/>
-      <c r="G5" s="20"/>
-      <c r="H5" s="20"/>
-      <c r="I5" s="21"/>
-      <c r="J5" s="22"/>
-    </row>
-    <row r="6" ht="150" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="23" t="s">
-        <v>20</v>
-      </c>
-      <c r="B6" s="24" t="s">
-        <v>19</v>
-      </c>
-      <c r="C6" s="25"/>
-      <c r="D6" s="26"/>
-      <c r="E6" s="27"/>
-      <c r="F6" s="28"/>
-      <c r="G6" s="28"/>
-      <c r="H6" s="28"/>
-      <c r="I6" s="29"/>
-      <c r="J6" s="30"/>
-    </row>
-    <row r="7" ht="78.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="31" t="s">
-        <v>21</v>
-      </c>
-      <c r="B8" s="31"/>
-      <c r="C8" s="31"/>
-      <c r="D8" s="31"/>
-      <c r="E8" s="31"/>
-      <c r="F8" s="32" t="s">
-        <v>22</v>
-      </c>
-      <c r="G8" s="32"/>
-      <c r="H8" s="32"/>
-      <c r="I8" s="32"/>
-      <c r="J8" s="32"/>
-    </row>
-    <row r="9" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="31"/>
-      <c r="B9" s="31"/>
-      <c r="C9" s="31"/>
-      <c r="D9" s="31"/>
-      <c r="E9" s="31"/>
-      <c r="F9" s="32"/>
-      <c r="G9" s="32"/>
-      <c r="H9" s="32"/>
-      <c r="I9" s="32"/>
-      <c r="J9" s="32"/>
-    </row>
-    <row r="10" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="31" t="s">
-        <v>23</v>
-      </c>
-      <c r="B10" s="31"/>
-      <c r="C10" s="31"/>
-      <c r="D10" s="31"/>
-      <c r="E10" s="31"/>
-      <c r="F10" s="32" t="s">
-        <v>24</v>
-      </c>
-      <c r="G10" s="32"/>
-      <c r="H10" s="32"/>
-      <c r="I10" s="32"/>
-      <c r="J10" s="32"/>
-    </row>
-    <row r="11" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="31"/>
-      <c r="B11" s="31"/>
-      <c r="C11" s="31"/>
-      <c r="D11" s="31"/>
-      <c r="E11" s="31"/>
-      <c r="F11" s="32"/>
-      <c r="G11" s="32"/>
-      <c r="H11" s="32"/>
-      <c r="I11" s="32"/>
-      <c r="J11" s="32"/>
-    </row>
-  </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="B1:C1"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="I2:J2"/>
-    <mergeCell ref="A8:E9"/>
-    <mergeCell ref="F8:J9"/>
-    <mergeCell ref="A10:E11"/>
-    <mergeCell ref="F10:J11"/>
-  </mergeCells>
-  <printOptions horizontalCentered="1" verticalCentered="1"/>
-  <pageMargins left="0.7086614173228347" right="0.7086614173228347" top="0.7480314960629921" bottom="0.7480314960629921" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:J11"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="10" width="42.15" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="4"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="J1" s="6"/>
-    </row>
-    <row r="2" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
-    </row>
-    <row r="3" ht="78.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="10"/>
-      <c r="D4" s="11"/>
-      <c r="E4" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="F4" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="G4" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="H4" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="I4" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J4" s="14" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" ht="150" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="B5" s="16"/>
-      <c r="C5" s="17"/>
-      <c r="D5" s="18"/>
-      <c r="E5" s="19"/>
-      <c r="F5" s="20"/>
-      <c r="G5" s="20"/>
-      <c r="H5" s="20"/>
-      <c r="I5" s="21"/>
-      <c r="J5" s="22"/>
-    </row>
-    <row r="6" ht="150" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="23" t="s">
-        <v>20</v>
-      </c>
-      <c r="B6" s="24"/>
-      <c r="C6" s="25"/>
-      <c r="D6" s="26"/>
-      <c r="E6" s="27"/>
-      <c r="F6" s="28"/>
-      <c r="G6" s="28"/>
-      <c r="H6" s="28"/>
-      <c r="I6" s="29"/>
-      <c r="J6" s="30"/>
-    </row>
-    <row r="7" ht="78.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="31" t="s">
-        <v>21</v>
-      </c>
-      <c r="B8" s="31"/>
-      <c r="C8" s="31"/>
-      <c r="D8" s="31"/>
-      <c r="E8" s="31"/>
-      <c r="F8" s="32" t="s">
-        <v>22</v>
-      </c>
-      <c r="G8" s="32"/>
-      <c r="H8" s="32"/>
-      <c r="I8" s="32"/>
-      <c r="J8" s="32"/>
-    </row>
-    <row r="9" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="31"/>
-      <c r="B9" s="31"/>
-      <c r="C9" s="31"/>
-      <c r="D9" s="31"/>
-      <c r="E9" s="31"/>
-      <c r="F9" s="32"/>
-      <c r="G9" s="32"/>
-      <c r="H9" s="32"/>
-      <c r="I9" s="32"/>
-      <c r="J9" s="32"/>
-    </row>
-    <row r="10" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="31" t="s">
-        <v>23</v>
-      </c>
-      <c r="B10" s="31"/>
-      <c r="C10" s="31"/>
-      <c r="D10" s="31"/>
-      <c r="E10" s="31"/>
-      <c r="F10" s="32" t="s">
-        <v>24</v>
-      </c>
-      <c r="G10" s="32"/>
-      <c r="H10" s="32"/>
-      <c r="I10" s="32"/>
-      <c r="J10" s="32"/>
-    </row>
-    <row r="11" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="31"/>
-      <c r="B11" s="31"/>
-      <c r="C11" s="31"/>
-      <c r="D11" s="31"/>
-      <c r="E11" s="31"/>
-      <c r="F11" s="32"/>
-      <c r="G11" s="32"/>
-      <c r="H11" s="32"/>
-      <c r="I11" s="32"/>
-      <c r="J11" s="32"/>
-    </row>
-  </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="B1:C1"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="I2:J2"/>
-    <mergeCell ref="A8:E9"/>
-    <mergeCell ref="F8:J9"/>
-    <mergeCell ref="A10:E11"/>
-    <mergeCell ref="F10:J11"/>
-  </mergeCells>
-  <printOptions horizontalCentered="1" verticalCentered="1"/>
-  <pageMargins left="0.7086614173228347" right="0.7086614173228347" top="0.7480314960629921" bottom="0.7480314960629921" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:J11"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="10" width="42.15" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="4"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="J1" s="6"/>
-    </row>
-    <row r="2" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
-    </row>
-    <row r="3" ht="78.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="10"/>
-      <c r="D4" s="11"/>
-      <c r="E4" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="F4" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="G4" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="H4" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="I4" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J4" s="14" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" ht="150" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="B5" s="16"/>
-      <c r="C5" s="17"/>
-      <c r="D5" s="18"/>
-      <c r="E5" s="19"/>
-      <c r="F5" s="20"/>
-      <c r="G5" s="20"/>
-      <c r="H5" s="20"/>
-      <c r="I5" s="21"/>
-      <c r="J5" s="22"/>
-    </row>
-    <row r="6" ht="150" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="23" t="s">
-        <v>20</v>
-      </c>
-      <c r="B6" s="24"/>
-      <c r="C6" s="25"/>
-      <c r="D6" s="26"/>
-      <c r="E6" s="27"/>
-      <c r="F6" s="28"/>
-      <c r="G6" s="28"/>
-      <c r="H6" s="28"/>
-      <c r="I6" s="29"/>
-      <c r="J6" s="30"/>
-    </row>
-    <row r="7" ht="78.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="31" t="s">
-        <v>21</v>
-      </c>
-      <c r="B8" s="31"/>
-      <c r="C8" s="31"/>
-      <c r="D8" s="31"/>
-      <c r="E8" s="31"/>
-      <c r="F8" s="32" t="s">
-        <v>22</v>
-      </c>
-      <c r="G8" s="32"/>
-      <c r="H8" s="32"/>
-      <c r="I8" s="32"/>
-      <c r="J8" s="32"/>
-    </row>
-    <row r="9" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="31"/>
-      <c r="B9" s="31"/>
-      <c r="C9" s="31"/>
-      <c r="D9" s="31"/>
-      <c r="E9" s="31"/>
-      <c r="F9" s="32"/>
-      <c r="G9" s="32"/>
-      <c r="H9" s="32"/>
-      <c r="I9" s="32"/>
-      <c r="J9" s="32"/>
-    </row>
-    <row r="10" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="31" t="s">
-        <v>23</v>
-      </c>
-      <c r="B10" s="31"/>
-      <c r="C10" s="31"/>
-      <c r="D10" s="31"/>
-      <c r="E10" s="31"/>
-      <c r="F10" s="32" t="s">
-        <v>24</v>
-      </c>
-      <c r="G10" s="32"/>
-      <c r="H10" s="32"/>
-      <c r="I10" s="32"/>
-      <c r="J10" s="32"/>
-    </row>
-    <row r="11" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="31"/>
-      <c r="B11" s="31"/>
-      <c r="C11" s="31"/>
-      <c r="D11" s="31"/>
-      <c r="E11" s="31"/>
-      <c r="F11" s="32"/>
-      <c r="G11" s="32"/>
-      <c r="H11" s="32"/>
-      <c r="I11" s="32"/>
-      <c r="J11" s="32"/>
-    </row>
-  </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="B1:C1"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="I2:J2"/>
-    <mergeCell ref="A8:E9"/>
-    <mergeCell ref="F8:J9"/>
-    <mergeCell ref="A10:E11"/>
-    <mergeCell ref="F10:J11"/>
-  </mergeCells>
-  <printOptions horizontalCentered="1" verticalCentered="1"/>
-  <pageMargins left="0.7086614173228347" right="0.7086614173228347" top="0.7480314960629921" bottom="0.7480314960629921" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:J11"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="10" width="42.15" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="4"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="J1" s="6"/>
-    </row>
-    <row r="2" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
-    </row>
-    <row r="3" ht="78.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="10"/>
-      <c r="D4" s="11"/>
-      <c r="E4" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="F4" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="G4" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="H4" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="I4" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J4" s="14" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" ht="150" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="B5" s="16"/>
-      <c r="C5" s="17"/>
-      <c r="D5" s="18"/>
-      <c r="E5" s="19"/>
-      <c r="F5" s="20"/>
-      <c r="G5" s="20"/>
-      <c r="H5" s="20"/>
-      <c r="I5" s="21"/>
-      <c r="J5" s="22"/>
-    </row>
-    <row r="6" ht="150" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="23" t="s">
-        <v>20</v>
-      </c>
-      <c r="B6" s="24"/>
-      <c r="C6" s="25"/>
-      <c r="D6" s="26"/>
-      <c r="E6" s="27"/>
-      <c r="F6" s="28"/>
-      <c r="G6" s="28"/>
-      <c r="H6" s="28"/>
-      <c r="I6" s="29"/>
-      <c r="J6" s="30"/>
-    </row>
-    <row r="7" ht="78.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="31" t="s">
-        <v>21</v>
-      </c>
-      <c r="B8" s="31"/>
-      <c r="C8" s="31"/>
-      <c r="D8" s="31"/>
-      <c r="E8" s="31"/>
-      <c r="F8" s="32" t="s">
-        <v>22</v>
-      </c>
-      <c r="G8" s="32"/>
-      <c r="H8" s="32"/>
-      <c r="I8" s="32"/>
-      <c r="J8" s="32"/>
-    </row>
-    <row r="9" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="31"/>
-      <c r="B9" s="31"/>
-      <c r="C9" s="31"/>
-      <c r="D9" s="31"/>
-      <c r="E9" s="31"/>
-      <c r="F9" s="32"/>
-      <c r="G9" s="32"/>
-      <c r="H9" s="32"/>
-      <c r="I9" s="32"/>
-      <c r="J9" s="32"/>
-    </row>
-    <row r="10" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="31" t="s">
-        <v>23</v>
-      </c>
-      <c r="B10" s="31"/>
-      <c r="C10" s="31"/>
-      <c r="D10" s="31"/>
-      <c r="E10" s="31"/>
-      <c r="F10" s="32" t="s">
-        <v>24</v>
-      </c>
-      <c r="G10" s="32"/>
-      <c r="H10" s="32"/>
-      <c r="I10" s="32"/>
-      <c r="J10" s="32"/>
-    </row>
-    <row r="11" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="31"/>
-      <c r="B11" s="31"/>
-      <c r="C11" s="31"/>
-      <c r="D11" s="31"/>
-      <c r="E11" s="31"/>
-      <c r="F11" s="32"/>
-      <c r="G11" s="32"/>
-      <c r="H11" s="32"/>
-      <c r="I11" s="32"/>
-      <c r="J11" s="32"/>
+      <c r="A11" s="27"/>
+      <c r="B11" s="27"/>
+      <c r="C11" s="27"/>
+      <c r="D11" s="27"/>
+      <c r="E11" s="27"/>
+      <c r="F11" s="28"/>
+      <c r="G11" s="28"/>
+      <c r="H11" s="28"/>
+      <c r="I11" s="28"/>
+      <c r="J11" s="28"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -9481,1340 +7887,96 @@
       <c r="B5" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="C5" s="17"/>
-      <c r="D5" s="18"/>
-      <c r="E5" s="19"/>
-      <c r="F5" s="20"/>
-      <c r="G5" s="20"/>
-      <c r="H5" s="20"/>
-      <c r="I5" s="21"/>
-      <c r="J5" s="22"/>
+      <c r="C5" s="16"/>
+      <c r="D5" s="16"/>
+      <c r="E5" s="17"/>
+      <c r="F5" s="18"/>
+      <c r="G5" s="18"/>
+      <c r="H5" s="18"/>
+      <c r="I5" s="19"/>
+      <c r="J5" s="20"/>
     </row>
     <row r="6" ht="150" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="23" t="s">
+      <c r="A6" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="24" t="s">
+      <c r="B6" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="C6" s="25"/>
-      <c r="D6" s="26"/>
-      <c r="E6" s="27"/>
-      <c r="F6" s="28"/>
-      <c r="G6" s="28"/>
-      <c r="H6" s="28"/>
-      <c r="I6" s="29"/>
-      <c r="J6" s="30"/>
+      <c r="C6" s="22"/>
+      <c r="D6" s="22"/>
+      <c r="E6" s="23"/>
+      <c r="F6" s="24"/>
+      <c r="G6" s="24"/>
+      <c r="H6" s="24"/>
+      <c r="I6" s="25"/>
+      <c r="J6" s="26"/>
     </row>
     <row r="7" ht="78.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="8" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="31" t="s">
+      <c r="A8" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="31"/>
-      <c r="C8" s="31"/>
-      <c r="D8" s="31"/>
-      <c r="E8" s="31"/>
-      <c r="F8" s="32" t="s">
+      <c r="B8" s="27"/>
+      <c r="C8" s="27"/>
+      <c r="D8" s="27"/>
+      <c r="E8" s="27"/>
+      <c r="F8" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="G8" s="32"/>
-      <c r="H8" s="32"/>
-      <c r="I8" s="32"/>
-      <c r="J8" s="32"/>
+      <c r="G8" s="28"/>
+      <c r="H8" s="28"/>
+      <c r="I8" s="28"/>
+      <c r="J8" s="28"/>
     </row>
     <row r="9" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="31"/>
-      <c r="B9" s="31"/>
-      <c r="C9" s="31"/>
-      <c r="D9" s="31"/>
-      <c r="E9" s="31"/>
-      <c r="F9" s="32"/>
-      <c r="G9" s="32"/>
-      <c r="H9" s="32"/>
-      <c r="I9" s="32"/>
-      <c r="J9" s="32"/>
+      <c r="A9" s="27"/>
+      <c r="B9" s="27"/>
+      <c r="C9" s="27"/>
+      <c r="D9" s="27"/>
+      <c r="E9" s="27"/>
+      <c r="F9" s="28"/>
+      <c r="G9" s="28"/>
+      <c r="H9" s="28"/>
+      <c r="I9" s="28"/>
+      <c r="J9" s="28"/>
     </row>
     <row r="10" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="31" t="s">
+      <c r="A10" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="B10" s="31"/>
-      <c r="C10" s="31"/>
-      <c r="D10" s="31"/>
-      <c r="E10" s="31"/>
-      <c r="F10" s="32" t="s">
+      <c r="B10" s="27"/>
+      <c r="C10" s="27"/>
+      <c r="D10" s="27"/>
+      <c r="E10" s="27"/>
+      <c r="F10" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="G10" s="32"/>
-      <c r="H10" s="32"/>
-      <c r="I10" s="32"/>
-      <c r="J10" s="32"/>
+      <c r="G10" s="28"/>
+      <c r="H10" s="28"/>
+      <c r="I10" s="28"/>
+      <c r="J10" s="28"/>
     </row>
     <row r="11" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="31"/>
-      <c r="B11" s="31"/>
-      <c r="C11" s="31"/>
-      <c r="D11" s="31"/>
-      <c r="E11" s="31"/>
-      <c r="F11" s="32"/>
-      <c r="G11" s="32"/>
-      <c r="H11" s="32"/>
-      <c r="I11" s="32"/>
-      <c r="J11" s="32"/>
+      <c r="A11" s="27"/>
+      <c r="B11" s="27"/>
+      <c r="C11" s="27"/>
+      <c r="D11" s="27"/>
+      <c r="E11" s="27"/>
+      <c r="F11" s="28"/>
+      <c r="G11" s="28"/>
+      <c r="H11" s="28"/>
+      <c r="I11" s="28"/>
+      <c r="J11" s="28"/>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="10">
     <mergeCell ref="B1:C1"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="G2:H2"/>
     <mergeCell ref="I2:J2"/>
-    <mergeCell ref="A8:E9"/>
-    <mergeCell ref="F8:J9"/>
-    <mergeCell ref="A10:E11"/>
-    <mergeCell ref="F10:J11"/>
-  </mergeCells>
-  <printOptions horizontalCentered="1" verticalCentered="1"/>
-  <pageMargins left="0.7086614173228347" right="0.7086614173228347" top="0.7480314960629921" bottom="0.7480314960629921" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet50.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:J11"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="10" width="42.15" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="4"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="J1" s="6"/>
-    </row>
-    <row r="2" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
-    </row>
-    <row r="3" ht="78.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="10"/>
-      <c r="D4" s="11"/>
-      <c r="E4" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="F4" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="G4" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="H4" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="I4" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J4" s="14" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" ht="150" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="B5" s="16"/>
-      <c r="C5" s="17"/>
-      <c r="D5" s="18"/>
-      <c r="E5" s="19"/>
-      <c r="F5" s="20"/>
-      <c r="G5" s="20"/>
-      <c r="H5" s="20"/>
-      <c r="I5" s="21"/>
-      <c r="J5" s="22"/>
-    </row>
-    <row r="6" ht="150" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="23" t="s">
-        <v>20</v>
-      </c>
-      <c r="B6" s="24"/>
-      <c r="C6" s="25"/>
-      <c r="D6" s="26"/>
-      <c r="E6" s="27"/>
-      <c r="F6" s="28"/>
-      <c r="G6" s="28"/>
-      <c r="H6" s="28"/>
-      <c r="I6" s="29"/>
-      <c r="J6" s="30"/>
-    </row>
-    <row r="7" ht="78.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="31" t="s">
-        <v>21</v>
-      </c>
-      <c r="B8" s="31"/>
-      <c r="C8" s="31"/>
-      <c r="D8" s="31"/>
-      <c r="E8" s="31"/>
-      <c r="F8" s="32" t="s">
-        <v>22</v>
-      </c>
-      <c r="G8" s="32"/>
-      <c r="H8" s="32"/>
-      <c r="I8" s="32"/>
-      <c r="J8" s="32"/>
-    </row>
-    <row r="9" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="31"/>
-      <c r="B9" s="31"/>
-      <c r="C9" s="31"/>
-      <c r="D9" s="31"/>
-      <c r="E9" s="31"/>
-      <c r="F9" s="32"/>
-      <c r="G9" s="32"/>
-      <c r="H9" s="32"/>
-      <c r="I9" s="32"/>
-      <c r="J9" s="32"/>
-    </row>
-    <row r="10" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="31" t="s">
-        <v>23</v>
-      </c>
-      <c r="B10" s="31"/>
-      <c r="C10" s="31"/>
-      <c r="D10" s="31"/>
-      <c r="E10" s="31"/>
-      <c r="F10" s="32" t="s">
-        <v>24</v>
-      </c>
-      <c r="G10" s="32"/>
-      <c r="H10" s="32"/>
-      <c r="I10" s="32"/>
-      <c r="J10" s="32"/>
-    </row>
-    <row r="11" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="31"/>
-      <c r="B11" s="31"/>
-      <c r="C11" s="31"/>
-      <c r="D11" s="31"/>
-      <c r="E11" s="31"/>
-      <c r="F11" s="32"/>
-      <c r="G11" s="32"/>
-      <c r="H11" s="32"/>
-      <c r="I11" s="32"/>
-      <c r="J11" s="32"/>
-    </row>
-  </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="B1:C1"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="I2:J2"/>
-    <mergeCell ref="A8:E9"/>
-    <mergeCell ref="F8:J9"/>
-    <mergeCell ref="A10:E11"/>
-    <mergeCell ref="F10:J11"/>
-  </mergeCells>
-  <printOptions horizontalCentered="1" verticalCentered="1"/>
-  <pageMargins left="0.7086614173228347" right="0.7086614173228347" top="0.7480314960629921" bottom="0.7480314960629921" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet51.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:J11"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="10" width="42.15" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="4"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="J1" s="6"/>
-    </row>
-    <row r="2" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
-    </row>
-    <row r="3" ht="78.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="10"/>
-      <c r="D4" s="11"/>
-      <c r="E4" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="F4" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="G4" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="H4" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="I4" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J4" s="14" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" ht="150" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="B5" s="16"/>
-      <c r="C5" s="17"/>
-      <c r="D5" s="18"/>
-      <c r="E5" s="19"/>
-      <c r="F5" s="20"/>
-      <c r="G5" s="20"/>
-      <c r="H5" s="20"/>
-      <c r="I5" s="21"/>
-      <c r="J5" s="22"/>
-    </row>
-    <row r="6" ht="150" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="23" t="s">
-        <v>20</v>
-      </c>
-      <c r="B6" s="24"/>
-      <c r="C6" s="25"/>
-      <c r="D6" s="26"/>
-      <c r="E6" s="27"/>
-      <c r="F6" s="28"/>
-      <c r="G6" s="28"/>
-      <c r="H6" s="28"/>
-      <c r="I6" s="29"/>
-      <c r="J6" s="30"/>
-    </row>
-    <row r="7" ht="78.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="31" t="s">
-        <v>21</v>
-      </c>
-      <c r="B8" s="31"/>
-      <c r="C8" s="31"/>
-      <c r="D8" s="31"/>
-      <c r="E8" s="31"/>
-      <c r="F8" s="32" t="s">
-        <v>22</v>
-      </c>
-      <c r="G8" s="32"/>
-      <c r="H8" s="32"/>
-      <c r="I8" s="32"/>
-      <c r="J8" s="32"/>
-    </row>
-    <row r="9" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="31"/>
-      <c r="B9" s="31"/>
-      <c r="C9" s="31"/>
-      <c r="D9" s="31"/>
-      <c r="E9" s="31"/>
-      <c r="F9" s="32"/>
-      <c r="G9" s="32"/>
-      <c r="H9" s="32"/>
-      <c r="I9" s="32"/>
-      <c r="J9" s="32"/>
-    </row>
-    <row r="10" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="31" t="s">
-        <v>23</v>
-      </c>
-      <c r="B10" s="31"/>
-      <c r="C10" s="31"/>
-      <c r="D10" s="31"/>
-      <c r="E10" s="31"/>
-      <c r="F10" s="32" t="s">
-        <v>24</v>
-      </c>
-      <c r="G10" s="32"/>
-      <c r="H10" s="32"/>
-      <c r="I10" s="32"/>
-      <c r="J10" s="32"/>
-    </row>
-    <row r="11" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="31"/>
-      <c r="B11" s="31"/>
-      <c r="C11" s="31"/>
-      <c r="D11" s="31"/>
-      <c r="E11" s="31"/>
-      <c r="F11" s="32"/>
-      <c r="G11" s="32"/>
-      <c r="H11" s="32"/>
-      <c r="I11" s="32"/>
-      <c r="J11" s="32"/>
-    </row>
-  </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="B1:C1"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="I2:J2"/>
-    <mergeCell ref="A8:E9"/>
-    <mergeCell ref="F8:J9"/>
-    <mergeCell ref="A10:E11"/>
-    <mergeCell ref="F10:J11"/>
-  </mergeCells>
-  <printOptions horizontalCentered="1" verticalCentered="1"/>
-  <pageMargins left="0.7086614173228347" right="0.7086614173228347" top="0.7480314960629921" bottom="0.7480314960629921" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet52.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:J11"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="10" width="42.15" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="4"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="J1" s="6"/>
-    </row>
-    <row r="2" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
-    </row>
-    <row r="3" ht="78.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="10"/>
-      <c r="D4" s="11"/>
-      <c r="E4" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="F4" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="G4" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="H4" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="I4" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J4" s="14" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" ht="150" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="B5" s="16"/>
-      <c r="C5" s="17"/>
-      <c r="D5" s="18"/>
-      <c r="E5" s="19"/>
-      <c r="F5" s="20"/>
-      <c r="G5" s="20"/>
-      <c r="H5" s="20"/>
-      <c r="I5" s="21"/>
-      <c r="J5" s="22"/>
-    </row>
-    <row r="6" ht="150" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="23" t="s">
-        <v>20</v>
-      </c>
-      <c r="B6" s="24"/>
-      <c r="C6" s="25"/>
-      <c r="D6" s="26"/>
-      <c r="E6" s="27"/>
-      <c r="F6" s="28"/>
-      <c r="G6" s="28"/>
-      <c r="H6" s="28"/>
-      <c r="I6" s="29"/>
-      <c r="J6" s="30"/>
-    </row>
-    <row r="7" ht="78.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="31" t="s">
-        <v>21</v>
-      </c>
-      <c r="B8" s="31"/>
-      <c r="C8" s="31"/>
-      <c r="D8" s="31"/>
-      <c r="E8" s="31"/>
-      <c r="F8" s="32" t="s">
-        <v>22</v>
-      </c>
-      <c r="G8" s="32"/>
-      <c r="H8" s="32"/>
-      <c r="I8" s="32"/>
-      <c r="J8" s="32"/>
-    </row>
-    <row r="9" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="31"/>
-      <c r="B9" s="31"/>
-      <c r="C9" s="31"/>
-      <c r="D9" s="31"/>
-      <c r="E9" s="31"/>
-      <c r="F9" s="32"/>
-      <c r="G9" s="32"/>
-      <c r="H9" s="32"/>
-      <c r="I9" s="32"/>
-      <c r="J9" s="32"/>
-    </row>
-    <row r="10" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="31" t="s">
-        <v>23</v>
-      </c>
-      <c r="B10" s="31"/>
-      <c r="C10" s="31"/>
-      <c r="D10" s="31"/>
-      <c r="E10" s="31"/>
-      <c r="F10" s="32" t="s">
-        <v>24</v>
-      </c>
-      <c r="G10" s="32"/>
-      <c r="H10" s="32"/>
-      <c r="I10" s="32"/>
-      <c r="J10" s="32"/>
-    </row>
-    <row r="11" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="31"/>
-      <c r="B11" s="31"/>
-      <c r="C11" s="31"/>
-      <c r="D11" s="31"/>
-      <c r="E11" s="31"/>
-      <c r="F11" s="32"/>
-      <c r="G11" s="32"/>
-      <c r="H11" s="32"/>
-      <c r="I11" s="32"/>
-      <c r="J11" s="32"/>
-    </row>
-  </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="B1:C1"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="I2:J2"/>
-    <mergeCell ref="A8:E9"/>
-    <mergeCell ref="F8:J9"/>
-    <mergeCell ref="A10:E11"/>
-    <mergeCell ref="F10:J11"/>
-  </mergeCells>
-  <printOptions horizontalCentered="1" verticalCentered="1"/>
-  <pageMargins left="0.7086614173228347" right="0.7086614173228347" top="0.7480314960629921" bottom="0.7480314960629921" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet53.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:J11"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="10" width="42.15" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="4"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="J1" s="6"/>
-    </row>
-    <row r="2" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
-    </row>
-    <row r="3" ht="78.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="10"/>
-      <c r="D4" s="11"/>
-      <c r="E4" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="F4" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="G4" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="H4" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="I4" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J4" s="14" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" ht="150" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="B5" s="16"/>
-      <c r="C5" s="17"/>
-      <c r="D5" s="18"/>
-      <c r="E5" s="19"/>
-      <c r="F5" s="20"/>
-      <c r="G5" s="20"/>
-      <c r="H5" s="20"/>
-      <c r="I5" s="21"/>
-      <c r="J5" s="22"/>
-    </row>
-    <row r="6" ht="150" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="23" t="s">
-        <v>20</v>
-      </c>
-      <c r="B6" s="24"/>
-      <c r="C6" s="25"/>
-      <c r="D6" s="26"/>
-      <c r="E6" s="27"/>
-      <c r="F6" s="28"/>
-      <c r="G6" s="28"/>
-      <c r="H6" s="28"/>
-      <c r="I6" s="29"/>
-      <c r="J6" s="30"/>
-    </row>
-    <row r="7" ht="78.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="31" t="s">
-        <v>21</v>
-      </c>
-      <c r="B8" s="31"/>
-      <c r="C8" s="31"/>
-      <c r="D8" s="31"/>
-      <c r="E8" s="31"/>
-      <c r="F8" s="32" t="s">
-        <v>22</v>
-      </c>
-      <c r="G8" s="32"/>
-      <c r="H8" s="32"/>
-      <c r="I8" s="32"/>
-      <c r="J8" s="32"/>
-    </row>
-    <row r="9" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="31"/>
-      <c r="B9" s="31"/>
-      <c r="C9" s="31"/>
-      <c r="D9" s="31"/>
-      <c r="E9" s="31"/>
-      <c r="F9" s="32"/>
-      <c r="G9" s="32"/>
-      <c r="H9" s="32"/>
-      <c r="I9" s="32"/>
-      <c r="J9" s="32"/>
-    </row>
-    <row r="10" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="31" t="s">
-        <v>23</v>
-      </c>
-      <c r="B10" s="31"/>
-      <c r="C10" s="31"/>
-      <c r="D10" s="31"/>
-      <c r="E10" s="31"/>
-      <c r="F10" s="32" t="s">
-        <v>24</v>
-      </c>
-      <c r="G10" s="32"/>
-      <c r="H10" s="32"/>
-      <c r="I10" s="32"/>
-      <c r="J10" s="32"/>
-    </row>
-    <row r="11" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="31"/>
-      <c r="B11" s="31"/>
-      <c r="C11" s="31"/>
-      <c r="D11" s="31"/>
-      <c r="E11" s="31"/>
-      <c r="F11" s="32"/>
-      <c r="G11" s="32"/>
-      <c r="H11" s="32"/>
-      <c r="I11" s="32"/>
-      <c r="J11" s="32"/>
-    </row>
-  </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="B1:C1"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="I2:J2"/>
-    <mergeCell ref="A8:E9"/>
-    <mergeCell ref="F8:J9"/>
-    <mergeCell ref="A10:E11"/>
-    <mergeCell ref="F10:J11"/>
-  </mergeCells>
-  <printOptions horizontalCentered="1" verticalCentered="1"/>
-  <pageMargins left="0.7086614173228347" right="0.7086614173228347" top="0.7480314960629921" bottom="0.7480314960629921" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet54.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:J11"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="10" width="42.15" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="4"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="J1" s="6"/>
-    </row>
-    <row r="2" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
-    </row>
-    <row r="3" ht="78.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="10"/>
-      <c r="D4" s="11"/>
-      <c r="E4" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="F4" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="G4" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="H4" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="I4" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J4" s="14" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" ht="150" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="B5" s="16"/>
-      <c r="C5" s="17"/>
-      <c r="D5" s="18"/>
-      <c r="E5" s="19"/>
-      <c r="F5" s="20"/>
-      <c r="G5" s="20"/>
-      <c r="H5" s="20"/>
-      <c r="I5" s="21"/>
-      <c r="J5" s="22"/>
-    </row>
-    <row r="6" ht="150" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="23" t="s">
-        <v>20</v>
-      </c>
-      <c r="B6" s="24"/>
-      <c r="C6" s="25"/>
-      <c r="D6" s="26"/>
-      <c r="E6" s="27"/>
-      <c r="F6" s="28"/>
-      <c r="G6" s="28"/>
-      <c r="H6" s="28"/>
-      <c r="I6" s="29"/>
-      <c r="J6" s="30"/>
-    </row>
-    <row r="7" ht="78.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="31" t="s">
-        <v>21</v>
-      </c>
-      <c r="B8" s="31"/>
-      <c r="C8" s="31"/>
-      <c r="D8" s="31"/>
-      <c r="E8" s="31"/>
-      <c r="F8" s="32" t="s">
-        <v>22</v>
-      </c>
-      <c r="G8" s="32"/>
-      <c r="H8" s="32"/>
-      <c r="I8" s="32"/>
-      <c r="J8" s="32"/>
-    </row>
-    <row r="9" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="31"/>
-      <c r="B9" s="31"/>
-      <c r="C9" s="31"/>
-      <c r="D9" s="31"/>
-      <c r="E9" s="31"/>
-      <c r="F9" s="32"/>
-      <c r="G9" s="32"/>
-      <c r="H9" s="32"/>
-      <c r="I9" s="32"/>
-      <c r="J9" s="32"/>
-    </row>
-    <row r="10" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="31" t="s">
-        <v>23</v>
-      </c>
-      <c r="B10" s="31"/>
-      <c r="C10" s="31"/>
-      <c r="D10" s="31"/>
-      <c r="E10" s="31"/>
-      <c r="F10" s="32" t="s">
-        <v>24</v>
-      </c>
-      <c r="G10" s="32"/>
-      <c r="H10" s="32"/>
-      <c r="I10" s="32"/>
-      <c r="J10" s="32"/>
-    </row>
-    <row r="11" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="31"/>
-      <c r="B11" s="31"/>
-      <c r="C11" s="31"/>
-      <c r="D11" s="31"/>
-      <c r="E11" s="31"/>
-      <c r="F11" s="32"/>
-      <c r="G11" s="32"/>
-      <c r="H11" s="32"/>
-      <c r="I11" s="32"/>
-      <c r="J11" s="32"/>
-    </row>
-  </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="B1:C1"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="I2:J2"/>
-    <mergeCell ref="A8:E9"/>
-    <mergeCell ref="F8:J9"/>
-    <mergeCell ref="A10:E11"/>
-    <mergeCell ref="F10:J11"/>
-  </mergeCells>
-  <printOptions horizontalCentered="1" verticalCentered="1"/>
-  <pageMargins left="0.7086614173228347" right="0.7086614173228347" top="0.7480314960629921" bottom="0.7480314960629921" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet55.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:J11"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="10" width="42.15" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="4"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="J1" s="6"/>
-    </row>
-    <row r="2" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
-    </row>
-    <row r="3" ht="78.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="10"/>
-      <c r="D4" s="11"/>
-      <c r="E4" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="F4" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="G4" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="H4" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="I4" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J4" s="14" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" ht="150" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="B5" s="16"/>
-      <c r="C5" s="17"/>
-      <c r="D5" s="18"/>
-      <c r="E5" s="19"/>
-      <c r="F5" s="20"/>
-      <c r="G5" s="20"/>
-      <c r="H5" s="20"/>
-      <c r="I5" s="21"/>
-      <c r="J5" s="22"/>
-    </row>
-    <row r="6" ht="150" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="23" t="s">
-        <v>20</v>
-      </c>
-      <c r="B6" s="24"/>
-      <c r="C6" s="25"/>
-      <c r="D6" s="26"/>
-      <c r="E6" s="27"/>
-      <c r="F6" s="28"/>
-      <c r="G6" s="28"/>
-      <c r="H6" s="28"/>
-      <c r="I6" s="29"/>
-      <c r="J6" s="30"/>
-    </row>
-    <row r="7" ht="78.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="31" t="s">
-        <v>21</v>
-      </c>
-      <c r="B8" s="31"/>
-      <c r="C8" s="31"/>
-      <c r="D8" s="31"/>
-      <c r="E8" s="31"/>
-      <c r="F8" s="32" t="s">
-        <v>22</v>
-      </c>
-      <c r="G8" s="32"/>
-      <c r="H8" s="32"/>
-      <c r="I8" s="32"/>
-      <c r="J8" s="32"/>
-    </row>
-    <row r="9" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="31"/>
-      <c r="B9" s="31"/>
-      <c r="C9" s="31"/>
-      <c r="D9" s="31"/>
-      <c r="E9" s="31"/>
-      <c r="F9" s="32"/>
-      <c r="G9" s="32"/>
-      <c r="H9" s="32"/>
-      <c r="I9" s="32"/>
-      <c r="J9" s="32"/>
-    </row>
-    <row r="10" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="31" t="s">
-        <v>23</v>
-      </c>
-      <c r="B10" s="31"/>
-      <c r="C10" s="31"/>
-      <c r="D10" s="31"/>
-      <c r="E10" s="31"/>
-      <c r="F10" s="32" t="s">
-        <v>24</v>
-      </c>
-      <c r="G10" s="32"/>
-      <c r="H10" s="32"/>
-      <c r="I10" s="32"/>
-      <c r="J10" s="32"/>
-    </row>
-    <row r="11" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="31"/>
-      <c r="B11" s="31"/>
-      <c r="C11" s="31"/>
-      <c r="D11" s="31"/>
-      <c r="E11" s="31"/>
-      <c r="F11" s="32"/>
-      <c r="G11" s="32"/>
-      <c r="H11" s="32"/>
-      <c r="I11" s="32"/>
-      <c r="J11" s="32"/>
-    </row>
-  </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="B1:C1"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="I2:J2"/>
-    <mergeCell ref="A8:E9"/>
-    <mergeCell ref="F8:J9"/>
-    <mergeCell ref="A10:E11"/>
-    <mergeCell ref="F10:J11"/>
-  </mergeCells>
-  <printOptions horizontalCentered="1" verticalCentered="1"/>
-  <pageMargins left="0.7086614173228347" right="0.7086614173228347" top="0.7480314960629921" bottom="0.7480314960629921" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet56.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:J11"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="10" width="42.15" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="4"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="J1" s="6"/>
-    </row>
-    <row r="2" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
-    </row>
-    <row r="3" ht="78.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="10"/>
-      <c r="D4" s="11"/>
-      <c r="E4" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="F4" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="G4" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="H4" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="I4" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J4" s="14" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" ht="150" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="B5" s="16"/>
-      <c r="C5" s="17"/>
-      <c r="D5" s="18"/>
-      <c r="E5" s="19"/>
-      <c r="F5" s="20"/>
-      <c r="G5" s="20"/>
-      <c r="H5" s="20"/>
-      <c r="I5" s="21"/>
-      <c r="J5" s="22"/>
-    </row>
-    <row r="6" ht="150" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="23" t="s">
-        <v>20</v>
-      </c>
-      <c r="B6" s="24"/>
-      <c r="C6" s="25"/>
-      <c r="D6" s="26"/>
-      <c r="E6" s="27"/>
-      <c r="F6" s="28"/>
-      <c r="G6" s="28"/>
-      <c r="H6" s="28"/>
-      <c r="I6" s="29"/>
-      <c r="J6" s="30"/>
-    </row>
-    <row r="7" ht="78.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="31" t="s">
-        <v>21</v>
-      </c>
-      <c r="B8" s="31"/>
-      <c r="C8" s="31"/>
-      <c r="D8" s="31"/>
-      <c r="E8" s="31"/>
-      <c r="F8" s="32" t="s">
-        <v>22</v>
-      </c>
-      <c r="G8" s="32"/>
-      <c r="H8" s="32"/>
-      <c r="I8" s="32"/>
-      <c r="J8" s="32"/>
-    </row>
-    <row r="9" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="31"/>
-      <c r="B9" s="31"/>
-      <c r="C9" s="31"/>
-      <c r="D9" s="31"/>
-      <c r="E9" s="31"/>
-      <c r="F9" s="32"/>
-      <c r="G9" s="32"/>
-      <c r="H9" s="32"/>
-      <c r="I9" s="32"/>
-      <c r="J9" s="32"/>
-    </row>
-    <row r="10" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="31" t="s">
-        <v>23</v>
-      </c>
-      <c r="B10" s="31"/>
-      <c r="C10" s="31"/>
-      <c r="D10" s="31"/>
-      <c r="E10" s="31"/>
-      <c r="F10" s="32" t="s">
-        <v>24</v>
-      </c>
-      <c r="G10" s="32"/>
-      <c r="H10" s="32"/>
-      <c r="I10" s="32"/>
-      <c r="J10" s="32"/>
-    </row>
-    <row r="11" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="31"/>
-      <c r="B11" s="31"/>
-      <c r="C11" s="31"/>
-      <c r="D11" s="31"/>
-      <c r="E11" s="31"/>
-      <c r="F11" s="32"/>
-      <c r="G11" s="32"/>
-      <c r="H11" s="32"/>
-      <c r="I11" s="32"/>
-      <c r="J11" s="32"/>
-    </row>
-  </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="B1:C1"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B6:D6"/>
     <mergeCell ref="A8:E9"/>
     <mergeCell ref="F8:J9"/>
     <mergeCell ref="A10:E11"/>
@@ -10919,94 +8081,96 @@
       <c r="B5" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="C5" s="17"/>
-      <c r="D5" s="18"/>
-      <c r="E5" s="19"/>
-      <c r="F5" s="20"/>
-      <c r="G5" s="20"/>
-      <c r="H5" s="20"/>
-      <c r="I5" s="21"/>
-      <c r="J5" s="22"/>
+      <c r="C5" s="16"/>
+      <c r="D5" s="16"/>
+      <c r="E5" s="17"/>
+      <c r="F5" s="18"/>
+      <c r="G5" s="18"/>
+      <c r="H5" s="18"/>
+      <c r="I5" s="19"/>
+      <c r="J5" s="20"/>
     </row>
     <row r="6" ht="150" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="23" t="s">
+      <c r="A6" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="24" t="s">
+      <c r="B6" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="C6" s="25"/>
-      <c r="D6" s="26"/>
-      <c r="E6" s="27"/>
-      <c r="F6" s="28"/>
-      <c r="G6" s="28"/>
-      <c r="H6" s="28"/>
-      <c r="I6" s="29"/>
-      <c r="J6" s="30"/>
+      <c r="C6" s="22"/>
+      <c r="D6" s="22"/>
+      <c r="E6" s="23"/>
+      <c r="F6" s="24"/>
+      <c r="G6" s="24"/>
+      <c r="H6" s="24"/>
+      <c r="I6" s="25"/>
+      <c r="J6" s="26"/>
     </row>
     <row r="7" ht="78.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="8" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="31" t="s">
+      <c r="A8" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="31"/>
-      <c r="C8" s="31"/>
-      <c r="D8" s="31"/>
-      <c r="E8" s="31"/>
-      <c r="F8" s="32" t="s">
+      <c r="B8" s="27"/>
+      <c r="C8" s="27"/>
+      <c r="D8" s="27"/>
+      <c r="E8" s="27"/>
+      <c r="F8" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="G8" s="32"/>
-      <c r="H8" s="32"/>
-      <c r="I8" s="32"/>
-      <c r="J8" s="32"/>
+      <c r="G8" s="28"/>
+      <c r="H8" s="28"/>
+      <c r="I8" s="28"/>
+      <c r="J8" s="28"/>
     </row>
     <row r="9" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="31"/>
-      <c r="B9" s="31"/>
-      <c r="C9" s="31"/>
-      <c r="D9" s="31"/>
-      <c r="E9" s="31"/>
-      <c r="F9" s="32"/>
-      <c r="G9" s="32"/>
-      <c r="H9" s="32"/>
-      <c r="I9" s="32"/>
-      <c r="J9" s="32"/>
+      <c r="A9" s="27"/>
+      <c r="B9" s="27"/>
+      <c r="C9" s="27"/>
+      <c r="D9" s="27"/>
+      <c r="E9" s="27"/>
+      <c r="F9" s="28"/>
+      <c r="G9" s="28"/>
+      <c r="H9" s="28"/>
+      <c r="I9" s="28"/>
+      <c r="J9" s="28"/>
     </row>
     <row r="10" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="31" t="s">
+      <c r="A10" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="B10" s="31"/>
-      <c r="C10" s="31"/>
-      <c r="D10" s="31"/>
-      <c r="E10" s="31"/>
-      <c r="F10" s="32" t="s">
+      <c r="B10" s="27"/>
+      <c r="C10" s="27"/>
+      <c r="D10" s="27"/>
+      <c r="E10" s="27"/>
+      <c r="F10" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="G10" s="32"/>
-      <c r="H10" s="32"/>
-      <c r="I10" s="32"/>
-      <c r="J10" s="32"/>
+      <c r="G10" s="28"/>
+      <c r="H10" s="28"/>
+      <c r="I10" s="28"/>
+      <c r="J10" s="28"/>
     </row>
     <row r="11" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="31"/>
-      <c r="B11" s="31"/>
-      <c r="C11" s="31"/>
-      <c r="D11" s="31"/>
-      <c r="E11" s="31"/>
-      <c r="F11" s="32"/>
-      <c r="G11" s="32"/>
-      <c r="H11" s="32"/>
-      <c r="I11" s="32"/>
-      <c r="J11" s="32"/>
+      <c r="A11" s="27"/>
+      <c r="B11" s="27"/>
+      <c r="C11" s="27"/>
+      <c r="D11" s="27"/>
+      <c r="E11" s="27"/>
+      <c r="F11" s="28"/>
+      <c r="G11" s="28"/>
+      <c r="H11" s="28"/>
+      <c r="I11" s="28"/>
+      <c r="J11" s="28"/>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="10">
     <mergeCell ref="B1:C1"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="G2:H2"/>
     <mergeCell ref="I2:J2"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B6:D6"/>
     <mergeCell ref="A8:E9"/>
     <mergeCell ref="F8:J9"/>
     <mergeCell ref="A10:E11"/>
@@ -11111,94 +8275,96 @@
       <c r="B5" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="C5" s="17"/>
-      <c r="D5" s="18"/>
-      <c r="E5" s="19"/>
-      <c r="F5" s="20"/>
-      <c r="G5" s="20"/>
-      <c r="H5" s="20"/>
-      <c r="I5" s="21"/>
-      <c r="J5" s="22"/>
+      <c r="C5" s="16"/>
+      <c r="D5" s="16"/>
+      <c r="E5" s="17"/>
+      <c r="F5" s="18"/>
+      <c r="G5" s="18"/>
+      <c r="H5" s="18"/>
+      <c r="I5" s="19"/>
+      <c r="J5" s="20"/>
     </row>
     <row r="6" ht="150" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="23" t="s">
+      <c r="A6" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="24" t="s">
+      <c r="B6" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="C6" s="25"/>
-      <c r="D6" s="26"/>
-      <c r="E6" s="27"/>
-      <c r="F6" s="28"/>
-      <c r="G6" s="28"/>
-      <c r="H6" s="28"/>
-      <c r="I6" s="29"/>
-      <c r="J6" s="30"/>
+      <c r="C6" s="22"/>
+      <c r="D6" s="22"/>
+      <c r="E6" s="23"/>
+      <c r="F6" s="24"/>
+      <c r="G6" s="24"/>
+      <c r="H6" s="24"/>
+      <c r="I6" s="25"/>
+      <c r="J6" s="26"/>
     </row>
     <row r="7" ht="78.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="8" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="31" t="s">
+      <c r="A8" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="31"/>
-      <c r="C8" s="31"/>
-      <c r="D8" s="31"/>
-      <c r="E8" s="31"/>
-      <c r="F8" s="32" t="s">
+      <c r="B8" s="27"/>
+      <c r="C8" s="27"/>
+      <c r="D8" s="27"/>
+      <c r="E8" s="27"/>
+      <c r="F8" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="G8" s="32"/>
-      <c r="H8" s="32"/>
-      <c r="I8" s="32"/>
-      <c r="J8" s="32"/>
+      <c r="G8" s="28"/>
+      <c r="H8" s="28"/>
+      <c r="I8" s="28"/>
+      <c r="J8" s="28"/>
     </row>
     <row r="9" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="31"/>
-      <c r="B9" s="31"/>
-      <c r="C9" s="31"/>
-      <c r="D9" s="31"/>
-      <c r="E9" s="31"/>
-      <c r="F9" s="32"/>
-      <c r="G9" s="32"/>
-      <c r="H9" s="32"/>
-      <c r="I9" s="32"/>
-      <c r="J9" s="32"/>
+      <c r="A9" s="27"/>
+      <c r="B9" s="27"/>
+      <c r="C9" s="27"/>
+      <c r="D9" s="27"/>
+      <c r="E9" s="27"/>
+      <c r="F9" s="28"/>
+      <c r="G9" s="28"/>
+      <c r="H9" s="28"/>
+      <c r="I9" s="28"/>
+      <c r="J9" s="28"/>
     </row>
     <row r="10" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="31" t="s">
+      <c r="A10" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="B10" s="31"/>
-      <c r="C10" s="31"/>
-      <c r="D10" s="31"/>
-      <c r="E10" s="31"/>
-      <c r="F10" s="32" t="s">
+      <c r="B10" s="27"/>
+      <c r="C10" s="27"/>
+      <c r="D10" s="27"/>
+      <c r="E10" s="27"/>
+      <c r="F10" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="G10" s="32"/>
-      <c r="H10" s="32"/>
-      <c r="I10" s="32"/>
-      <c r="J10" s="32"/>
+      <c r="G10" s="28"/>
+      <c r="H10" s="28"/>
+      <c r="I10" s="28"/>
+      <c r="J10" s="28"/>
     </row>
     <row r="11" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="31"/>
-      <c r="B11" s="31"/>
-      <c r="C11" s="31"/>
-      <c r="D11" s="31"/>
-      <c r="E11" s="31"/>
-      <c r="F11" s="32"/>
-      <c r="G11" s="32"/>
-      <c r="H11" s="32"/>
-      <c r="I11" s="32"/>
-      <c r="J11" s="32"/>
+      <c r="A11" s="27"/>
+      <c r="B11" s="27"/>
+      <c r="C11" s="27"/>
+      <c r="D11" s="27"/>
+      <c r="E11" s="27"/>
+      <c r="F11" s="28"/>
+      <c r="G11" s="28"/>
+      <c r="H11" s="28"/>
+      <c r="I11" s="28"/>
+      <c r="J11" s="28"/>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="10">
     <mergeCell ref="B1:C1"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="G2:H2"/>
     <mergeCell ref="I2:J2"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B6:D6"/>
     <mergeCell ref="A8:E9"/>
     <mergeCell ref="F8:J9"/>
     <mergeCell ref="A10:E11"/>
@@ -11303,94 +8469,96 @@
       <c r="B5" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="C5" s="17"/>
-      <c r="D5" s="18"/>
-      <c r="E5" s="19"/>
-      <c r="F5" s="20"/>
-      <c r="G5" s="20"/>
-      <c r="H5" s="20"/>
-      <c r="I5" s="21"/>
-      <c r="J5" s="22"/>
+      <c r="C5" s="16"/>
+      <c r="D5" s="16"/>
+      <c r="E5" s="17"/>
+      <c r="F5" s="18"/>
+      <c r="G5" s="18"/>
+      <c r="H5" s="18"/>
+      <c r="I5" s="19"/>
+      <c r="J5" s="20"/>
     </row>
     <row r="6" ht="150" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="23" t="s">
+      <c r="A6" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="24" t="s">
+      <c r="B6" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="C6" s="25"/>
-      <c r="D6" s="26"/>
-      <c r="E6" s="27"/>
-      <c r="F6" s="28"/>
-      <c r="G6" s="28"/>
-      <c r="H6" s="28"/>
-      <c r="I6" s="29"/>
-      <c r="J6" s="30"/>
+      <c r="C6" s="22"/>
+      <c r="D6" s="22"/>
+      <c r="E6" s="23"/>
+      <c r="F6" s="24"/>
+      <c r="G6" s="24"/>
+      <c r="H6" s="24"/>
+      <c r="I6" s="25"/>
+      <c r="J6" s="26"/>
     </row>
     <row r="7" ht="78.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="8" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="31" t="s">
+      <c r="A8" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="31"/>
-      <c r="C8" s="31"/>
-      <c r="D8" s="31"/>
-      <c r="E8" s="31"/>
-      <c r="F8" s="32" t="s">
+      <c r="B8" s="27"/>
+      <c r="C8" s="27"/>
+      <c r="D8" s="27"/>
+      <c r="E8" s="27"/>
+      <c r="F8" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="G8" s="32"/>
-      <c r="H8" s="32"/>
-      <c r="I8" s="32"/>
-      <c r="J8" s="32"/>
+      <c r="G8" s="28"/>
+      <c r="H8" s="28"/>
+      <c r="I8" s="28"/>
+      <c r="J8" s="28"/>
     </row>
     <row r="9" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="31"/>
-      <c r="B9" s="31"/>
-      <c r="C9" s="31"/>
-      <c r="D9" s="31"/>
-      <c r="E9" s="31"/>
-      <c r="F9" s="32"/>
-      <c r="G9" s="32"/>
-      <c r="H9" s="32"/>
-      <c r="I9" s="32"/>
-      <c r="J9" s="32"/>
+      <c r="A9" s="27"/>
+      <c r="B9" s="27"/>
+      <c r="C9" s="27"/>
+      <c r="D9" s="27"/>
+      <c r="E9" s="27"/>
+      <c r="F9" s="28"/>
+      <c r="G9" s="28"/>
+      <c r="H9" s="28"/>
+      <c r="I9" s="28"/>
+      <c r="J9" s="28"/>
     </row>
     <row r="10" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="31" t="s">
+      <c r="A10" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="B10" s="31"/>
-      <c r="C10" s="31"/>
-      <c r="D10" s="31"/>
-      <c r="E10" s="31"/>
-      <c r="F10" s="32" t="s">
+      <c r="B10" s="27"/>
+      <c r="C10" s="27"/>
+      <c r="D10" s="27"/>
+      <c r="E10" s="27"/>
+      <c r="F10" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="G10" s="32"/>
-      <c r="H10" s="32"/>
-      <c r="I10" s="32"/>
-      <c r="J10" s="32"/>
+      <c r="G10" s="28"/>
+      <c r="H10" s="28"/>
+      <c r="I10" s="28"/>
+      <c r="J10" s="28"/>
     </row>
     <row r="11" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="31"/>
-      <c r="B11" s="31"/>
-      <c r="C11" s="31"/>
-      <c r="D11" s="31"/>
-      <c r="E11" s="31"/>
-      <c r="F11" s="32"/>
-      <c r="G11" s="32"/>
-      <c r="H11" s="32"/>
-      <c r="I11" s="32"/>
-      <c r="J11" s="32"/>
+      <c r="A11" s="27"/>
+      <c r="B11" s="27"/>
+      <c r="C11" s="27"/>
+      <c r="D11" s="27"/>
+      <c r="E11" s="27"/>
+      <c r="F11" s="28"/>
+      <c r="G11" s="28"/>
+      <c r="H11" s="28"/>
+      <c r="I11" s="28"/>
+      <c r="J11" s="28"/>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="10">
     <mergeCell ref="B1:C1"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="G2:H2"/>
     <mergeCell ref="I2:J2"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B6:D6"/>
     <mergeCell ref="A8:E9"/>
     <mergeCell ref="F8:J9"/>
     <mergeCell ref="A10:E11"/>
@@ -11495,94 +8663,96 @@
       <c r="B5" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="C5" s="17"/>
-      <c r="D5" s="18"/>
-      <c r="E5" s="19"/>
-      <c r="F5" s="20"/>
-      <c r="G5" s="20"/>
-      <c r="H5" s="20"/>
-      <c r="I5" s="21"/>
-      <c r="J5" s="22"/>
+      <c r="C5" s="16"/>
+      <c r="D5" s="16"/>
+      <c r="E5" s="17"/>
+      <c r="F5" s="18"/>
+      <c r="G5" s="18"/>
+      <c r="H5" s="18"/>
+      <c r="I5" s="19"/>
+      <c r="J5" s="20"/>
     </row>
     <row r="6" ht="150" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="23" t="s">
+      <c r="A6" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="24" t="s">
+      <c r="B6" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="C6" s="25"/>
-      <c r="D6" s="26"/>
-      <c r="E6" s="27"/>
-      <c r="F6" s="28"/>
-      <c r="G6" s="28"/>
-      <c r="H6" s="28"/>
-      <c r="I6" s="29"/>
-      <c r="J6" s="30"/>
+      <c r="C6" s="22"/>
+      <c r="D6" s="22"/>
+      <c r="E6" s="23"/>
+      <c r="F6" s="24"/>
+      <c r="G6" s="24"/>
+      <c r="H6" s="24"/>
+      <c r="I6" s="25"/>
+      <c r="J6" s="26"/>
     </row>
     <row r="7" ht="78.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="8" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="31" t="s">
+      <c r="A8" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="31"/>
-      <c r="C8" s="31"/>
-      <c r="D8" s="31"/>
-      <c r="E8" s="31"/>
-      <c r="F8" s="32" t="s">
+      <c r="B8" s="27"/>
+      <c r="C8" s="27"/>
+      <c r="D8" s="27"/>
+      <c r="E8" s="27"/>
+      <c r="F8" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="G8" s="32"/>
-      <c r="H8" s="32"/>
-      <c r="I8" s="32"/>
-      <c r="J8" s="32"/>
+      <c r="G8" s="28"/>
+      <c r="H8" s="28"/>
+      <c r="I8" s="28"/>
+      <c r="J8" s="28"/>
     </row>
     <row r="9" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="31"/>
-      <c r="B9" s="31"/>
-      <c r="C9" s="31"/>
-      <c r="D9" s="31"/>
-      <c r="E9" s="31"/>
-      <c r="F9" s="32"/>
-      <c r="G9" s="32"/>
-      <c r="H9" s="32"/>
-      <c r="I9" s="32"/>
-      <c r="J9" s="32"/>
+      <c r="A9" s="27"/>
+      <c r="B9" s="27"/>
+      <c r="C9" s="27"/>
+      <c r="D9" s="27"/>
+      <c r="E9" s="27"/>
+      <c r="F9" s="28"/>
+      <c r="G9" s="28"/>
+      <c r="H9" s="28"/>
+      <c r="I9" s="28"/>
+      <c r="J9" s="28"/>
     </row>
     <row r="10" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="31" t="s">
+      <c r="A10" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="B10" s="31"/>
-      <c r="C10" s="31"/>
-      <c r="D10" s="31"/>
-      <c r="E10" s="31"/>
-      <c r="F10" s="32" t="s">
+      <c r="B10" s="27"/>
+      <c r="C10" s="27"/>
+      <c r="D10" s="27"/>
+      <c r="E10" s="27"/>
+      <c r="F10" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="G10" s="32"/>
-      <c r="H10" s="32"/>
-      <c r="I10" s="32"/>
-      <c r="J10" s="32"/>
+      <c r="G10" s="28"/>
+      <c r="H10" s="28"/>
+      <c r="I10" s="28"/>
+      <c r="J10" s="28"/>
     </row>
     <row r="11" ht="78.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="31"/>
-      <c r="B11" s="31"/>
-      <c r="C11" s="31"/>
-      <c r="D11" s="31"/>
-      <c r="E11" s="31"/>
-      <c r="F11" s="32"/>
-      <c r="G11" s="32"/>
-      <c r="H11" s="32"/>
-      <c r="I11" s="32"/>
-      <c r="J11" s="32"/>
+      <c r="A11" s="27"/>
+      <c r="B11" s="27"/>
+      <c r="C11" s="27"/>
+      <c r="D11" s="27"/>
+      <c r="E11" s="27"/>
+      <c r="F11" s="28"/>
+      <c r="G11" s="28"/>
+      <c r="H11" s="28"/>
+      <c r="I11" s="28"/>
+      <c r="J11" s="28"/>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="10">
     <mergeCell ref="B1:C1"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="G2:H2"/>
     <mergeCell ref="I2:J2"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B6:D6"/>
     <mergeCell ref="A8:E9"/>
     <mergeCell ref="F8:J9"/>
     <mergeCell ref="A10:E11"/>
